--- a/DesignData/Excel_Masters/CharacterAssets_Master.xlsx
+++ b/DesignData/Excel_Masters/CharacterAssets_Master.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="106">
   <si>
     <t>Char_Anubis</t>
   </si>
@@ -130,6 +130,213 @@
   </si>
   <si>
     <t>UltimateEffectTag</t>
+  </si>
+  <si>
+    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Anubis/SKM_Anubis_Base.SKM_Anubis_Base'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Anubis.Icon_Anubis'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Anubis.Icon_Anubis'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Army/SKM_Army_Base.SKM_Army_Base'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Army.Icon_Army'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Army.Icon_Army'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Bard/SKM_Bard_Base.SKM_Bard_Base'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Bard.Icon_Bard'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Bard.Icon_Bard'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Binder/SKM_Binder_Base.SKM_Binder_Base'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Binder.Icon_Binder'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Binder.Icon_Binder'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Courier/SKM_Courier_Base.SKM_Courier_Base'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Courier.Icon_Courier'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Courier.Icon_Courier'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Demonia/SKM_Demonia_Base.SKM_Demonia_Base'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Demonia.Icon_Demonia'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Demonia.Icon_Demonia'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Enchanter/SKM_Enchanter_Base.SKM_Enchanter_Base'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Enchanter.Icon_Enchanter'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Enchanter.Icon_Enchanter'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Guard/SKM_Guard_Base.SKM_Guard_Base'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Guard.Icon_Guard'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Guard.Icon_Guard'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Hermit/SKM_Hermit_Base.SKM_Hermit_Base'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Hermit.Icon_Hermit'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Hermit.Icon_Hermit'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Hornet/SKM_Hornet_Base.SKM_Hornet_Base'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Hornet.Icon_Hornet'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Hornet.Icon_Hornet'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Looter/SKM_Looter_Base.SKM_Looter_Base'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Looter.Icon_Looter'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Looter.Icon_Looter'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Maid/SKM_Maid_Base.SKM_Maid_Base'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Maid.Icon_Maid'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Maid.Icon_Maid'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Merry/SKM_Merry_Base.SKM_Merry_Base'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Merry.Icon_Merry'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Merry.Icon_Merry'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Muzzle/SKM_Muzzle_Base.SKM_Muzzle_Base'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Muzzle.Icon_Muzzle'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Muzzle.Icon_Muzzle'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Noble/SKM_Noble_Base.SKM_Noble_Base'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Noble.Icon_Noble'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Noble.Icon_Noble'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Nurse/SKM_Nurse_Base.SKM_Nurse_Base'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Nurse.Icon_Nurse'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Nurse.Icon_Nurse'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Outsider/SKM_Outsider_Base.SKM_Outsider_Base'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Outsider.Icon_Outsider'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Outsider.Icon_Outsider'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Pioneer/SKM_Pioneer_Base.SKM_Pioneer_Base'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Pioneer.Icon_Pioneer'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Pioneer.Icon_Pioneer'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Rogue/SKM_Rogue_Base.SKM_Rogue_Base'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Rogue.Icon_Rogue'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Rogue.Icon_Rogue'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Tinker/SKM_Tinker_Base.SKM_Tinker_Base'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Tinker.Icon_Tinker'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Tinker.Icon_Tinker'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Tuner/SKM_Tuner_Base.SKM_Tuner_Base'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Tuner.Icon_Tuner'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Tuner.Icon_Tuner'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Weaver/SKM_Weaver_Base.SKM_Weaver_Base'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Weaver.Icon_Weaver'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Weaver.Icon_Weaver'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Writer/SKM_Writer_Base.SKM_Writer_Base'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Writer.Icon_Writer'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Writer.Icon_Writer'</t>
   </si>
 </sst>
 </file>
@@ -1098,115 +1305,322 @@
       <c r="A2" t="s">
         <v>0</v>
       </c>
+      <c r="B2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
+      <c r="B3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J3" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
+      <c r="B4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J4" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
+      <c r="B5" t="s">
+        <v>46</v>
+      </c>
+      <c r="I5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J5" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
+      <c r="B6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J6" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
+      <c r="B7" t="s">
+        <v>52</v>
+      </c>
+      <c r="I7" t="s">
+        <v>53</v>
+      </c>
+      <c r="J7" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
+      <c r="B8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I8" t="s">
+        <v>56</v>
+      </c>
+      <c r="J8" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
+      <c r="B9" t="s">
+        <v>58</v>
+      </c>
+      <c r="I9" t="s">
+        <v>59</v>
+      </c>
+      <c r="J9" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
+      <c r="B10" t="s">
+        <v>61</v>
+      </c>
+      <c r="I10" t="s">
+        <v>62</v>
+      </c>
+      <c r="J10" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
+      <c r="B11" t="s">
+        <v>64</v>
+      </c>
+      <c r="I11" t="s">
+        <v>65</v>
+      </c>
+      <c r="J11" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>10</v>
       </c>
+      <c r="B12" t="s">
+        <v>67</v>
+      </c>
+      <c r="I12" t="s">
+        <v>68</v>
+      </c>
+      <c r="J12" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>11</v>
       </c>
+      <c r="B13" t="s">
+        <v>70</v>
+      </c>
+      <c r="I13" t="s">
+        <v>71</v>
+      </c>
+      <c r="J13" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
+      <c r="B14" t="s">
+        <v>73</v>
+      </c>
+      <c r="I14" t="s">
+        <v>74</v>
+      </c>
+      <c r="J14" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>13</v>
       </c>
+      <c r="B15" t="s">
+        <v>76</v>
+      </c>
+      <c r="I15" t="s">
+        <v>77</v>
+      </c>
+      <c r="J15" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>79</v>
+      </c>
+      <c r="I16" t="s">
+        <v>80</v>
+      </c>
+      <c r="J16" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>82</v>
+      </c>
+      <c r="I17" t="s">
+        <v>83</v>
+      </c>
+      <c r="J17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>85</v>
+      </c>
+      <c r="I18" t="s">
+        <v>86</v>
+      </c>
+      <c r="J18" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>88</v>
+      </c>
+      <c r="I19" t="s">
+        <v>89</v>
+      </c>
+      <c r="J19" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>91</v>
+      </c>
+      <c r="I20" t="s">
+        <v>92</v>
+      </c>
+      <c r="J20" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>94</v>
+      </c>
+      <c r="I21" t="s">
+        <v>95</v>
+      </c>
+      <c r="J21" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>97</v>
+      </c>
+      <c r="I22" t="s">
+        <v>98</v>
+      </c>
+      <c r="J22" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>100</v>
+      </c>
+      <c r="I23" t="s">
+        <v>101</v>
+      </c>
+      <c r="J23" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>103</v>
+      </c>
+      <c r="I24" t="s">
+        <v>104</v>
+      </c>
+      <c r="J24" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/DesignData/Excel_Masters/CharacterAssets_Master.xlsx
+++ b/DesignData/Excel_Masters/CharacterAssets_Master.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>Char_Anubis</t>
   </si>
@@ -130,213 +130,6 @@
   </si>
   <si>
     <t>UltimateEffectTag</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Anubis/SKM_Anubis_Base.SKM_Anubis_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Anubis.Icon_Anubis'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Anubis.Icon_Anubis'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Army/SKM_Army_Base.SKM_Army_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Army.Icon_Army'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Army.Icon_Army'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Bard/SKM_Bard_Base.SKM_Bard_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Bard.Icon_Bard'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Bard.Icon_Bard'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Binder/SKM_Binder_Base.SKM_Binder_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Binder.Icon_Binder'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Binder.Icon_Binder'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Courier/SKM_Courier_Base.SKM_Courier_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Courier.Icon_Courier'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Courier.Icon_Courier'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Demonia/SKM_Demonia_Base.SKM_Demonia_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Demonia.Icon_Demonia'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Demonia.Icon_Demonia'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Enchanter/SKM_Enchanter_Base.SKM_Enchanter_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Enchanter.Icon_Enchanter'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Enchanter.Icon_Enchanter'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Guard/SKM_Guard_Base.SKM_Guard_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Guard.Icon_Guard'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Guard.Icon_Guard'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Hermit/SKM_Hermit_Base.SKM_Hermit_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Hermit.Icon_Hermit'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Hermit.Icon_Hermit'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Hornet/SKM_Hornet_Base.SKM_Hornet_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Hornet.Icon_Hornet'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Hornet.Icon_Hornet'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Looter/SKM_Looter_Base.SKM_Looter_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Looter.Icon_Looter'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Looter.Icon_Looter'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Maid/SKM_Maid_Base.SKM_Maid_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Maid.Icon_Maid'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Maid.Icon_Maid'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Merry/SKM_Merry_Base.SKM_Merry_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Merry.Icon_Merry'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Merry.Icon_Merry'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Muzzle/SKM_Muzzle_Base.SKM_Muzzle_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Muzzle.Icon_Muzzle'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Muzzle.Icon_Muzzle'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Noble/SKM_Noble_Base.SKM_Noble_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Noble.Icon_Noble'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Noble.Icon_Noble'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Nurse/SKM_Nurse_Base.SKM_Nurse_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Nurse.Icon_Nurse'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Nurse.Icon_Nurse'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Outsider/SKM_Outsider_Base.SKM_Outsider_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Outsider.Icon_Outsider'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Outsider.Icon_Outsider'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Pioneer/SKM_Pioneer_Base.SKM_Pioneer_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Pioneer.Icon_Pioneer'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Pioneer.Icon_Pioneer'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Rogue/SKM_Rogue_Base.SKM_Rogue_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Rogue.Icon_Rogue'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Rogue.Icon_Rogue'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Tinker/SKM_Tinker_Base.SKM_Tinker_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Tinker.Icon_Tinker'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Tinker.Icon_Tinker'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Tuner/SKM_Tuner_Base.SKM_Tuner_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Tuner.Icon_Tuner'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Tuner.Icon_Tuner'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Weaver/SKM_Weaver_Base.SKM_Weaver_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Weaver.Icon_Weaver'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Weaver.Icon_Weaver'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Writer/SKM_Writer_Base.SKM_Writer_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Writer.Icon_Writer'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Writer.Icon_Writer'</t>
   </si>
 </sst>
 </file>
@@ -1305,322 +1098,115 @@
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J2" t="s">
-        <v>39</v>
-      </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
-        <v>40</v>
-      </c>
-      <c r="I3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J3" t="s">
-        <v>42</v>
-      </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
-        <v>43</v>
-      </c>
-      <c r="I4" t="s">
-        <v>44</v>
-      </c>
-      <c r="J4" t="s">
-        <v>45</v>
-      </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I5" t="s">
-        <v>47</v>
-      </c>
-      <c r="J5" t="s">
-        <v>48</v>
-      </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="B6" t="s">
-        <v>49</v>
-      </c>
-      <c r="I6" t="s">
-        <v>50</v>
-      </c>
-      <c r="J6" t="s">
-        <v>51</v>
-      </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
-      <c r="B7" t="s">
-        <v>52</v>
-      </c>
-      <c r="I7" t="s">
-        <v>53</v>
-      </c>
-      <c r="J7" t="s">
-        <v>54</v>
-      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
-      <c r="B8" t="s">
-        <v>55</v>
-      </c>
-      <c r="I8" t="s">
-        <v>56</v>
-      </c>
-      <c r="J8" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
-      <c r="B9" t="s">
-        <v>58</v>
-      </c>
-      <c r="I9" t="s">
-        <v>59</v>
-      </c>
-      <c r="J9" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
-      <c r="B10" t="s">
-        <v>61</v>
-      </c>
-      <c r="I10" t="s">
-        <v>62</v>
-      </c>
-      <c r="J10" t="s">
-        <v>63</v>
-      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
-      <c r="B11" t="s">
-        <v>64</v>
-      </c>
-      <c r="I11" t="s">
-        <v>65</v>
-      </c>
-      <c r="J11" t="s">
-        <v>66</v>
-      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>10</v>
       </c>
-      <c r="B12" t="s">
-        <v>67</v>
-      </c>
-      <c r="I12" t="s">
-        <v>68</v>
-      </c>
-      <c r="J12" t="s">
-        <v>69</v>
-      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>11</v>
       </c>
-      <c r="B13" t="s">
-        <v>70</v>
-      </c>
-      <c r="I13" t="s">
-        <v>71</v>
-      </c>
-      <c r="J13" t="s">
-        <v>72</v>
-      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
-      <c r="B14" t="s">
-        <v>73</v>
-      </c>
-      <c r="I14" t="s">
-        <v>74</v>
-      </c>
-      <c r="J14" t="s">
-        <v>75</v>
-      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>13</v>
       </c>
-      <c r="B15" t="s">
-        <v>76</v>
-      </c>
-      <c r="I15" t="s">
-        <v>77</v>
-      </c>
-      <c r="J15" t="s">
-        <v>78</v>
-      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>14</v>
       </c>
-      <c r="B16" t="s">
-        <v>79</v>
-      </c>
-      <c r="I16" t="s">
-        <v>80</v>
-      </c>
-      <c r="J16" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>15</v>
       </c>
-      <c r="B17" t="s">
-        <v>82</v>
-      </c>
-      <c r="I17" t="s">
-        <v>83</v>
-      </c>
-      <c r="J17" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>16</v>
       </c>
-      <c r="B18" t="s">
-        <v>85</v>
-      </c>
-      <c r="I18" t="s">
-        <v>86</v>
-      </c>
-      <c r="J18" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>17</v>
       </c>
-      <c r="B19" t="s">
-        <v>88</v>
-      </c>
-      <c r="I19" t="s">
-        <v>89</v>
-      </c>
-      <c r="J19" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
-      <c r="B20" t="s">
-        <v>91</v>
-      </c>
-      <c r="I20" t="s">
-        <v>92</v>
-      </c>
-      <c r="J20" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>19</v>
       </c>
-      <c r="B21" t="s">
-        <v>94</v>
-      </c>
-      <c r="I21" t="s">
-        <v>95</v>
-      </c>
-      <c r="J21" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>20</v>
       </c>
-      <c r="B22" t="s">
-        <v>97</v>
-      </c>
-      <c r="I22" t="s">
-        <v>98</v>
-      </c>
-      <c r="J22" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>21</v>
       </c>
-      <c r="B23" t="s">
-        <v>100</v>
-      </c>
-      <c r="I23" t="s">
-        <v>101</v>
-      </c>
-      <c r="J23" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>22</v>
-      </c>
-      <c r="B24" t="s">
-        <v>103</v>
-      </c>
-      <c r="I24" t="s">
-        <v>104</v>
-      </c>
-      <c r="J24" t="s">
-        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/DesignData/Excel_Masters/CharacterAssets_Master.xlsx
+++ b/DesignData/Excel_Masters/CharacterAssets_Master.xlsx
@@ -9,334 +9,430 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21555" windowHeight="8040"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25680" windowHeight="10965"/>
   </bookViews>
   <sheets>
-    <sheet name="CharacterStats_Master" sheetId="1" r:id="rId1"/>
+    <sheet name="CharacterAssets" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="138">
+  <si>
+    <t>---</t>
+  </si>
+  <si>
+    <t>FaceIcon</t>
+  </si>
+  <si>
+    <t>BodyIcon</t>
+  </si>
+  <si>
+    <t>UltimateAbility</t>
+  </si>
+  <si>
+    <t>UltimateDamageEffect</t>
+  </si>
+  <si>
+    <t>UltimateMontage</t>
+  </si>
+  <si>
+    <t>WeaponAnimMap</t>
+  </si>
+  <si>
+    <t>UltimateEffectTag</t>
+  </si>
+  <si>
+    <t>FactionTag</t>
+  </si>
+  <si>
+    <t>SkeletalMesh</t>
+  </si>
+  <si>
+    <t>AnimBlueprint</t>
+  </si>
+  <si>
+    <t>HitMontage</t>
+  </si>
+  <si>
+    <t>DeathMontage</t>
+  </si>
+  <si>
+    <t>ReactionFX</t>
+  </si>
   <si>
     <t>Char_Anubis</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Anubis.Icon_Anubis</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Anubis.Icon_Anubis</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>()</t>
+  </si>
+  <si>
+    <t>(TagName="")</t>
+  </si>
+  <si>
+    <t>(TagName="Unit.Faction.Friendly.Player")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Player/Anubis/SKM_Anubis_Base.SKM_Anubis_Base</t>
+  </si>
+  <si>
+    <t>(ReactionFXData=None,HitTag=(TagName=""),DeathTag=(TagName=""))</t>
+  </si>
+  <si>
     <t>Char_Army</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Army.Icon_Army</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Army.Icon_Army</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Player/Army/AM_Army_Ultimate_Attack.AM_Army_Ultimate_Attack</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Army/AM_Army_Book_Attack.AM_Army_Book_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Army/AM_Army_Book_Skill.AM_Army_Book_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Army/AM_Army_Melee_Attack.AM_Army_Melee_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Army/AM_Army_Melee_Attack.AM_Army_Melee_Attack")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Army/AM_Army_Gun_Attack.AM_Army_Gun_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Army/AM_Army_Gun_Attack.AM_Army_Gun_Attack")))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Player/Army/SKM_Army_Base.SKM_Army_Base</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Player/Army/ABP_Base_Army.ABP_Base_Army_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Player/Army/AM_Army_Damage.AM_Army_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Player/Army/AM_Army_Dead.AM_Army_Dead</t>
+  </si>
+  <si>
     <t>Char_Bard</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Bard.Icon_Bard</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Bard.Icon_Bard</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Player/Bard/SKM_Bard_Base.SKM_Bard_Base</t>
+  </si>
+  <si>
     <t>Char_Binder</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Binder.Icon_Binder</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Binder.Icon_Binder</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Player/Binder/SKM_Binder_Base.SKM_Binder_Base</t>
+  </si>
+  <si>
     <t>Char_Courier</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Courier.Icon_Courier</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Courier.Icon_Courier</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Player/Courier/SKM_Courier_Base.SKM_Courier_Base</t>
+  </si>
+  <si>
     <t>Char_Demonia</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Demonia.Icon_Demonia</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Demonia.Icon_Demonia</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Player/Demonia/SKM_Demonia_Base.SKM_Demonia_Base</t>
+  </si>
+  <si>
     <t>Char_Enchanter</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Enchanter.Icon_Enchanter</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Enchanter.Icon_Enchanter</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Player/Enchanter/SKM_Enchanter_Base.SKM_Enchanter_Base</t>
+  </si>
+  <si>
     <t>Char_Guard</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Guard.Icon_Guard</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Guard.Icon_Guard</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Player/Guard/SKM_Guard_Base.SKM_Guard_Base</t>
+  </si>
+  <si>
     <t>Char_Hermit</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Hermit.Icon_Hermit</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Hermit.Icon_Hermit</t>
+  </si>
+  <si>
+    <t>/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_MeleeUltimate.GA_MeleeUltimate_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Standard.GE_Damage_Standard_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Ultimate_Attack.AM_Hermit_Ultimate_Attack</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Book_Attack.AM_Hermit_Book_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Book_Attack.AM_Hermit_Book_Attack")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Melee_Attack.AM_Hermit_Melee_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Melee_Attack.AM_Hermit_Melee_Attack")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Gun_Attack.AM_Hermit_Gun_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Gun_Attack.AM_Hermit_Gun_Attack")))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Player/Hermit/SKM_Hermit_Base.SKM_Hermit_Base</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Player/Hermit/ABP_Base_Hermit.ABP_Base_Hermit_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Damage.AM_Hermit_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Dead.AM_Hermit_Dead</t>
+  </si>
+  <si>
     <t>Char_Hornet</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Hornet.Icon_Hornet</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Hornet.Icon_Hornet</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Ultimate.AM_Hornet_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Book_Attack.AM_Hornet_Book_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Book_Attack.AM_Hornet_Book_Attack")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Melee_Attack.AM_Hornet_Melee_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Melee_Attack.AM_Hornet_Melee_Attack")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Gun_Attack.AM_Hornet_Gun_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Gun_Attack.AM_Hornet_Gun_Attack")))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Player/Hornet/SKM_Hornet_Base.SKM_Hornet_Base</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Player/Hornet/ABP_Base_Hornet.ABP_Base_Hornet_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Damage.AM_Hornet_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Dead.AM_Hornet_Dead</t>
+  </si>
+  <si>
     <t>Char_Looter</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Looter.Icon_Looter</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Looter.Icon_Looter</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Player/Looter/SKM_Looter_Base.SKM_Looter_Base</t>
+  </si>
+  <si>
     <t>Char_Maid</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Maid.Icon_Maid</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Maid.Icon_Maid</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Player/Maid/SKM_Maid_Base.SKM_Maid_Base</t>
+  </si>
+  <si>
     <t>Char_Merry</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Merry.Icon_Merry</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Merry.Icon_Merry</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Player/Merry/SKM_Merry_Base.SKM_Merry_Base</t>
+  </si>
+  <si>
     <t>Char_Muzzle</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Muzzle.Icon_Muzzle</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Muzzle.Icon_Muzzle</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Player/Muzzle/SKM_Muzzle_Base.SKM_Muzzle_Base</t>
+  </si>
+  <si>
     <t>Char_Noble</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Noble.Icon_Noble</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Noble.Icon_Noble</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Player/Noble/SKM_Noble_Base.SKM_Noble_Base</t>
+  </si>
+  <si>
     <t>Char_Nurse</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Nurse.Icon_Nurse</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Nurse.Icon_Nurse</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Player/Nurse/SKM_Nurse_Base.SKM_Nurse_Base</t>
+  </si>
+  <si>
     <t>Char_Outsider</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Outsider.Icon_Outsider</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Outsider.Icon_Outsider</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Player/Outsider/SKM_Outsider_Base.SKM_Outsider_Base</t>
+  </si>
+  <si>
     <t>Char_Pioneer</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Pioneer.Icon_Pioneer</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Pioneer.Icon_Pioneer</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Ultimate.AM_Pioneer_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Book_Attack.AM_Pioneer_Book_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Book_Attack.AM_Pioneer_Book_Attack")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Sword_Attack.AM_Pioneer_Sword_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Sword_Attack.AM_Pioneer_Sword_Attack")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Gun_Attack.AM_Pioneer_Gun_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Gun_Attack.AM_Pioneer_Gun_Attack")))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Player/Pioneer/SKM_Pioneer_Base.SKM_Pioneer_Base</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Player/Pioneer/ABP_Pioneer.ABP_Pioneer_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Damage.AM_Pioneer_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Dead.AM_Pioneer_Dead</t>
+  </si>
+  <si>
     <t>Char_Rogue</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Rogue.Icon_Rogue</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Rogue.Icon_Rogue</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Player/Rogue/SKM_Rogue_Base.SKM_Rogue_Base</t>
+  </si>
+  <si>
     <t>Char_Tinker</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Tinker.Icon_Tinker</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Tinker.Icon_Tinker</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Player/Tinker/AM_Ultimate_Attack.AM_Ultimate_Attack</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Tinker/AM_Book_Attack.AM_Book_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Tinker/AM_Book_Attack.AM_Book_Attack")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Tinker/AM_Melee_Attack.AM_Melee_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Tinker/AM_Melee_Blunt_Attack.AM_Melee_Blunt_Attack")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Tinker/AM_Gun_Attack.AM_Gun_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Tinker/AM_Gun_Attack.AM_Gun_Attack")))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Player/Tinker/SKM_Tinker_Base.SKM_Tinker_Base</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Player/Tinker/ABP_Base.ABP_Base_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Player/Tinker/AM_Damage.AM_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Player/Tinker/AM_Dead.AM_Dead</t>
+  </si>
+  <si>
     <t>Char_Tuner</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Tuner.Icon_Tuner</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Tuner.Icon_Tuner</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Player/Tuner/SKM_Tuner_Base.SKM_Tuner_Base</t>
+  </si>
+  <si>
     <t>Char_Weaver</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Weaver.Icon_Weaver</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Weaver.Icon_Weaver</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Player/Weaver/SKM_Weaver_Base.SKM_Weaver_Base</t>
+  </si>
+  <si>
     <t>Char_Writer</t>
   </si>
   <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>SkeletalMesh</t>
-  </si>
-  <si>
-    <t>AnimBlueprint</t>
-  </si>
-  <si>
-    <t>AttackMontage</t>
-  </si>
-  <si>
-    <t>HitMontage</t>
-  </si>
-  <si>
-    <t>DeathMontage</t>
-  </si>
-  <si>
-    <t>VoiceDataAsset</t>
-  </si>
-  <si>
-    <t>HitReactionTag</t>
-  </si>
-  <si>
-    <t>FaceIcon</t>
-  </si>
-  <si>
-    <t>BodyIcon</t>
-  </si>
-  <si>
-    <t>UltimateAbility</t>
-  </si>
-  <si>
-    <t>UltimateDamageEffect</t>
-  </si>
-  <si>
-    <t>UltimateMontage</t>
-  </si>
-  <si>
-    <t>UltimateEffectTag</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Anubis/SKM_Anubis_Base.SKM_Anubis_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Anubis.Icon_Anubis'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Anubis.Icon_Anubis'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Army/SKM_Army_Base.SKM_Army_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Army.Icon_Army'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Army.Icon_Army'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Bard/SKM_Bard_Base.SKM_Bard_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Bard.Icon_Bard'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Bard.Icon_Bard'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Binder/SKM_Binder_Base.SKM_Binder_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Binder.Icon_Binder'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Binder.Icon_Binder'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Courier/SKM_Courier_Base.SKM_Courier_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Courier.Icon_Courier'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Courier.Icon_Courier'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Demonia/SKM_Demonia_Base.SKM_Demonia_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Demonia.Icon_Demonia'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Demonia.Icon_Demonia'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Enchanter/SKM_Enchanter_Base.SKM_Enchanter_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Enchanter.Icon_Enchanter'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Enchanter.Icon_Enchanter'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Guard/SKM_Guard_Base.SKM_Guard_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Guard.Icon_Guard'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Guard.Icon_Guard'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Hermit/SKM_Hermit_Base.SKM_Hermit_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Hermit.Icon_Hermit'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Hermit.Icon_Hermit'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Hornet/SKM_Hornet_Base.SKM_Hornet_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Hornet.Icon_Hornet'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Hornet.Icon_Hornet'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Looter/SKM_Looter_Base.SKM_Looter_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Looter.Icon_Looter'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Looter.Icon_Looter'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Maid/SKM_Maid_Base.SKM_Maid_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Maid.Icon_Maid'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Maid.Icon_Maid'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Merry/SKM_Merry_Base.SKM_Merry_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Merry.Icon_Merry'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Merry.Icon_Merry'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Muzzle/SKM_Muzzle_Base.SKM_Muzzle_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Muzzle.Icon_Muzzle'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Muzzle.Icon_Muzzle'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Noble/SKM_Noble_Base.SKM_Noble_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Noble.Icon_Noble'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Noble.Icon_Noble'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Nurse/SKM_Nurse_Base.SKM_Nurse_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Nurse.Icon_Nurse'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Nurse.Icon_Nurse'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Outsider/SKM_Outsider_Base.SKM_Outsider_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Outsider.Icon_Outsider'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Outsider.Icon_Outsider'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Pioneer/SKM_Pioneer_Base.SKM_Pioneer_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Pioneer.Icon_Pioneer'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Pioneer.Icon_Pioneer'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Rogue/SKM_Rogue_Base.SKM_Rogue_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Rogue.Icon_Rogue'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Rogue.Icon_Rogue'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Tinker/SKM_Tinker_Base.SKM_Tinker_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Tinker.Icon_Tinker'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Tinker.Icon_Tinker'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Tuner/SKM_Tuner_Base.SKM_Tuner_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Tuner.Icon_Tuner'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Tuner.Icon_Tuner'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Weaver/SKM_Weaver_Base.SKM_Weaver_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Weaver.Icon_Weaver'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Weaver.Icon_Weaver'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.SkeletalMesh'/Game/External_Assets/Player/Writer/SKM_Writer_Base.SKM_Writer_Base'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/AvatarThumb/Icon_Writer.Icon_Writer'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.Texture2D'/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Writer.Icon_Writer'</t>
+    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Writer.Icon_Writer</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Writer.Icon_Writer</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Player/Writer/SKM_Writer_Base.SKM_Writer_Base</t>
   </si>
 </sst>
 </file>
@@ -1256,397 +1352,1069 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N24"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="33.875" customWidth="1"/>
+    <col min="5" max="5" width="43.5" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="N1" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" t="s">
+        <v>19</v>
       </c>
       <c r="I2" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="J2" t="s">
-        <v>39</v>
+        <v>21</v>
+      </c>
+      <c r="K2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N2" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" t="s">
+        <v>19</v>
       </c>
       <c r="I3" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="J3" t="s">
-        <v>42</v>
+        <v>28</v>
+      </c>
+      <c r="K3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" t="s">
+        <v>19</v>
       </c>
       <c r="I4" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="J4" t="s">
-        <v>45</v>
+        <v>35</v>
+      </c>
+      <c r="K4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" t="s">
+        <v>17</v>
+      </c>
+      <c r="M4" t="s">
+        <v>17</v>
+      </c>
+      <c r="N4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s">
-        <v>46</v>
+        <v>37</v>
+      </c>
+      <c r="C5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" t="s">
+        <v>19</v>
       </c>
       <c r="I5" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="J5" t="s">
-        <v>48</v>
+        <v>39</v>
+      </c>
+      <c r="K5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L5" t="s">
+        <v>17</v>
+      </c>
+      <c r="M5" t="s">
+        <v>17</v>
+      </c>
+      <c r="N5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>41</v>
+      </c>
+      <c r="C6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" t="s">
+        <v>19</v>
       </c>
       <c r="I6" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J6" t="s">
-        <v>51</v>
+        <v>43</v>
+      </c>
+      <c r="K6" t="s">
+        <v>17</v>
+      </c>
+      <c r="L6" t="s">
+        <v>17</v>
+      </c>
+      <c r="M6" t="s">
+        <v>17</v>
+      </c>
+      <c r="N6" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>45</v>
+      </c>
+      <c r="C7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" t="s">
+        <v>19</v>
       </c>
       <c r="I7" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="J7" t="s">
-        <v>54</v>
+        <v>47</v>
+      </c>
+      <c r="K7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L7" t="s">
+        <v>17</v>
+      </c>
+      <c r="M7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N7" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>49</v>
+      </c>
+      <c r="C8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" t="s">
+        <v>19</v>
       </c>
       <c r="I8" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="J8" t="s">
-        <v>57</v>
+        <v>51</v>
+      </c>
+      <c r="K8" t="s">
+        <v>17</v>
+      </c>
+      <c r="L8" t="s">
+        <v>17</v>
+      </c>
+      <c r="M8" t="s">
+        <v>17</v>
+      </c>
+      <c r="N8" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>53</v>
+      </c>
+      <c r="C9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" t="s">
+        <v>19</v>
       </c>
       <c r="I9" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="J9" t="s">
-        <v>60</v>
+        <v>55</v>
+      </c>
+      <c r="K9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N9" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="B10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" t="s">
         <v>61</v>
       </c>
+      <c r="G10" t="s">
+        <v>62</v>
+      </c>
+      <c r="H10" t="s">
+        <v>19</v>
+      </c>
       <c r="I10" t="s">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="J10" t="s">
         <v>63</v>
+      </c>
+      <c r="K10" t="s">
+        <v>64</v>
+      </c>
+      <c r="L10" t="s">
+        <v>65</v>
+      </c>
+      <c r="M10" t="s">
+        <v>66</v>
+      </c>
+      <c r="N10" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>68</v>
+      </c>
+      <c r="C11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D11" t="s">
+        <v>59</v>
+      </c>
+      <c r="E11" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" t="s">
+        <v>70</v>
+      </c>
+      <c r="G11" t="s">
+        <v>71</v>
+      </c>
+      <c r="H11" t="s">
+        <v>19</v>
       </c>
       <c r="I11" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="J11" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="K11" t="s">
+        <v>73</v>
+      </c>
+      <c r="L11" t="s">
+        <v>74</v>
+      </c>
+      <c r="M11" t="s">
+        <v>75</v>
+      </c>
+      <c r="N11" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>76</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>77</v>
+      </c>
+      <c r="C12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" t="s">
+        <v>60</v>
+      </c>
+      <c r="F12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" t="s">
+        <v>19</v>
       </c>
       <c r="I12" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="J12" t="s">
-        <v>69</v>
+        <v>79</v>
+      </c>
+      <c r="K12" t="s">
+        <v>17</v>
+      </c>
+      <c r="L12" t="s">
+        <v>17</v>
+      </c>
+      <c r="M12" t="s">
+        <v>17</v>
+      </c>
+      <c r="N12" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>81</v>
+      </c>
+      <c r="C13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" t="s">
+        <v>60</v>
+      </c>
+      <c r="F13" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" t="s">
+        <v>19</v>
       </c>
       <c r="I13" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="J13" t="s">
-        <v>72</v>
+        <v>83</v>
+      </c>
+      <c r="K13" t="s">
+        <v>17</v>
+      </c>
+      <c r="L13" t="s">
+        <v>17</v>
+      </c>
+      <c r="M13" t="s">
+        <v>17</v>
+      </c>
+      <c r="N13" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>85</v>
+      </c>
+      <c r="C14" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" t="s">
+        <v>19</v>
       </c>
       <c r="I14" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="J14" t="s">
-        <v>75</v>
+        <v>87</v>
+      </c>
+      <c r="K14" t="s">
+        <v>17</v>
+      </c>
+      <c r="L14" t="s">
+        <v>17</v>
+      </c>
+      <c r="M14" t="s">
+        <v>17</v>
+      </c>
+      <c r="N14" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>88</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>89</v>
+      </c>
+      <c r="C15" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" t="s">
+        <v>60</v>
+      </c>
+      <c r="F15" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" t="s">
+        <v>19</v>
       </c>
       <c r="I15" t="s">
-        <v>77</v>
+        <v>20</v>
       </c>
       <c r="J15" t="s">
-        <v>78</v>
+        <v>91</v>
+      </c>
+      <c r="K15" t="s">
+        <v>17</v>
+      </c>
+      <c r="L15" t="s">
+        <v>17</v>
+      </c>
+      <c r="M15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N15" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>93</v>
+      </c>
+      <c r="C16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" t="s">
+        <v>60</v>
+      </c>
+      <c r="F16" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16" t="s">
+        <v>19</v>
       </c>
       <c r="I16" t="s">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="J16" t="s">
-        <v>81</v>
+        <v>95</v>
+      </c>
+      <c r="K16" t="s">
+        <v>17</v>
+      </c>
+      <c r="L16" t="s">
+        <v>17</v>
+      </c>
+      <c r="M16" t="s">
+        <v>17</v>
+      </c>
+      <c r="N16" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>96</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>97</v>
+      </c>
+      <c r="C17" t="s">
+        <v>98</v>
+      </c>
+      <c r="D17" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" t="s">
+        <v>19</v>
       </c>
       <c r="I17" t="s">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="J17" t="s">
-        <v>84</v>
+        <v>99</v>
+      </c>
+      <c r="K17" t="s">
+        <v>17</v>
+      </c>
+      <c r="L17" t="s">
+        <v>17</v>
+      </c>
+      <c r="M17" t="s">
+        <v>17</v>
+      </c>
+      <c r="N17" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>101</v>
+      </c>
+      <c r="C18" t="s">
+        <v>102</v>
+      </c>
+      <c r="D18" t="s">
+        <v>59</v>
+      </c>
+      <c r="E18" t="s">
+        <v>60</v>
+      </c>
+      <c r="F18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18" t="s">
+        <v>19</v>
       </c>
       <c r="I18" t="s">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="J18" t="s">
-        <v>87</v>
+        <v>103</v>
+      </c>
+      <c r="K18" t="s">
+        <v>17</v>
+      </c>
+      <c r="L18" t="s">
+        <v>17</v>
+      </c>
+      <c r="M18" t="s">
+        <v>17</v>
+      </c>
+      <c r="N18" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>104</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>105</v>
+      </c>
+      <c r="C19" t="s">
+        <v>106</v>
+      </c>
+      <c r="D19" t="s">
+        <v>59</v>
+      </c>
+      <c r="E19" t="s">
+        <v>60</v>
+      </c>
+      <c r="F19" t="s">
+        <v>107</v>
+      </c>
+      <c r="G19" t="s">
+        <v>108</v>
+      </c>
+      <c r="H19" t="s">
+        <v>19</v>
       </c>
       <c r="I19" t="s">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J19" t="s">
-        <v>90</v>
+        <v>109</v>
+      </c>
+      <c r="K19" t="s">
+        <v>110</v>
+      </c>
+      <c r="L19" t="s">
+        <v>111</v>
+      </c>
+      <c r="M19" t="s">
+        <v>112</v>
+      </c>
+      <c r="N19" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>113</v>
+      </c>
+      <c r="B20" t="s">
+        <v>114</v>
+      </c>
+      <c r="C20" t="s">
+        <v>115</v>
+      </c>
+      <c r="D20" t="s">
+        <v>59</v>
+      </c>
+      <c r="E20" t="s">
+        <v>60</v>
+      </c>
+      <c r="F20" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20" t="s">
         <v>18</v>
       </c>
-      <c r="B20" t="s">
-        <v>91</v>
+      <c r="H20" t="s">
+        <v>19</v>
       </c>
       <c r="I20" t="s">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="J20" t="s">
-        <v>93</v>
+        <v>116</v>
+      </c>
+      <c r="K20" t="s">
+        <v>17</v>
+      </c>
+      <c r="L20" t="s">
+        <v>17</v>
+      </c>
+      <c r="M20" t="s">
+        <v>17</v>
+      </c>
+      <c r="N20" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>117</v>
+      </c>
+      <c r="B21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C21" t="s">
+        <v>119</v>
+      </c>
+      <c r="D21" t="s">
+        <v>59</v>
+      </c>
+      <c r="E21" t="s">
+        <v>60</v>
+      </c>
+      <c r="F21" t="s">
+        <v>120</v>
+      </c>
+      <c r="G21" t="s">
+        <v>121</v>
+      </c>
+      <c r="H21" t="s">
         <v>19</v>
       </c>
-      <c r="B21" t="s">
-        <v>94</v>
-      </c>
       <c r="I21" t="s">
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="J21" t="s">
-        <v>96</v>
+        <v>122</v>
+      </c>
+      <c r="K21" t="s">
+        <v>123</v>
+      </c>
+      <c r="L21" t="s">
+        <v>124</v>
+      </c>
+      <c r="M21" t="s">
+        <v>125</v>
+      </c>
+      <c r="N21" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>126</v>
+      </c>
+      <c r="B22" t="s">
+        <v>127</v>
+      </c>
+      <c r="C22" t="s">
+        <v>128</v>
+      </c>
+      <c r="D22" t="s">
+        <v>59</v>
+      </c>
+      <c r="E22" t="s">
+        <v>60</v>
+      </c>
+      <c r="F22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G22" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" t="s">
+        <v>19</v>
+      </c>
+      <c r="I22" t="s">
         <v>20</v>
       </c>
-      <c r="B22" t="s">
-        <v>97</v>
-      </c>
-      <c r="I22" t="s">
-        <v>98</v>
-      </c>
       <c r="J22" t="s">
-        <v>99</v>
+        <v>129</v>
+      </c>
+      <c r="K22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L22" t="s">
+        <v>17</v>
+      </c>
+      <c r="M22" t="s">
+        <v>17</v>
+      </c>
+      <c r="N22" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="B23" t="s">
-        <v>100</v>
+        <v>131</v>
+      </c>
+      <c r="C23" t="s">
+        <v>132</v>
+      </c>
+      <c r="D23" t="s">
+        <v>59</v>
+      </c>
+      <c r="E23" t="s">
+        <v>60</v>
+      </c>
+      <c r="F23" t="s">
+        <v>17</v>
+      </c>
+      <c r="G23" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23" t="s">
+        <v>19</v>
       </c>
       <c r="I23" t="s">
-        <v>101</v>
+        <v>20</v>
       </c>
       <c r="J23" t="s">
-        <v>102</v>
+        <v>133</v>
+      </c>
+      <c r="K23" t="s">
+        <v>17</v>
+      </c>
+      <c r="L23" t="s">
+        <v>17</v>
+      </c>
+      <c r="M23" t="s">
+        <v>17</v>
+      </c>
+      <c r="N23" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>134</v>
+      </c>
+      <c r="B24" t="s">
+        <v>135</v>
+      </c>
+      <c r="C24" t="s">
+        <v>136</v>
+      </c>
+      <c r="D24" t="s">
+        <v>59</v>
+      </c>
+      <c r="E24" t="s">
+        <v>60</v>
+      </c>
+      <c r="F24" t="s">
+        <v>17</v>
+      </c>
+      <c r="G24" t="s">
+        <v>18</v>
+      </c>
+      <c r="H24" t="s">
+        <v>19</v>
+      </c>
+      <c r="I24" t="s">
+        <v>20</v>
+      </c>
+      <c r="J24" t="s">
+        <v>137</v>
+      </c>
+      <c r="K24" t="s">
+        <v>17</v>
+      </c>
+      <c r="L24" t="s">
+        <v>17</v>
+      </c>
+      <c r="M24" t="s">
+        <v>17</v>
+      </c>
+      <c r="N24" t="s">
         <v>22</v>
-      </c>
-      <c r="B24" t="s">
-        <v>103</v>
-      </c>
-      <c r="I24" t="s">
-        <v>104</v>
-      </c>
-      <c r="J24" t="s">
-        <v>105</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
-  <dataValidations count="6">
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="범위 오류" error="UltimateDamageRate는 1.0 이상의 숫자만 가능합니다._x000a_(예: 15% -&gt; 1.15)" sqref="G1:G1048576">
-      <formula1>1</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="입력 오류" error=" 음수(-)는 입력할 수 없습니다. 0 이상의 숫자를 입력해주세요." sqref="F2:F1048576">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="범위 오류" error="CritRate은 0.0 ~ 1.0 사이의 소수점만 가능합니다. (예: 15% -&gt; 0.15)" sqref="L3:L1048576 M2">
-      <formula1>0</formula1>
-      <formula2>1</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="입력 오류" error="음수(-)는 입력할 수 없습니다. 0 이상의 숫자를 입력해주세요." sqref="H3:H1048576 K2 I2:J1048576">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="입력 오류" error="HP는 0 보다 큰 숫자를 입력해주세요." sqref="H2">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="입력 오류" error="음수(-)는 입력할 수 없습니다. 0 이상의 숫자를 입력해주세요._x000a_언리얼 단위(cm/s)입니다. 보통 걷기는 300~400, 달리기는 600 정도입니다." sqref="K3:K1048576 L2">
-      <formula1>0</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/DesignData/Excel_Masters/CharacterAssets_Master.xlsx
+++ b/DesignData/Excel_Masters/CharacterAssets_Master.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Documents\Unreal Projects\ProjectParadise\DesignData\Excel_Masters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25680" windowHeight="10965"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22065" windowHeight="9420"/>
   </bookViews>
   <sheets>
     <sheet name="CharacterAssets" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="236">
   <si>
     <t>---</t>
   </si>
@@ -30,10 +30,19 @@
     <t>BodyIcon</t>
   </si>
   <si>
-    <t>UltimateAbility</t>
-  </si>
-  <si>
-    <t>UltimateDamageEffect</t>
+    <t>AwakeningPieceIcon</t>
+  </si>
+  <si>
+    <t>IdleAnim</t>
+  </si>
+  <si>
+    <t>UltimateIcon</t>
+  </si>
+  <si>
+    <t>Rarity</t>
+  </si>
+  <si>
+    <t>UltimateAttackSetup</t>
   </si>
   <si>
     <t>UltimateMontage</t>
@@ -72,22 +81,34 @@
     <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Anubis.Icon_Anubis</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Anubis.Icon_Anubis</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Anubis/Ani/Anubis_Base_Battle_Idle_Anim_Anubis_Base_Battle_Idle1.Anubis_Base_Battle_Idle_Anim_Anubis_Base_Battle_Idle1</t>
+  </si>
+  <si>
     <t>None</t>
   </si>
   <si>
+    <t>Legendary</t>
+  </si>
+  <si>
+    <t>(AbilityClass=None,EffectClass=None,ProjectileClass=None)</t>
+  </si>
+  <si>
     <t>()</t>
   </si>
   <si>
-    <t>(TagName="")</t>
+    <t>(TagName="FX.Character.Anubis.Ultimate")</t>
   </si>
   <si>
     <t>(TagName="Unit.Faction.Friendly.Player")</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Player/Anubis/SKM_Anubis_Base.SKM_Anubis_Base</t>
-  </si>
-  <si>
-    <t>(ReactionFXData=None,HitTag=(TagName=""),DeathTag=(TagName=""))</t>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Anubis/SKM_Anubis_Base.SKM_Anubis_Base</t>
+  </si>
+  <si>
+    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Anubis.DA_CharFX_Anubis",HitTag=(TagName="FX.Character.Anubis.Hit"),DeathTag=(TagName="FX.Character.Anubis.Death"))</t>
   </si>
   <si>
     <t>Char_Army</t>
@@ -99,13 +120,28 @@
     <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Army.Icon_Army</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Army.Icon_Army</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Army/Ani/Army_Base_Battle_Idle.Army_Base_Battle_Idle</t>
+  </si>
+  <si>
+    <t>Common</t>
+  </si>
+  <si>
+    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_AreaUltimate.GA_AreaUltimate_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Buff_AttackPowerUp.GE_Buff_AttackPowerUp_C'",ProjectileClass=None)</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Player/Army/AM_Army_Ultimate_Attack.AM_Army_Ultimate_Attack</t>
   </si>
   <si>
     <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Army/AM_Army_Book_Attack.AM_Army_Book_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Army/AM_Army_Book_Skill.AM_Army_Book_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Army/AM_Army_Melee_Attack.AM_Army_Melee_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Army/AM_Army_Melee_Attack.AM_Army_Melee_Attack")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Army/AM_Army_Gun_Attack.AM_Army_Gun_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Army/AM_Army_Gun_Attack.AM_Army_Gun_Attack")))</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Player/Army/SKM_Army_Base.SKM_Army_Base</t>
+    <t>(TagName="FX.Character.Army.Ultimate")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Army/SKM_Army_Base.SKM_Army_Base</t>
   </si>
   <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Player/Army/ABP_Base_Army.ABP_Base_Army_C'</t>
@@ -126,7 +162,16 @@
     <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Bard.Icon_Bard</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Player/Bard/SKM_Bard_Base.SKM_Bard_Base</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Bard.Icon_Bard</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Bard/Bard_Modify/Ani/Bard_Base_Battle_Idle.Bard_Base_Battle_Idle</t>
+  </si>
+  <si>
+    <t>Uncommon</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Bard/Bard_Modify/SKM_Bard_Base_Modified.SKM_Bard_Base_Modified</t>
   </si>
   <si>
     <t>Char_Binder</t>
@@ -138,6 +183,15 @@
     <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Binder.Icon_Binder</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Binder.Icon_Binder</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Binder/Ani/Binder_Base_Battle_Idle.Binder_Base_Battle_Idle</t>
+  </si>
+  <si>
+    <t>Epic</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Player/Binder/SKM_Binder_Base.SKM_Binder_Base</t>
   </si>
   <si>
@@ -150,7 +204,16 @@
     <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Courier.Icon_Courier</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Player/Courier/SKM_Courier_Base.SKM_Courier_Base</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Courier.Icon_Courier</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Courier/Ani/Courier_Base_Lobby_Idle_Anim_Take_0011.Courier_Base_Lobby_Idle_Anim_Take_0011</t>
+  </si>
+  <si>
+    <t>Rare</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Courier/SKM_Courier_Base2.SKM_Courier_Base2</t>
   </si>
   <si>
     <t>Char_Demonia</t>
@@ -162,7 +225,13 @@
     <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Demonia.Icon_Demonia</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Player/Demonia/SKM_Demonia_Base.SKM_Demonia_Base</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Demonia.Icon_Demonia</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Demonia/Ani/Demonia_Base_Battle_Idle.Demonia_Base_Battle_Idle</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Demonia/SKM_Demonia_Base.SKM_Demonia_Base</t>
   </si>
   <si>
     <t>Char_Enchanter</t>
@@ -174,7 +243,13 @@
     <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Enchanter.Icon_Enchanter</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Player/Enchanter/SKM_Enchanter_Base.SKM_Enchanter_Base</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Enchanter.Icon_Enchanter</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Enchanter/Ani/Enchanter_Base_Battle_Idle_Anim_Take_001.Enchanter_Base_Battle_Idle_Anim_Take_001</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Enchanter/SKM_Enchanter_Base.SKM_Enchanter_Base</t>
   </si>
   <si>
     <t>Char_Guard</t>
@@ -186,7 +261,13 @@
     <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Guard.Icon_Guard</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Player/Guard/SKM_Guard_Base.SKM_Guard_Base</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Guard.Icon_Guard</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Guard/Ani/Guard_Base_Battle_Idle.Guard_Base_Battle_Idle</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Guard/SKM_Guard_Base.SKM_Guard_Base</t>
   </si>
   <si>
     <t>Char_Hermit</t>
@@ -198,10 +279,10 @@
     <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Hermit.Icon_Hermit</t>
   </si>
   <si>
-    <t>/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_MeleeUltimate.GA_MeleeUltimate_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Standard.GE_Damage_Standard_C'</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Hermit.Icon_Hermit</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Hermit/Ani/Hermit_Base_Battle_Idle_Anim_Hermit_Battle_Idle.Hermit_Base_Battle_Idle_Anim_Hermit_Battle_Idle</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Ultimate_Attack.AM_Hermit_Ultimate_Attack</t>
@@ -210,7 +291,7 @@
     <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Book_Attack.AM_Hermit_Book_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Book_Attack.AM_Hermit_Book_Attack")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Melee_Attack.AM_Hermit_Melee_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Melee_Attack.AM_Hermit_Melee_Attack")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Gun_Attack.AM_Hermit_Gun_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Gun_Attack.AM_Hermit_Gun_Attack")))</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Player/Hermit/SKM_Hermit_Base.SKM_Hermit_Base</t>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Hermit/SKM_Hermit_Base.SKM_Hermit_Base</t>
   </si>
   <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Player/Hermit/ABP_Base_Hermit.ABP_Base_Hermit_C'</t>
@@ -231,13 +312,19 @@
     <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Hornet.Icon_Hornet</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Hornet.Icon_Hornet</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Hornet/Ani/Hornet_Base_Battle_Idle.Hornet_Base_Battle_Idle</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Ultimate.AM_Hornet_Ultimate</t>
   </si>
   <si>
     <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Book_Attack.AM_Hornet_Book_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Book_Attack.AM_Hornet_Book_Attack")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Melee_Attack.AM_Hornet_Melee_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Melee_Attack.AM_Hornet_Melee_Attack")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Gun_Attack.AM_Hornet_Gun_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Gun_Attack.AM_Hornet_Gun_Attack")))</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Player/Hornet/SKM_Hornet_Base.SKM_Hornet_Base</t>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Hornet/SKM_Hornet_Base.SKM_Hornet_Base</t>
   </si>
   <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Player/Hornet/ABP_Base_Hornet.ABP_Base_Hornet_C'</t>
@@ -258,7 +345,13 @@
     <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Looter.Icon_Looter</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Player/Looter/SKM_Looter_Base.SKM_Looter_Base</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Looter.Icon_Looter</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Looter/Ani/Looter_Base_Battle_Idle.Looter_Base_Battle_Idle</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Looter/SKM_Looter_Base.SKM_Looter_Base</t>
   </si>
   <si>
     <t>Char_Maid</t>
@@ -270,7 +363,13 @@
     <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Maid.Icon_Maid</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Player/Maid/SKM_Maid_Base.SKM_Maid_Base</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Maid.Icon_Maid</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Maid/Ani/Maid_Base_Idle_Battle.Maid_Base_Idle_Battle</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Maid/SKM_Maid_Base.SKM_Maid_Base</t>
   </si>
   <si>
     <t>Char_Merry</t>
@@ -282,7 +381,13 @@
     <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Merry.Icon_Merry</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Player/Merry/SKM_Merry_Base.SKM_Merry_Base</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Merry.Icon_Merry</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Merry/Ani/Merry_Base_Battle_Idle.Merry_Base_Battle_Idle</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Merry/SKM_Merry_Base.SKM_Merry_Base</t>
   </si>
   <si>
     <t>Char_Muzzle</t>
@@ -294,7 +399,13 @@
     <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Muzzle.Icon_Muzzle</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Player/Muzzle/SKM_Muzzle_Base.SKM_Muzzle_Base</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Muzzle.Icon_Muzzle</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Muzzle/Ani/Muzzle_Base_Lobby_Idle_NoWeapon.Muzzle_Base_Lobby_Idle_NoWeapon</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Muzzle/SKM_Muzzle_Base.SKM_Muzzle_Base</t>
   </si>
   <si>
     <t>Char_Noble</t>
@@ -306,7 +417,13 @@
     <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Noble.Icon_Noble</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Player/Noble/SKM_Noble_Base.SKM_Noble_Base</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Noble.Icon_Noble</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Noble/Ani/Noble_Base_Battle_Idle_Anim_Take_0011.Noble_Base_Battle_Idle_Anim_Take_0011</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Noble/SKM_Noble_Base.SKM_Noble_Base</t>
   </si>
   <si>
     <t>Char_Nurse</t>
@@ -318,7 +435,13 @@
     <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Nurse.Icon_Nurse</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Player/Nurse/SKM_Nurse_Base.SKM_Nurse_Base</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Nurse.Icon_Nurse</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Nurse/Ani/Nurse_Base_Battle_Idle.Nurse_Base_Battle_Idle</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Nurse/SKM_Nurse_Base.SKM_Nurse_Base</t>
   </si>
   <si>
     <t>Char_Outsider</t>
@@ -330,7 +453,13 @@
     <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Outsider.Icon_Outsider</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Player/Outsider/SKM_Outsider_Base.SKM_Outsider_Base</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Outsider.Icon_Outsider</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Outsider/Ani/Outsider_Base_Battle_Idle.Outsider_Base_Battle_Idle</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Outsider/SKM_Outsider_Base.SKM_Outsider_Base</t>
   </si>
   <si>
     <t>Char_Pioneer</t>
@@ -342,13 +471,19 @@
     <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Pioneer.Icon_Pioneer</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Pioneer.Icon_Pioneer</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Pioneer/Ani/Pioneer_Base_Battle_Idle.Pioneer_Base_Battle_Idle</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Ultimate.AM_Pioneer_Ultimate</t>
   </si>
   <si>
     <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Book_Attack.AM_Pioneer_Book_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Book_Attack.AM_Pioneer_Book_Attack")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Sword_Attack.AM_Pioneer_Sword_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Sword_Attack.AM_Pioneer_Sword_Attack")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Gun_Attack.AM_Pioneer_Gun_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Gun_Attack.AM_Pioneer_Gun_Attack")))</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Player/Pioneer/SKM_Pioneer_Base.SKM_Pioneer_Base</t>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Pioneer/SKM_Pioneer_Base.SKM_Pioneer_Base</t>
   </si>
   <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Player/Pioneer/ABP_Pioneer.ABP_Pioneer_C'</t>
@@ -369,7 +504,13 @@
     <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Rogue.Icon_Rogue</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Player/Rogue/SKM_Rogue_Base.SKM_Rogue_Base</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Rogue.Icon_Rogue</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Rogue/Ani/Rogue_Base_Battle_Idle_Anim_Rogue_Base_Battle_Idle.Rogue_Base_Battle_Idle_Anim_Rogue_Base_Battle_Idle</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Rogue/SKM_Rogue_Base.SKM_Rogue_Base</t>
   </si>
   <si>
     <t>Char_Tinker</t>
@@ -381,13 +522,19 @@
     <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Tinker.Icon_Tinker</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Tinker.Icon_Tinker</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Tinker/Ani/Tinker_Base_Battle_Idle_Anim_Tinker_Base_Battle_Idle.Tinker_Base_Battle_Idle_Anim_Tinker_Base_Battle_Idle</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Player/Tinker/AM_Ultimate_Attack.AM_Ultimate_Attack</t>
   </si>
   <si>
     <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Tinker/AM_Book_Attack.AM_Book_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Tinker/AM_Book_Attack.AM_Book_Attack")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Tinker/AM_Melee_Attack.AM_Melee_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Tinker/AM_Melee_Blunt_Attack.AM_Melee_Blunt_Attack")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Tinker/AM_Gun_Attack.AM_Gun_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Tinker/AM_Gun_Attack.AM_Gun_Attack")))</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Player/Tinker/SKM_Tinker_Base.SKM_Tinker_Base</t>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Tinker/SKM_Tinker_Base.SKM_Tinker_Base</t>
   </si>
   <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Player/Tinker/ABP_Base.ABP_Base_C'</t>
@@ -408,7 +555,13 @@
     <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Tuner.Icon_Tuner</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Player/Tuner/SKM_Tuner_Base.SKM_Tuner_Base</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Tuner.Icon_Tuner</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Tuner/Ani/Tuner_Base_Battle_Idle.Tuner_Base_Battle_Idle</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Tuner/SKM_Tuner_Base.SKM_Tuner_Base</t>
   </si>
   <si>
     <t>Char_Weaver</t>
@@ -420,7 +573,13 @@
     <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Weaver.Icon_Weaver</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Player/Weaver/SKM_Weaver_Base.SKM_Weaver_Base</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Weaver.Icon_Weaver</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Weaver/Ani/Weaver_Base_Battle_Idle_Anim_Take_001.Weaver_Base_Battle_Idle_Anim_Take_001</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Weaver/SKM_Weaver_Base.SKM_Weaver_Base</t>
   </si>
   <si>
     <t>Char_Writer</t>
@@ -432,7 +591,142 @@
     <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Writer.Icon_Writer</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Player/Writer/SKM_Writer_Base.SKM_Writer_Base</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Writer.Icon_Writer</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Writer/Ani/Writer_Base_Battle_Idle.Writer_Base_Battle_Idle</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Writer/SKM_Writer_Base.SKM_Writer_Base</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Bard.Ultimate")</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Binder.Ultimate")</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Courier.Ultimate")</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Demonia.Ultimate")</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Enchanter.Ultimate")</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Guard.Ultimate")</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Hermit.Ultimate")</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Hornet.Ultimate")</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Looter.Ultimate")</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Maid.Ultimate")</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Merry.Ultimate")</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Muzzle.Ultimate")</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Noble.Ultimate")</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Nurse.Ultimate")</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Outsider.Ultimate")</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Pioneer.Ultimate")</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Rogue.Ultimate")</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Tinker.Ultimate")</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Tuner.Ultimate")</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Weaver.Ultimate")</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Writer.Ultimate")</t>
+  </si>
+  <si>
+    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Army.DA_CharFX_Army",HitTag=(TagName="FX.Character.Army.Hit"),DeathTag=(TagName="FX.Character.Army.Death"))</t>
+  </si>
+  <si>
+    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Bard.DA_CharFX_Bard",HitTag=(TagName="FX.Character.Bard.Hit"),DeathTag=(TagName="FX.Character.Bard.Death"))</t>
+  </si>
+  <si>
+    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Binder.DA_CharFX_Binder",HitTag=(TagName="FX.Character.Binder.Hit"),DeathTag=(TagName="FX.Character.Binder.Death"))</t>
+  </si>
+  <si>
+    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Courier.DA_CharFX_Courier",HitTag=(TagName="FX.Character.Courier.Hit"),DeathTag=(TagName="FX.Character.Courier.Death"))</t>
+  </si>
+  <si>
+    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Demonia.DA_CharFX_Demonia",HitTag=(TagName="FX.Character.Demonia.Hit"),DeathTag=(TagName="FX.Character.Demonia.Death"))</t>
+  </si>
+  <si>
+    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Enchanter.DA_CharFX_Enchanter",HitTag=(TagName="FX.Character.Enchanter.Hit"),DeathTag=(TagName="FX.Character.Enchanter.Death"))</t>
+  </si>
+  <si>
+    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Guard.DA_CharFX_Guard",HitTag=(TagName="FX.Character.Guard.Hit"),DeathTag=(TagName="FX.Character.Guard.Death"))</t>
+  </si>
+  <si>
+    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Hermit.DA_CharFX_Hermit",HitTag=(TagName="FX.Character.Hermit.Hit"),DeathTag=(TagName="FX.Character.Hermit.Death"))</t>
+  </si>
+  <si>
+    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Hornet.DA_CharFX_Hornet",HitTag=(TagName="FX.Character.Hornet.Hit"),DeathTag=(TagName="FX.Character.Hornet.Death"))</t>
+  </si>
+  <si>
+    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Looter.DA_CharFX_Looter",HitTag=(TagName="FX.Character.Looter.Hit"),DeathTag=(TagName="FX.Character.Looter.Death"))</t>
+  </si>
+  <si>
+    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Maid.DA_CharFX_Maid",HitTag=(TagName="FX.Character.Maid.Hit"),DeathTag=(TagName="FX.Character.Maid.Death"))</t>
+  </si>
+  <si>
+    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Merry.DA_CharFX_Merry",HitTag=(TagName="FX.Character.Merry.Hit"),DeathTag=(TagName="FX.Character.Merry.Death"))</t>
+  </si>
+  <si>
+    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Muzzle.DA_CharFX_Muzzle",HitTag=(TagName="FX.Character.Muzzle.Hit"),DeathTag=(TagName="FX.Character.Muzzle.Death"))</t>
+  </si>
+  <si>
+    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Noble.DA_CharFX_Noble",HitTag=(TagName="FX.Character.Noble.Hit"),DeathTag=(TagName="FX.Character.Noble.Death"))</t>
+  </si>
+  <si>
+    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Nurse.DA_CharFX_Nurse",HitTag=(TagName="FX.Character.Nurse.Hit"),DeathTag=(TagName="FX.Character.Nurse.Death"))</t>
+  </si>
+  <si>
+    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Outsider.DA_CharFX_Outsider",HitTag=(TagName="FX.Character.Outsider.Hit"),DeathTag=(TagName="FX.Character.Outsider.Death"))</t>
+  </si>
+  <si>
+    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Pioneer.DA_CharFX_Pioneer",HitTag=(TagName="FX.Character.Pioneer.Hit"),DeathTag=(TagName="FX.Character.Pioneer.Death"))</t>
+  </si>
+  <si>
+    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Rogue.DA_CharFX_Rogue",HitTag=(TagName="FX.Character.Rogue.Hit"),DeathTag=(TagName="FX.Character.Rogue.Death"))</t>
+  </si>
+  <si>
+    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Tinker.DA_CharFX_Tinker",HitTag=(TagName="FX.Character.Tinker.Hit"),DeathTag=(TagName="FX.Character.Tinker.Death"))</t>
+  </si>
+  <si>
+    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Tuner.DA_CharFX_Tuner",HitTag=(TagName="FX.Character.Tuner.Hit"),DeathTag=(TagName="FX.Character.Tuner.Death"))</t>
+  </si>
+  <si>
+    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Weaver.DA_CharFX_Weaver",HitTag=(TagName="FX.Character.Weaver.Hit"),DeathTag=(TagName="FX.Character.Weaver.Death"))</t>
+  </si>
+  <si>
+    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Writer.DA_CharFX_Writer",HitTag=(TagName="FX.Character.Writer.Hit"),DeathTag=(TagName="FX.Character.Writer.Death"))</t>
   </si>
 </sst>
 </file>
@@ -1350,14 +1644,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="33.875" customWidth="1"/>
-    <col min="5" max="5" width="43.5" customWidth="1"/>
+    <col min="1" max="1" width="18.625" customWidth="1"/>
+    <col min="11" max="11" width="18.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1400,1021 +1694,1238 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" t="s">
+        <v>22</v>
+      </c>
+      <c r="P2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N3" t="s">
+        <v>41</v>
+      </c>
+      <c r="O3" t="s">
+        <v>42</v>
+      </c>
+      <c r="P3" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" t="s">
+        <v>193</v>
+      </c>
+      <c r="L4" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4" t="s">
+        <v>50</v>
+      </c>
+      <c r="N4" t="s">
+        <v>22</v>
+      </c>
+      <c r="O4" t="s">
+        <v>22</v>
+      </c>
+      <c r="P4" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" t="s">
+        <v>56</v>
+      </c>
+      <c r="H5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K5" t="s">
+        <v>194</v>
+      </c>
+      <c r="L5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5" t="s">
+        <v>57</v>
+      </c>
+      <c r="N5" t="s">
+        <v>22</v>
+      </c>
+      <c r="O5" t="s">
+        <v>22</v>
+      </c>
+      <c r="P5" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" t="s">
         <v>59</v>
       </c>
-      <c r="E2" t="s">
+      <c r="C6" t="s">
         <v>60</v>
       </c>
-      <c r="F2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N2" t="s">
-        <v>22</v>
+      <c r="D6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" t="s">
+        <v>62</v>
+      </c>
+      <c r="F6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" t="s">
+        <v>63</v>
+      </c>
+      <c r="H6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K6" t="s">
+        <v>195</v>
+      </c>
+      <c r="L6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M6" t="s">
+        <v>64</v>
+      </c>
+      <c r="N6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P6" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>217</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" t="s">
+        <v>69</v>
+      </c>
+      <c r="F7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" t="s">
         <v>23</v>
       </c>
-      <c r="B3" t="s">
+      <c r="H7" t="s">
         <v>24</v>
       </c>
-      <c r="C3" t="s">
+      <c r="I7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" t="s">
         <v>25</v>
       </c>
-      <c r="D3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="K7" t="s">
+        <v>196</v>
+      </c>
+      <c r="L7" t="s">
         <v>27</v>
       </c>
-      <c r="H3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" t="s">
-        <v>28</v>
-      </c>
-      <c r="K3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N3" t="s">
-        <v>22</v>
+      <c r="M7" t="s">
+        <v>70</v>
+      </c>
+      <c r="N7" t="s">
+        <v>22</v>
+      </c>
+      <c r="O7" t="s">
+        <v>22</v>
+      </c>
+      <c r="P7" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>218</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" t="s">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" t="s">
+        <v>197</v>
+      </c>
+      <c r="L8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M8" t="s">
+        <v>76</v>
+      </c>
+      <c r="N8" t="s">
+        <v>22</v>
+      </c>
+      <c r="O8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P8" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E9" t="s">
+        <v>81</v>
+      </c>
+      <c r="F9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" t="s">
         <v>35</v>
       </c>
-      <c r="K4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L4" t="s">
-        <v>17</v>
-      </c>
-      <c r="M4" t="s">
-        <v>17</v>
-      </c>
-      <c r="N4" t="s">
-        <v>22</v>
+      <c r="H9" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" t="s">
+        <v>25</v>
+      </c>
+      <c r="K9" t="s">
+        <v>198</v>
+      </c>
+      <c r="L9" t="s">
+        <v>27</v>
+      </c>
+      <c r="M9" t="s">
+        <v>82</v>
+      </c>
+      <c r="N9" t="s">
+        <v>22</v>
+      </c>
+      <c r="O9" t="s">
+        <v>22</v>
+      </c>
+      <c r="P9" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>220</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E5" t="s">
-        <v>60</v>
-      </c>
-      <c r="F5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I5" t="s">
-        <v>20</v>
-      </c>
-      <c r="J5" t="s">
-        <v>39</v>
-      </c>
-      <c r="K5" t="s">
-        <v>17</v>
-      </c>
-      <c r="L5" t="s">
-        <v>17</v>
-      </c>
-      <c r="M5" t="s">
-        <v>17</v>
-      </c>
-      <c r="N5" t="s">
-        <v>22</v>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" t="s">
+        <v>85</v>
+      </c>
+      <c r="D10" t="s">
+        <v>86</v>
+      </c>
+      <c r="E10" t="s">
+        <v>87</v>
+      </c>
+      <c r="F10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" t="s">
+        <v>88</v>
+      </c>
+      <c r="J10" t="s">
+        <v>89</v>
+      </c>
+      <c r="K10" t="s">
+        <v>199</v>
+      </c>
+      <c r="L10" t="s">
+        <v>27</v>
+      </c>
+      <c r="M10" t="s">
+        <v>90</v>
+      </c>
+      <c r="N10" t="s">
+        <v>91</v>
+      </c>
+      <c r="O10" t="s">
+        <v>92</v>
+      </c>
+      <c r="P10" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>221</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J6" t="s">
-        <v>43</v>
-      </c>
-      <c r="K6" t="s">
-        <v>17</v>
-      </c>
-      <c r="L6" t="s">
-        <v>17</v>
-      </c>
-      <c r="M6" t="s">
-        <v>17</v>
-      </c>
-      <c r="N6" t="s">
-        <v>22</v>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" t="s">
+        <v>96</v>
+      </c>
+      <c r="D11" t="s">
+        <v>97</v>
+      </c>
+      <c r="E11" t="s">
+        <v>98</v>
+      </c>
+      <c r="F11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" t="s">
+        <v>99</v>
+      </c>
+      <c r="J11" t="s">
+        <v>100</v>
+      </c>
+      <c r="K11" t="s">
+        <v>200</v>
+      </c>
+      <c r="L11" t="s">
+        <v>27</v>
+      </c>
+      <c r="M11" t="s">
+        <v>101</v>
+      </c>
+      <c r="N11" t="s">
+        <v>102</v>
+      </c>
+      <c r="O11" t="s">
+        <v>103</v>
+      </c>
+      <c r="P11" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>222</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J7" t="s">
-        <v>47</v>
-      </c>
-      <c r="K7" t="s">
-        <v>17</v>
-      </c>
-      <c r="L7" t="s">
-        <v>17</v>
-      </c>
-      <c r="M7" t="s">
-        <v>17</v>
-      </c>
-      <c r="N7" t="s">
-        <v>22</v>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>105</v>
+      </c>
+      <c r="B12" t="s">
+        <v>106</v>
+      </c>
+      <c r="C12" t="s">
+        <v>107</v>
+      </c>
+      <c r="D12" t="s">
+        <v>108</v>
+      </c>
+      <c r="E12" t="s">
+        <v>109</v>
+      </c>
+      <c r="F12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" t="s">
+        <v>49</v>
+      </c>
+      <c r="H12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" t="s">
+        <v>25</v>
+      </c>
+      <c r="K12" t="s">
+        <v>201</v>
+      </c>
+      <c r="L12" t="s">
+        <v>27</v>
+      </c>
+      <c r="M12" t="s">
+        <v>110</v>
+      </c>
+      <c r="N12" t="s">
+        <v>22</v>
+      </c>
+      <c r="O12" t="s">
+        <v>22</v>
+      </c>
+      <c r="P12" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>223</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B8" t="s">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>111</v>
+      </c>
+      <c r="B13" t="s">
+        <v>112</v>
+      </c>
+      <c r="C13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D13" t="s">
+        <v>114</v>
+      </c>
+      <c r="E13" t="s">
+        <v>115</v>
+      </c>
+      <c r="F13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" t="s">
+        <v>56</v>
+      </c>
+      <c r="H13" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" t="s">
+        <v>25</v>
+      </c>
+      <c r="K13" t="s">
+        <v>202</v>
+      </c>
+      <c r="L13" t="s">
+        <v>27</v>
+      </c>
+      <c r="M13" t="s">
+        <v>116</v>
+      </c>
+      <c r="N13" t="s">
+        <v>22</v>
+      </c>
+      <c r="O13" t="s">
+        <v>22</v>
+      </c>
+      <c r="P13" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>117</v>
+      </c>
+      <c r="B14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" t="s">
+        <v>119</v>
+      </c>
+      <c r="D14" t="s">
+        <v>120</v>
+      </c>
+      <c r="E14" t="s">
+        <v>121</v>
+      </c>
+      <c r="F14" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" t="s">
         <v>49</v>
       </c>
-      <c r="C8" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E8" t="s">
-        <v>60</v>
-      </c>
-      <c r="F8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J8" t="s">
-        <v>51</v>
-      </c>
-      <c r="K8" t="s">
-        <v>17</v>
-      </c>
-      <c r="L8" t="s">
-        <v>17</v>
-      </c>
-      <c r="M8" t="s">
-        <v>17</v>
-      </c>
-      <c r="N8" t="s">
-        <v>22</v>
+      <c r="H14" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" t="s">
+        <v>22</v>
+      </c>
+      <c r="J14" t="s">
+        <v>25</v>
+      </c>
+      <c r="K14" t="s">
+        <v>203</v>
+      </c>
+      <c r="L14" t="s">
+        <v>27</v>
+      </c>
+      <c r="M14" t="s">
+        <v>122</v>
+      </c>
+      <c r="N14" t="s">
+        <v>22</v>
+      </c>
+      <c r="O14" t="s">
+        <v>22</v>
+      </c>
+      <c r="P14" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>225</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C9" t="s">
-        <v>54</v>
-      </c>
-      <c r="D9" t="s">
-        <v>59</v>
-      </c>
-      <c r="E9" t="s">
-        <v>60</v>
-      </c>
-      <c r="F9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" t="s">
-        <v>19</v>
-      </c>
-      <c r="I9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J9" t="s">
-        <v>55</v>
-      </c>
-      <c r="K9" t="s">
-        <v>17</v>
-      </c>
-      <c r="L9" t="s">
-        <v>17</v>
-      </c>
-      <c r="M9" t="s">
-        <v>17</v>
-      </c>
-      <c r="N9" t="s">
-        <v>22</v>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>123</v>
+      </c>
+      <c r="B15" t="s">
+        <v>124</v>
+      </c>
+      <c r="C15" t="s">
+        <v>125</v>
+      </c>
+      <c r="D15" t="s">
+        <v>126</v>
+      </c>
+      <c r="E15" t="s">
+        <v>127</v>
+      </c>
+      <c r="F15" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" t="s">
+        <v>49</v>
+      </c>
+      <c r="H15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I15" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" t="s">
+        <v>25</v>
+      </c>
+      <c r="K15" t="s">
+        <v>204</v>
+      </c>
+      <c r="L15" t="s">
+        <v>27</v>
+      </c>
+      <c r="M15" t="s">
+        <v>128</v>
+      </c>
+      <c r="N15" t="s">
+        <v>22</v>
+      </c>
+      <c r="O15" t="s">
+        <v>22</v>
+      </c>
+      <c r="P15" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>226</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>129</v>
+      </c>
+      <c r="B16" t="s">
+        <v>130</v>
+      </c>
+      <c r="C16" t="s">
+        <v>131</v>
+      </c>
+      <c r="D16" t="s">
+        <v>132</v>
+      </c>
+      <c r="E16" t="s">
+        <v>133</v>
+      </c>
+      <c r="F16" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16" t="s">
+        <v>22</v>
+      </c>
+      <c r="J16" t="s">
+        <v>25</v>
+      </c>
+      <c r="K16" t="s">
+        <v>205</v>
+      </c>
+      <c r="L16" t="s">
+        <v>27</v>
+      </c>
+      <c r="M16" t="s">
+        <v>134</v>
+      </c>
+      <c r="N16" t="s">
+        <v>22</v>
+      </c>
+      <c r="O16" t="s">
+        <v>22</v>
+      </c>
+      <c r="P16" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>135</v>
+      </c>
+      <c r="B17" t="s">
+        <v>136</v>
+      </c>
+      <c r="C17" t="s">
+        <v>137</v>
+      </c>
+      <c r="D17" t="s">
+        <v>138</v>
+      </c>
+      <c r="E17" t="s">
+        <v>139</v>
+      </c>
+      <c r="F17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" t="s">
+        <v>49</v>
+      </c>
+      <c r="H17" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J17" t="s">
+        <v>25</v>
+      </c>
+      <c r="K17" t="s">
+        <v>206</v>
+      </c>
+      <c r="L17" t="s">
+        <v>27</v>
+      </c>
+      <c r="M17" t="s">
+        <v>140</v>
+      </c>
+      <c r="N17" t="s">
+        <v>22</v>
+      </c>
+      <c r="O17" t="s">
+        <v>22</v>
+      </c>
+      <c r="P17" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>141</v>
+      </c>
+      <c r="B18" t="s">
+        <v>142</v>
+      </c>
+      <c r="C18" t="s">
+        <v>143</v>
+      </c>
+      <c r="D18" t="s">
+        <v>144</v>
+      </c>
+      <c r="E18" t="s">
+        <v>145</v>
+      </c>
+      <c r="F18" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" t="s">
         <v>56</v>
       </c>
-      <c r="B10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" t="s">
-        <v>58</v>
-      </c>
-      <c r="D10" t="s">
-        <v>59</v>
-      </c>
-      <c r="E10" t="s">
-        <v>60</v>
-      </c>
-      <c r="F10" t="s">
-        <v>61</v>
-      </c>
-      <c r="G10" t="s">
-        <v>62</v>
-      </c>
-      <c r="H10" t="s">
-        <v>19</v>
-      </c>
-      <c r="I10" t="s">
-        <v>20</v>
-      </c>
-      <c r="J10" t="s">
+      <c r="H18" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18" t="s">
+        <v>22</v>
+      </c>
+      <c r="J18" t="s">
+        <v>25</v>
+      </c>
+      <c r="K18" t="s">
+        <v>207</v>
+      </c>
+      <c r="L18" t="s">
+        <v>27</v>
+      </c>
+      <c r="M18" t="s">
+        <v>146</v>
+      </c>
+      <c r="N18" t="s">
+        <v>22</v>
+      </c>
+      <c r="O18" t="s">
+        <v>22</v>
+      </c>
+      <c r="P18" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>147</v>
+      </c>
+      <c r="B19" t="s">
+        <v>148</v>
+      </c>
+      <c r="C19" t="s">
+        <v>149</v>
+      </c>
+      <c r="D19" t="s">
+        <v>150</v>
+      </c>
+      <c r="E19" t="s">
+        <v>151</v>
+      </c>
+      <c r="F19" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" t="s">
         <v>63</v>
       </c>
-      <c r="K10" t="s">
-        <v>64</v>
-      </c>
-      <c r="L10" t="s">
-        <v>65</v>
-      </c>
-      <c r="M10" t="s">
-        <v>66</v>
-      </c>
-      <c r="N10" t="s">
-        <v>22</v>
+      <c r="H19" t="s">
+        <v>24</v>
+      </c>
+      <c r="I19" t="s">
+        <v>152</v>
+      </c>
+      <c r="J19" t="s">
+        <v>153</v>
+      </c>
+      <c r="K19" t="s">
+        <v>208</v>
+      </c>
+      <c r="L19" t="s">
+        <v>27</v>
+      </c>
+      <c r="M19" t="s">
+        <v>154</v>
+      </c>
+      <c r="N19" t="s">
+        <v>155</v>
+      </c>
+      <c r="O19" t="s">
+        <v>156</v>
+      </c>
+      <c r="P19" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>230</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>67</v>
-      </c>
-      <c r="B11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" t="s">
-        <v>69</v>
-      </c>
-      <c r="D11" t="s">
-        <v>59</v>
-      </c>
-      <c r="E11" t="s">
-        <v>60</v>
-      </c>
-      <c r="F11" t="s">
-        <v>70</v>
-      </c>
-      <c r="G11" t="s">
-        <v>71</v>
-      </c>
-      <c r="H11" t="s">
-        <v>19</v>
-      </c>
-      <c r="I11" t="s">
-        <v>20</v>
-      </c>
-      <c r="J11" t="s">
-        <v>72</v>
-      </c>
-      <c r="K11" t="s">
-        <v>73</v>
-      </c>
-      <c r="L11" t="s">
-        <v>74</v>
-      </c>
-      <c r="M11" t="s">
-        <v>75</v>
-      </c>
-      <c r="N11" t="s">
-        <v>22</v>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>158</v>
+      </c>
+      <c r="B20" t="s">
+        <v>159</v>
+      </c>
+      <c r="C20" t="s">
+        <v>160</v>
+      </c>
+      <c r="D20" t="s">
+        <v>161</v>
+      </c>
+      <c r="E20" t="s">
+        <v>162</v>
+      </c>
+      <c r="F20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" t="s">
+        <v>35</v>
+      </c>
+      <c r="H20" t="s">
+        <v>24</v>
+      </c>
+      <c r="I20" t="s">
+        <v>22</v>
+      </c>
+      <c r="J20" t="s">
+        <v>25</v>
+      </c>
+      <c r="K20" t="s">
+        <v>209</v>
+      </c>
+      <c r="L20" t="s">
+        <v>27</v>
+      </c>
+      <c r="M20" t="s">
+        <v>163</v>
+      </c>
+      <c r="N20" t="s">
+        <v>22</v>
+      </c>
+      <c r="O20" t="s">
+        <v>22</v>
+      </c>
+      <c r="P20" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>231</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>76</v>
-      </c>
-      <c r="B12" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" t="s">
-        <v>78</v>
-      </c>
-      <c r="D12" t="s">
-        <v>59</v>
-      </c>
-      <c r="E12" t="s">
-        <v>60</v>
-      </c>
-      <c r="F12" t="s">
-        <v>17</v>
-      </c>
-      <c r="G12" t="s">
-        <v>18</v>
-      </c>
-      <c r="H12" t="s">
-        <v>19</v>
-      </c>
-      <c r="I12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J12" t="s">
-        <v>79</v>
-      </c>
-      <c r="K12" t="s">
-        <v>17</v>
-      </c>
-      <c r="L12" t="s">
-        <v>17</v>
-      </c>
-      <c r="M12" t="s">
-        <v>17</v>
-      </c>
-      <c r="N12" t="s">
-        <v>22</v>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>164</v>
+      </c>
+      <c r="B21" t="s">
+        <v>165</v>
+      </c>
+      <c r="C21" t="s">
+        <v>166</v>
+      </c>
+      <c r="D21" t="s">
+        <v>167</v>
+      </c>
+      <c r="E21" t="s">
+        <v>168</v>
+      </c>
+      <c r="F21" t="s">
+        <v>22</v>
+      </c>
+      <c r="G21" t="s">
+        <v>56</v>
+      </c>
+      <c r="H21" t="s">
+        <v>24</v>
+      </c>
+      <c r="I21" t="s">
+        <v>169</v>
+      </c>
+      <c r="J21" t="s">
+        <v>170</v>
+      </c>
+      <c r="K21" t="s">
+        <v>210</v>
+      </c>
+      <c r="L21" t="s">
+        <v>27</v>
+      </c>
+      <c r="M21" t="s">
+        <v>171</v>
+      </c>
+      <c r="N21" t="s">
+        <v>172</v>
+      </c>
+      <c r="O21" t="s">
+        <v>173</v>
+      </c>
+      <c r="P21" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>232</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>80</v>
-      </c>
-      <c r="B13" t="s">
-        <v>81</v>
-      </c>
-      <c r="C13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D13" t="s">
-        <v>59</v>
-      </c>
-      <c r="E13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F13" t="s">
-        <v>17</v>
-      </c>
-      <c r="G13" t="s">
-        <v>18</v>
-      </c>
-      <c r="H13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J13" t="s">
-        <v>83</v>
-      </c>
-      <c r="K13" t="s">
-        <v>17</v>
-      </c>
-      <c r="L13" t="s">
-        <v>17</v>
-      </c>
-      <c r="M13" t="s">
-        <v>17</v>
-      </c>
-      <c r="N13" t="s">
-        <v>22</v>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>175</v>
+      </c>
+      <c r="B22" t="s">
+        <v>176</v>
+      </c>
+      <c r="C22" t="s">
+        <v>177</v>
+      </c>
+      <c r="D22" t="s">
+        <v>178</v>
+      </c>
+      <c r="E22" t="s">
+        <v>179</v>
+      </c>
+      <c r="F22" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" t="s">
+        <v>63</v>
+      </c>
+      <c r="H22" t="s">
+        <v>24</v>
+      </c>
+      <c r="I22" t="s">
+        <v>22</v>
+      </c>
+      <c r="J22" t="s">
+        <v>25</v>
+      </c>
+      <c r="K22" t="s">
+        <v>211</v>
+      </c>
+      <c r="L22" t="s">
+        <v>27</v>
+      </c>
+      <c r="M22" t="s">
+        <v>180</v>
+      </c>
+      <c r="N22" t="s">
+        <v>22</v>
+      </c>
+      <c r="O22" t="s">
+        <v>22</v>
+      </c>
+      <c r="P22" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>233</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>84</v>
-      </c>
-      <c r="B14" t="s">
-        <v>85</v>
-      </c>
-      <c r="C14" t="s">
-        <v>86</v>
-      </c>
-      <c r="D14" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" t="s">
-        <v>60</v>
-      </c>
-      <c r="F14" t="s">
-        <v>17</v>
-      </c>
-      <c r="G14" t="s">
-        <v>18</v>
-      </c>
-      <c r="H14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I14" t="s">
-        <v>20</v>
-      </c>
-      <c r="J14" t="s">
-        <v>87</v>
-      </c>
-      <c r="K14" t="s">
-        <v>17</v>
-      </c>
-      <c r="L14" t="s">
-        <v>17</v>
-      </c>
-      <c r="M14" t="s">
-        <v>17</v>
-      </c>
-      <c r="N14" t="s">
-        <v>22</v>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>181</v>
+      </c>
+      <c r="B23" t="s">
+        <v>182</v>
+      </c>
+      <c r="C23" t="s">
+        <v>183</v>
+      </c>
+      <c r="D23" t="s">
+        <v>184</v>
+      </c>
+      <c r="E23" t="s">
+        <v>185</v>
+      </c>
+      <c r="F23" t="s">
+        <v>22</v>
+      </c>
+      <c r="G23" t="s">
+        <v>63</v>
+      </c>
+      <c r="H23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23" t="s">
+        <v>22</v>
+      </c>
+      <c r="J23" t="s">
+        <v>25</v>
+      </c>
+      <c r="K23" t="s">
+        <v>212</v>
+      </c>
+      <c r="L23" t="s">
+        <v>27</v>
+      </c>
+      <c r="M23" t="s">
+        <v>186</v>
+      </c>
+      <c r="N23" t="s">
+        <v>22</v>
+      </c>
+      <c r="O23" t="s">
+        <v>22</v>
+      </c>
+      <c r="P23" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>234</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>88</v>
-      </c>
-      <c r="B15" t="s">
-        <v>89</v>
-      </c>
-      <c r="C15" t="s">
-        <v>90</v>
-      </c>
-      <c r="D15" t="s">
-        <v>59</v>
-      </c>
-      <c r="E15" t="s">
-        <v>60</v>
-      </c>
-      <c r="F15" t="s">
-        <v>17</v>
-      </c>
-      <c r="G15" t="s">
-        <v>18</v>
-      </c>
-      <c r="H15" t="s">
-        <v>19</v>
-      </c>
-      <c r="I15" t="s">
-        <v>20</v>
-      </c>
-      <c r="J15" t="s">
-        <v>91</v>
-      </c>
-      <c r="K15" t="s">
-        <v>17</v>
-      </c>
-      <c r="L15" t="s">
-        <v>17</v>
-      </c>
-      <c r="M15" t="s">
-        <v>17</v>
-      </c>
-      <c r="N15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>92</v>
-      </c>
-      <c r="B16" t="s">
-        <v>93</v>
-      </c>
-      <c r="C16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D16" t="s">
-        <v>59</v>
-      </c>
-      <c r="E16" t="s">
-        <v>60</v>
-      </c>
-      <c r="F16" t="s">
-        <v>17</v>
-      </c>
-      <c r="G16" t="s">
-        <v>18</v>
-      </c>
-      <c r="H16" t="s">
-        <v>19</v>
-      </c>
-      <c r="I16" t="s">
-        <v>20</v>
-      </c>
-      <c r="J16" t="s">
-        <v>95</v>
-      </c>
-      <c r="K16" t="s">
-        <v>17</v>
-      </c>
-      <c r="L16" t="s">
-        <v>17</v>
-      </c>
-      <c r="M16" t="s">
-        <v>17</v>
-      </c>
-      <c r="N16" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>96</v>
-      </c>
-      <c r="B17" t="s">
-        <v>97</v>
-      </c>
-      <c r="C17" t="s">
-        <v>98</v>
-      </c>
-      <c r="D17" t="s">
-        <v>59</v>
-      </c>
-      <c r="E17" t="s">
-        <v>60</v>
-      </c>
-      <c r="F17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G17" t="s">
-        <v>18</v>
-      </c>
-      <c r="H17" t="s">
-        <v>19</v>
-      </c>
-      <c r="I17" t="s">
-        <v>20</v>
-      </c>
-      <c r="J17" t="s">
-        <v>99</v>
-      </c>
-      <c r="K17" t="s">
-        <v>17</v>
-      </c>
-      <c r="L17" t="s">
-        <v>17</v>
-      </c>
-      <c r="M17" t="s">
-        <v>17</v>
-      </c>
-      <c r="N17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>100</v>
-      </c>
-      <c r="B18" t="s">
-        <v>101</v>
-      </c>
-      <c r="C18" t="s">
-        <v>102</v>
-      </c>
-      <c r="D18" t="s">
-        <v>59</v>
-      </c>
-      <c r="E18" t="s">
-        <v>60</v>
-      </c>
-      <c r="F18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G18" t="s">
-        <v>18</v>
-      </c>
-      <c r="H18" t="s">
-        <v>19</v>
-      </c>
-      <c r="I18" t="s">
-        <v>20</v>
-      </c>
-      <c r="J18" t="s">
-        <v>103</v>
-      </c>
-      <c r="K18" t="s">
-        <v>17</v>
-      </c>
-      <c r="L18" t="s">
-        <v>17</v>
-      </c>
-      <c r="M18" t="s">
-        <v>17</v>
-      </c>
-      <c r="N18" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>104</v>
-      </c>
-      <c r="B19" t="s">
-        <v>105</v>
-      </c>
-      <c r="C19" t="s">
-        <v>106</v>
-      </c>
-      <c r="D19" t="s">
-        <v>59</v>
-      </c>
-      <c r="E19" t="s">
-        <v>60</v>
-      </c>
-      <c r="F19" t="s">
-        <v>107</v>
-      </c>
-      <c r="G19" t="s">
-        <v>108</v>
-      </c>
-      <c r="H19" t="s">
-        <v>19</v>
-      </c>
-      <c r="I19" t="s">
-        <v>20</v>
-      </c>
-      <c r="J19" t="s">
-        <v>109</v>
-      </c>
-      <c r="K19" t="s">
-        <v>110</v>
-      </c>
-      <c r="L19" t="s">
-        <v>111</v>
-      </c>
-      <c r="M19" t="s">
-        <v>112</v>
-      </c>
-      <c r="N19" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>113</v>
-      </c>
-      <c r="B20" t="s">
-        <v>114</v>
-      </c>
-      <c r="C20" t="s">
-        <v>115</v>
-      </c>
-      <c r="D20" t="s">
-        <v>59</v>
-      </c>
-      <c r="E20" t="s">
-        <v>60</v>
-      </c>
-      <c r="F20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G20" t="s">
-        <v>18</v>
-      </c>
-      <c r="H20" t="s">
-        <v>19</v>
-      </c>
-      <c r="I20" t="s">
-        <v>20</v>
-      </c>
-      <c r="J20" t="s">
-        <v>116</v>
-      </c>
-      <c r="K20" t="s">
-        <v>17</v>
-      </c>
-      <c r="L20" t="s">
-        <v>17</v>
-      </c>
-      <c r="M20" t="s">
-        <v>17</v>
-      </c>
-      <c r="N20" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>117</v>
-      </c>
-      <c r="B21" t="s">
-        <v>118</v>
-      </c>
-      <c r="C21" t="s">
-        <v>119</v>
-      </c>
-      <c r="D21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E21" t="s">
-        <v>60</v>
-      </c>
-      <c r="F21" t="s">
-        <v>120</v>
-      </c>
-      <c r="G21" t="s">
-        <v>121</v>
-      </c>
-      <c r="H21" t="s">
-        <v>19</v>
-      </c>
-      <c r="I21" t="s">
-        <v>20</v>
-      </c>
-      <c r="J21" t="s">
-        <v>122</v>
-      </c>
-      <c r="K21" t="s">
-        <v>123</v>
-      </c>
-      <c r="L21" t="s">
-        <v>124</v>
-      </c>
-      <c r="M21" t="s">
-        <v>125</v>
-      </c>
-      <c r="N21" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>126</v>
-      </c>
-      <c r="B22" t="s">
-        <v>127</v>
-      </c>
-      <c r="C22" t="s">
-        <v>128</v>
-      </c>
-      <c r="D22" t="s">
-        <v>59</v>
-      </c>
-      <c r="E22" t="s">
-        <v>60</v>
-      </c>
-      <c r="F22" t="s">
-        <v>17</v>
-      </c>
-      <c r="G22" t="s">
-        <v>18</v>
-      </c>
-      <c r="H22" t="s">
-        <v>19</v>
-      </c>
-      <c r="I22" t="s">
-        <v>20</v>
-      </c>
-      <c r="J22" t="s">
-        <v>129</v>
-      </c>
-      <c r="K22" t="s">
-        <v>17</v>
-      </c>
-      <c r="L22" t="s">
-        <v>17</v>
-      </c>
-      <c r="M22" t="s">
-        <v>17</v>
-      </c>
-      <c r="N22" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>130</v>
-      </c>
-      <c r="B23" t="s">
-        <v>131</v>
-      </c>
-      <c r="C23" t="s">
-        <v>132</v>
-      </c>
-      <c r="D23" t="s">
-        <v>59</v>
-      </c>
-      <c r="E23" t="s">
-        <v>60</v>
-      </c>
-      <c r="F23" t="s">
-        <v>17</v>
-      </c>
-      <c r="G23" t="s">
-        <v>18</v>
-      </c>
-      <c r="H23" t="s">
-        <v>19</v>
-      </c>
-      <c r="I23" t="s">
-        <v>20</v>
-      </c>
-      <c r="J23" t="s">
-        <v>133</v>
-      </c>
-      <c r="K23" t="s">
-        <v>17</v>
-      </c>
-      <c r="L23" t="s">
-        <v>17</v>
-      </c>
-      <c r="M23" t="s">
-        <v>17</v>
-      </c>
-      <c r="N23" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>134</v>
+        <v>187</v>
       </c>
       <c r="B24" t="s">
-        <v>135</v>
+        <v>188</v>
       </c>
       <c r="C24" t="s">
-        <v>136</v>
+        <v>189</v>
       </c>
       <c r="D24" t="s">
-        <v>59</v>
+        <v>190</v>
       </c>
       <c r="E24" t="s">
-        <v>60</v>
+        <v>191</v>
       </c>
       <c r="F24" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G24" t="s">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="H24" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I24" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J24" t="s">
-        <v>137</v>
+        <v>25</v>
       </c>
       <c r="K24" t="s">
-        <v>17</v>
+        <v>213</v>
       </c>
       <c r="L24" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="M24" t="s">
-        <v>17</v>
+        <v>192</v>
       </c>
       <c r="N24" t="s">
         <v>22</v>
+      </c>
+      <c r="O24" t="s">
+        <v>22</v>
+      </c>
+      <c r="P24" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>235</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/DesignData/Excel_Masters/CharacterAssets_Master.xlsx
+++ b/DesignData/Excel_Masters/CharacterAssets_Master.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22065" windowHeight="9420"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12285"/>
   </bookViews>
   <sheets>
     <sheet name="CharacterAssets" sheetId="1" r:id="rId1"/>
@@ -24,42 +24,45 @@
     <t>---</t>
   </si>
   <si>
+    <t>BodyIcon</t>
+  </si>
+  <si>
+    <t>AwakeningPieceIcon</t>
+  </si>
+  <si>
+    <t>IdleAnim</t>
+  </si>
+  <si>
+    <t>UltimateIcon</t>
+  </si>
+  <si>
+    <t>Rarity</t>
+  </si>
+  <si>
+    <t>UltimateAttackSetup</t>
+  </si>
+  <si>
+    <t>UltimateMontage</t>
+  </si>
+  <si>
+    <t>WeaponAnimMap</t>
+  </si>
+  <si>
+    <t>CharacterFX</t>
+  </si>
+  <si>
+    <t>UltimateEffectTag</t>
+  </si>
+  <si>
+    <t>FactionTag</t>
+  </si>
+  <si>
+    <t>SkeletalMesh</t>
+  </si>
+  <si>
     <t>FaceIcon</t>
   </si>
   <si>
-    <t>BodyIcon</t>
-  </si>
-  <si>
-    <t>AwakeningPieceIcon</t>
-  </si>
-  <si>
-    <t>IdleAnim</t>
-  </si>
-  <si>
-    <t>UltimateIcon</t>
-  </si>
-  <si>
-    <t>Rarity</t>
-  </si>
-  <si>
-    <t>UltimateAttackSetup</t>
-  </si>
-  <si>
-    <t>UltimateMontage</t>
-  </si>
-  <si>
-    <t>WeaponAnimMap</t>
-  </si>
-  <si>
-    <t>UltimateEffectTag</t>
-  </si>
-  <si>
-    <t>FactionTag</t>
-  </si>
-  <si>
-    <t>SkeletalMesh</t>
-  </si>
-  <si>
     <t>AnimBlueprint</t>
   </si>
   <si>
@@ -69,81 +72,75 @@
     <t>DeathMontage</t>
   </si>
   <si>
-    <t>ReactionFX</t>
-  </si>
-  <si>
     <t>Char_Anubis</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Anubis.Icon_Anubis</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Anubis.Icon_Anubis</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Anubis/Ani/Anubis_Base_Battle_Idle_Anim_Anubis_Base_Battle_Idle1.Anubis_Base_Battle_Idle_Anim_Anubis_Base_Battle_Idle1</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Legendary</t>
+  </si>
+  <si>
+    <t>(AbilityClass=None,EffectClass=None,ProjectileClass=None)</t>
+  </si>
+  <si>
+    <t>()</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Anubis.Ultimate")</t>
+  </si>
+  <si>
+    <t>(TagName="Unit.Faction.Friendly.Player")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Anubis/SKM_Anubis_Base.SKM_Anubis_Base</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Anubis.Icon_Anubis</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Anubis.Icon_Anubis</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Anubis.Icon_Anubis</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Anubis/Ani/Anubis_Base_Battle_Idle_Anim_Anubis_Base_Battle_Idle1.Anubis_Base_Battle_Idle_Anim_Anubis_Base_Battle_Idle1</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>Legendary</t>
-  </si>
-  <si>
-    <t>(AbilityClass=None,EffectClass=None,ProjectileClass=None)</t>
-  </si>
-  <si>
-    <t>()</t>
-  </si>
-  <si>
-    <t>(TagName="FX.Character.Anubis.Ultimate")</t>
-  </si>
-  <si>
-    <t>(TagName="Unit.Faction.Friendly.Player")</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Anubis/SKM_Anubis_Base.SKM_Anubis_Base</t>
-  </si>
-  <si>
-    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Anubis.DA_CharFX_Anubis",HitTag=(TagName="FX.Character.Anubis.Hit"),DeathTag=(TagName="FX.Character.Anubis.Death"))</t>
-  </si>
-  <si>
     <t>Char_Army</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Army.Icon_Army</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Army.Icon_Army</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Army/Ani/Army_Base_Battle_Idle.Army_Base_Battle_Idle</t>
+  </si>
+  <si>
+    <t>Common</t>
+  </si>
+  <si>
+    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_AreaUltimate.GA_AreaUltimate_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Buff_AttackPowerUp.GE_Buff_AttackPowerUp_C'",ProjectileClass=None)</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Player/Army/AM_Army_Ultimate_Attack.AM_Army_Ultimate_Attack</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Army/AM_Army_Book_Attack.AM_Army_Book_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Army/AM_Army_Book_Skill.AM_Army_Book_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Army/AM_Army_Melee_Attack.AM_Army_Melee_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Army/AM_Army_Melee_Attack.AM_Army_Melee_Attack")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Army/AM_Army_Gun_Attack.AM_Army_Gun_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Army/AM_Army_Gun_Attack.AM_Army_Gun_Attack")))</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Army.Ultimate")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Army/SKM_Army_Base.SKM_Army_Base</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Army.Icon_Army</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Army.Icon_Army</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Army.Icon_Army</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Army/Ani/Army_Base_Battle_Idle.Army_Base_Battle_Idle</t>
-  </si>
-  <si>
-    <t>Common</t>
-  </si>
-  <si>
-    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_AreaUltimate.GA_AreaUltimate_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Buff_AttackPowerUp.GE_Buff_AttackPowerUp_C'",ProjectileClass=None)</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Player/Army/AM_Army_Ultimate_Attack.AM_Army_Ultimate_Attack</t>
-  </si>
-  <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Army/AM_Army_Book_Attack.AM_Army_Book_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Army/AM_Army_Book_Skill.AM_Army_Book_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Army/AM_Army_Melee_Attack.AM_Army_Melee_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Army/AM_Army_Melee_Attack.AM_Army_Melee_Attack")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Army/AM_Army_Gun_Attack.AM_Army_Gun_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Army/AM_Army_Gun_Attack.AM_Army_Gun_Attack")))</t>
-  </si>
-  <si>
-    <t>(TagName="FX.Character.Army.Ultimate")</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Army/SKM_Army_Base.SKM_Army_Base</t>
-  </si>
-  <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Player/Army/ABP_Base_Army.ABP_Base_Army_C'</t>
   </si>
   <si>
@@ -156,144 +153,165 @@
     <t>Char_Bard</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Bard.Icon_Bard</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Bard.Icon_Bard</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Bard/Bard_Modify/Ani/Bard_Base_Battle_Idle.Bard_Base_Battle_Idle</t>
+  </si>
+  <si>
+    <t>Uncommon</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Bard.Ultimate")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Bard/Bard_Modify/SKM_Bard_Base_Modified.SKM_Bard_Base_Modified</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Bard.Icon_Bard</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Bard.Icon_Bard</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Bard.Icon_Bard</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Bard/Bard_Modify/Ani/Bard_Base_Battle_Idle.Bard_Base_Battle_Idle</t>
-  </si>
-  <si>
-    <t>Uncommon</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Bard/Bard_Modify/SKM_Bard_Base_Modified.SKM_Bard_Base_Modified</t>
-  </si>
-  <si>
     <t>Char_Binder</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Binder.Icon_Binder</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Binder.Icon_Binder</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Binder/Ani/Binder_Base_Battle_Idle.Binder_Base_Battle_Idle</t>
+  </si>
+  <si>
+    <t>Epic</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Binder.Ultimate")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Player/Binder/SKM_Binder_Base.SKM_Binder_Base</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Binder.Icon_Binder</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Binder.Icon_Binder</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Binder.Icon_Binder</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Binder/Ani/Binder_Base_Battle_Idle.Binder_Base_Battle_Idle</t>
-  </si>
-  <si>
-    <t>Epic</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Player/Binder/SKM_Binder_Base.SKM_Binder_Base</t>
-  </si>
-  <si>
     <t>Char_Courier</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Courier.Icon_Courier</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Courier.Icon_Courier</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Courier/Ani/Courier_Base_Lobby_Idle_Anim_Take_0011.Courier_Base_Lobby_Idle_Anim_Take_0011</t>
+  </si>
+  <si>
+    <t>Rare</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Courier.Ultimate")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Courier/SKM_Courier_Base2.SKM_Courier_Base2</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Courier.Icon_Courier</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Courier.Icon_Courier</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Courier.Icon_Courier</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Courier/Ani/Courier_Base_Lobby_Idle_Anim_Take_0011.Courier_Base_Lobby_Idle_Anim_Take_0011</t>
-  </si>
-  <si>
-    <t>Rare</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Courier/SKM_Courier_Base2.SKM_Courier_Base2</t>
-  </si>
-  <si>
     <t>Char_Demonia</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Demonia.Icon_Demonia</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Demonia.Icon_Demonia</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Demonia/Ani/Demonia_Base_Battle_Idle.Demonia_Base_Battle_Idle</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Demonia.Ultimate")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Demonia/SKM_Demonia_Base.SKM_Demonia_Base</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Demonia.Icon_Demonia</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Demonia.Icon_Demonia</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Demonia.Icon_Demonia</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Demonia/Ani/Demonia_Base_Battle_Idle.Demonia_Base_Battle_Idle</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Demonia/SKM_Demonia_Base.SKM_Demonia_Base</t>
-  </si>
-  <si>
     <t>Char_Enchanter</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Enchanter.Icon_Enchanter</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Enchanter.Icon_Enchanter</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Enchanter/Ani/Enchanter_Base_Battle_Idle_Anim_Take_001.Enchanter_Base_Battle_Idle_Anim_Take_001</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Enchanter.Ultimate")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Enchanter/SKM_Enchanter_Base.SKM_Enchanter_Base</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Enchanter.Icon_Enchanter</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Enchanter.Icon_Enchanter</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Enchanter.Icon_Enchanter</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Enchanter/Ani/Enchanter_Base_Battle_Idle_Anim_Take_001.Enchanter_Base_Battle_Idle_Anim_Take_001</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Enchanter/SKM_Enchanter_Base.SKM_Enchanter_Base</t>
-  </si>
-  <si>
     <t>Char_Guard</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Guard.Icon_Guard</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Guard.Icon_Guard</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Guard/Ani/Guard_Base_Battle_Idle.Guard_Base_Battle_Idle</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Guard.Ultimate")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Guard/SKM_Guard_Base.SKM_Guard_Base</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Guard.Icon_Guard</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Guard.Icon_Guard</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Guard.Icon_Guard</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Guard/Ani/Guard_Base_Battle_Idle.Guard_Base_Battle_Idle</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Guard/SKM_Guard_Base.SKM_Guard_Base</t>
-  </si>
-  <si>
     <t>Char_Hermit</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Hermit.Icon_Hermit</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Hermit.Icon_Hermit</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Hermit/Ani/Hermit_Base_Battle_Idle_Anim_Hermit_Battle_Idle.Hermit_Base_Battle_Idle_Anim_Hermit_Battle_Idle</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Ultimate_Attack.AM_Hermit_Ultimate_Attack</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Book_Attack.AM_Hermit_Book_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Book_Attack.AM_Hermit_Book_Attack")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Melee_Attack.AM_Hermit_Melee_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Melee_Attack.AM_Hermit_Melee_Attack")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Gun_Attack.AM_Hermit_Gun_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Gun_Attack.AM_Hermit_Gun_Attack")))</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Hermit.Ultimate")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Hermit/SKM_Hermit_Base.SKM_Hermit_Base</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Hermit.Icon_Hermit</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Hermit.Icon_Hermit</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Hermit.Icon_Hermit</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Hermit/Ani/Hermit_Base_Battle_Idle_Anim_Hermit_Battle_Idle.Hermit_Base_Battle_Idle_Anim_Hermit_Battle_Idle</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Ultimate_Attack.AM_Hermit_Ultimate_Attack</t>
-  </si>
-  <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Book_Attack.AM_Hermit_Book_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Book_Attack.AM_Hermit_Book_Attack")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Melee_Attack.AM_Hermit_Melee_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Melee_Attack.AM_Hermit_Melee_Attack")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Gun_Attack.AM_Hermit_Gun_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Gun_Attack.AM_Hermit_Gun_Attack")))</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Hermit/SKM_Hermit_Base.SKM_Hermit_Base</t>
-  </si>
-  <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Player/Hermit/ABP_Base_Hermit.ABP_Base_Hermit_C'</t>
   </si>
   <si>
@@ -306,27 +324,30 @@
     <t>Char_Hornet</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Hornet.Icon_Hornet</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Hornet.Icon_Hornet</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Hornet/Ani/Hornet_Base_Battle_Idle.Hornet_Base_Battle_Idle</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Ultimate.AM_Hornet_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Book_Attack.AM_Hornet_Book_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Book_Attack.AM_Hornet_Book_Attack")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Melee_Attack.AM_Hornet_Melee_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Melee_Attack.AM_Hornet_Melee_Attack")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Gun_Attack.AM_Hornet_Gun_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Gun_Attack.AM_Hornet_Gun_Attack")))</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Hornet.Ultimate")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Hornet/SKM_Hornet_Base.SKM_Hornet_Base</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Hornet.Icon_Hornet</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Hornet.Icon_Hornet</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Hornet.Icon_Hornet</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Hornet/Ani/Hornet_Base_Battle_Idle.Hornet_Base_Battle_Idle</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Ultimate.AM_Hornet_Ultimate</t>
-  </si>
-  <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Book_Attack.AM_Hornet_Book_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Book_Attack.AM_Hornet_Book_Attack")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Melee_Attack.AM_Hornet_Melee_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Melee_Attack.AM_Hornet_Melee_Attack")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Gun_Attack.AM_Hornet_Gun_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Gun_Attack.AM_Hornet_Gun_Attack")))</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Hornet/SKM_Hornet_Base.SKM_Hornet_Base</t>
-  </si>
-  <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Player/Hornet/ABP_Base_Hornet.ABP_Base_Hornet_C'</t>
   </si>
   <si>
@@ -339,153 +360,177 @@
     <t>Char_Looter</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Looter.Icon_Looter</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Looter.Icon_Looter</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Looter/Ani/Looter_Base_Battle_Idle.Looter_Base_Battle_Idle</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Looter.Ultimate")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Looter/SKM_Looter_Base.SKM_Looter_Base</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Looter.Icon_Looter</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Looter.Icon_Looter</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Looter.Icon_Looter</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Looter/Ani/Looter_Base_Battle_Idle.Looter_Base_Battle_Idle</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Looter/SKM_Looter_Base.SKM_Looter_Base</t>
-  </si>
-  <si>
     <t>Char_Maid</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Maid.Icon_Maid</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Maid.Icon_Maid</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Maid/Ani/Maid_Base_Idle_Battle.Maid_Base_Idle_Battle</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Maid.Ultimate")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Maid/SKM_Maid_Base.SKM_Maid_Base</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Maid.Icon_Maid</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Maid.Icon_Maid</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Maid.Icon_Maid</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Maid/Ani/Maid_Base_Idle_Battle.Maid_Base_Idle_Battle</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Maid/SKM_Maid_Base.SKM_Maid_Base</t>
-  </si>
-  <si>
     <t>Char_Merry</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Merry.Icon_Merry</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Merry.Icon_Merry</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Merry/Ani/Merry_Base_Battle_Idle.Merry_Base_Battle_Idle</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Merry.Ultimate")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Merry/SKM_Merry_Base.SKM_Merry_Base</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Merry.Icon_Merry</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Merry.Icon_Merry</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Merry.Icon_Merry</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Merry/Ani/Merry_Base_Battle_Idle.Merry_Base_Battle_Idle</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Merry/SKM_Merry_Base.SKM_Merry_Base</t>
-  </si>
-  <si>
     <t>Char_Muzzle</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Muzzle.Icon_Muzzle</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Muzzle.Icon_Muzzle</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Muzzle/Ani/Muzzle_Base_Lobby_Idle_NoWeapon.Muzzle_Base_Lobby_Idle_NoWeapon</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Muzzle.Ultimate")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Muzzle/SKM_Muzzle_Base.SKM_Muzzle_Base</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Muzzle.Icon_Muzzle</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Muzzle.Icon_Muzzle</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Muzzle.Icon_Muzzle</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Muzzle/Ani/Muzzle_Base_Lobby_Idle_NoWeapon.Muzzle_Base_Lobby_Idle_NoWeapon</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Muzzle/SKM_Muzzle_Base.SKM_Muzzle_Base</t>
-  </si>
-  <si>
     <t>Char_Noble</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Noble.Icon_Noble</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Noble.Icon_Noble</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Noble/Ani/Noble_Base_Battle_Idle_Anim_Take_0011.Noble_Base_Battle_Idle_Anim_Take_0011</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Noble.Ultimate")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Noble/SKM_Noble_Base.SKM_Noble_Base</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Noble.Icon_Noble</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Noble.Icon_Noble</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Noble.Icon_Noble</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Noble/Ani/Noble_Base_Battle_Idle_Anim_Take_0011.Noble_Base_Battle_Idle_Anim_Take_0011</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Noble/SKM_Noble_Base.SKM_Noble_Base</t>
-  </si>
-  <si>
     <t>Char_Nurse</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Nurse.Icon_Nurse</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Nurse.Icon_Nurse</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Nurse/Ani/Nurse_Base_Battle_Idle.Nurse_Base_Battle_Idle</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Nurse.Ultimate")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Nurse/SKM_Nurse_Base.SKM_Nurse_Base</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Nurse.Icon_Nurse</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Nurse.Icon_Nurse</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Nurse.Icon_Nurse</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Nurse/Ani/Nurse_Base_Battle_Idle.Nurse_Base_Battle_Idle</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Nurse/SKM_Nurse_Base.SKM_Nurse_Base</t>
-  </si>
-  <si>
     <t>Char_Outsider</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Outsider.Icon_Outsider</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Outsider.Icon_Outsider</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Outsider/Ani/Outsider_Base_Battle_Idle.Outsider_Base_Battle_Idle</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Outsider.Ultimate")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Outsider/SKM_Outsider_Base.SKM_Outsider_Base</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Outsider.Icon_Outsider</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Outsider.Icon_Outsider</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Outsider.Icon_Outsider</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Outsider/Ani/Outsider_Base_Battle_Idle.Outsider_Base_Battle_Idle</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Outsider/SKM_Outsider_Base.SKM_Outsider_Base</t>
-  </si>
-  <si>
     <t>Char_Pioneer</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Pioneer.Icon_Pioneer</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Pioneer.Icon_Pioneer</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Pioneer/Ani/Pioneer_Base_Battle_Idle.Pioneer_Base_Battle_Idle</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Ultimate.AM_Pioneer_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Book_Attack.AM_Pioneer_Book_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Book_Attack.AM_Pioneer_Book_Attack")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Sword_Attack.AM_Pioneer_Sword_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Sword_Attack.AM_Pioneer_Sword_Attack")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Gun_Attack.AM_Pioneer_Gun_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Gun_Attack.AM_Pioneer_Gun_Attack")))</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Pioneer.Ultimate")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Pioneer/SKM_Pioneer_Base.SKM_Pioneer_Base</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Pioneer.Icon_Pioneer</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Pioneer.Icon_Pioneer</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Pioneer.Icon_Pioneer</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Pioneer/Ani/Pioneer_Base_Battle_Idle.Pioneer_Base_Battle_Idle</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Ultimate.AM_Pioneer_Ultimate</t>
-  </si>
-  <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Book_Attack.AM_Pioneer_Book_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Book_Attack.AM_Pioneer_Book_Attack")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Sword_Attack.AM_Pioneer_Sword_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Sword_Attack.AM_Pioneer_Sword_Attack")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Gun_Attack.AM_Pioneer_Gun_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Gun_Attack.AM_Pioneer_Gun_Attack")))</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Pioneer/SKM_Pioneer_Base.SKM_Pioneer_Base</t>
-  </si>
-  <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Player/Pioneer/ABP_Pioneer.ABP_Pioneer_C'</t>
   </si>
   <si>
@@ -498,45 +543,51 @@
     <t>Char_Rogue</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Rogue.Icon_Rogue</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Rogue.Icon_Rogue</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Rogue/Ani/Rogue_Base_Battle_Idle_Anim_Rogue_Base_Battle_Idle.Rogue_Base_Battle_Idle_Anim_Rogue_Base_Battle_Idle</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Rogue.Ultimate")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Rogue/SKM_Rogue_Base.SKM_Rogue_Base</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Rogue.Icon_Rogue</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Rogue.Icon_Rogue</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Rogue.Icon_Rogue</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Rogue/Ani/Rogue_Base_Battle_Idle_Anim_Rogue_Base_Battle_Idle.Rogue_Base_Battle_Idle_Anim_Rogue_Base_Battle_Idle</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Rogue/SKM_Rogue_Base.SKM_Rogue_Base</t>
-  </si>
-  <si>
     <t>Char_Tinker</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Tinker.Icon_Tinker</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Tinker.Icon_Tinker</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Tinker/Ani/Tinker_Base_Battle_Idle_Anim_Tinker_Base_Battle_Idle.Tinker_Base_Battle_Idle_Anim_Tinker_Base_Battle_Idle</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Player/Tinker/AM_Ultimate_Attack.AM_Ultimate_Attack</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Tinker/AM_Book_Attack.AM_Book_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Tinker/AM_Book_Attack.AM_Book_Attack")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Tinker/AM_Melee_Attack.AM_Melee_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Tinker/AM_Melee_Blunt_Attack.AM_Melee_Blunt_Attack")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Tinker/AM_Gun_Attack.AM_Gun_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Tinker/AM_Gun_Attack.AM_Gun_Attack")))</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Tinker.Ultimate")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Tinker/SKM_Tinker_Base.SKM_Tinker_Base</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Tinker.Icon_Tinker</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Tinker.Icon_Tinker</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Tinker.Icon_Tinker</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Tinker/Ani/Tinker_Base_Battle_Idle_Anim_Tinker_Base_Battle_Idle.Tinker_Base_Battle_Idle_Anim_Tinker_Base_Battle_Idle</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Player/Tinker/AM_Ultimate_Attack.AM_Ultimate_Attack</t>
-  </si>
-  <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Tinker/AM_Book_Attack.AM_Book_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Tinker/AM_Book_Attack.AM_Book_Attack")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Tinker/AM_Melee_Attack.AM_Melee_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Tinker/AM_Melee_Blunt_Attack.AM_Melee_Blunt_Attack")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Tinker/AM_Gun_Attack.AM_Gun_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Tinker/AM_Gun_Attack.AM_Gun_Attack")))</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Tinker/SKM_Tinker_Base.SKM_Tinker_Base</t>
-  </si>
-  <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Player/Tinker/ABP_Base.ABP_Base_C'</t>
   </si>
   <si>
@@ -549,184 +600,134 @@
     <t>Char_Tuner</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Tuner.Icon_Tuner</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Tuner.Icon_Tuner</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Tuner/Ani/Tuner_Base_Battle_Idle.Tuner_Base_Battle_Idle</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Tuner.Ultimate")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Tuner/SKM_Tuner_Base.SKM_Tuner_Base</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Tuner.Icon_Tuner</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Tuner.Icon_Tuner</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Tuner.Icon_Tuner</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Tuner/Ani/Tuner_Base_Battle_Idle.Tuner_Base_Battle_Idle</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Tuner/SKM_Tuner_Base.SKM_Tuner_Base</t>
-  </si>
-  <si>
     <t>Char_Weaver</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Weaver.Icon_Weaver</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Weaver.Icon_Weaver</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Weaver/Ani/Weaver_Base_Battle_Idle_Anim_Take_001.Weaver_Base_Battle_Idle_Anim_Take_001</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Weaver.Ultimate")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Weaver/SKM_Weaver_Base.SKM_Weaver_Base</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Weaver.Icon_Weaver</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Weaver.Icon_Weaver</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Weaver.Icon_Weaver</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Weaver/Ani/Weaver_Base_Battle_Idle_Anim_Take_001.Weaver_Base_Battle_Idle_Anim_Take_001</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Weaver/SKM_Weaver_Base.SKM_Weaver_Base</t>
-  </si>
-  <si>
     <t>Char_Writer</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Writer.Icon_Writer</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Writer.Icon_Writer</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Writer/Ani/Writer_Base_Battle_Idle.Writer_Base_Battle_Idle</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Writer.Ultimate")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Writer/SKM_Writer_Base.SKM_Writer_Base</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Writer.Icon_Writer</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Writer.Icon_Writer</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Writer.Icon_Writer</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Writer/Ani/Writer_Base_Battle_Idle.Writer_Base_Battle_Idle</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Writer/SKM_Writer_Base.SKM_Writer_Base</t>
-  </si>
-  <si>
-    <t>(TagName="FX.Character.Bard.Ultimate")</t>
-  </si>
-  <si>
-    <t>(TagName="FX.Character.Binder.Ultimate")</t>
-  </si>
-  <si>
-    <t>(TagName="FX.Character.Courier.Ultimate")</t>
-  </si>
-  <si>
-    <t>(TagName="FX.Character.Demonia.Ultimate")</t>
-  </si>
-  <si>
-    <t>(TagName="FX.Character.Enchanter.Ultimate")</t>
-  </si>
-  <si>
-    <t>(TagName="FX.Character.Guard.Ultimate")</t>
-  </si>
-  <si>
-    <t>(TagName="FX.Character.Hermit.Ultimate")</t>
-  </si>
-  <si>
-    <t>(TagName="FX.Character.Hornet.Ultimate")</t>
-  </si>
-  <si>
-    <t>(TagName="FX.Character.Looter.Ultimate")</t>
-  </si>
-  <si>
-    <t>(TagName="FX.Character.Maid.Ultimate")</t>
-  </si>
-  <si>
-    <t>(TagName="FX.Character.Merry.Ultimate")</t>
-  </si>
-  <si>
-    <t>(TagName="FX.Character.Muzzle.Ultimate")</t>
-  </si>
-  <si>
-    <t>(TagName="FX.Character.Noble.Ultimate")</t>
-  </si>
-  <si>
-    <t>(TagName="FX.Character.Nurse.Ultimate")</t>
-  </si>
-  <si>
-    <t>(TagName="FX.Character.Outsider.Ultimate")</t>
-  </si>
-  <si>
-    <t>(TagName="FX.Character.Pioneer.Ultimate")</t>
-  </si>
-  <si>
-    <t>(TagName="FX.Character.Rogue.Ultimate")</t>
-  </si>
-  <si>
-    <t>(TagName="FX.Character.Tinker.Ultimate")</t>
-  </si>
-  <si>
-    <t>(TagName="FX.Character.Tuner.Ultimate")</t>
-  </si>
-  <si>
-    <t>(TagName="FX.Character.Weaver.Ultimate")</t>
-  </si>
-  <si>
-    <t>(TagName="FX.Character.Writer.Ultimate")</t>
-  </si>
-  <si>
-    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Army.DA_CharFX_Army",HitTag=(TagName="FX.Character.Army.Hit"),DeathTag=(TagName="FX.Character.Army.Death"))</t>
-  </si>
-  <si>
-    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Bard.DA_CharFX_Bard",HitTag=(TagName="FX.Character.Bard.Hit"),DeathTag=(TagName="FX.Character.Bard.Death"))</t>
-  </si>
-  <si>
-    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Binder.DA_CharFX_Binder",HitTag=(TagName="FX.Character.Binder.Hit"),DeathTag=(TagName="FX.Character.Binder.Death"))</t>
-  </si>
-  <si>
-    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Courier.DA_CharFX_Courier",HitTag=(TagName="FX.Character.Courier.Hit"),DeathTag=(TagName="FX.Character.Courier.Death"))</t>
-  </si>
-  <si>
-    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Demonia.DA_CharFX_Demonia",HitTag=(TagName="FX.Character.Demonia.Hit"),DeathTag=(TagName="FX.Character.Demonia.Death"))</t>
-  </si>
-  <si>
-    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Enchanter.DA_CharFX_Enchanter",HitTag=(TagName="FX.Character.Enchanter.Hit"),DeathTag=(TagName="FX.Character.Enchanter.Death"))</t>
-  </si>
-  <si>
-    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Guard.DA_CharFX_Guard",HitTag=(TagName="FX.Character.Guard.Hit"),DeathTag=(TagName="FX.Character.Guard.Death"))</t>
-  </si>
-  <si>
-    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Hermit.DA_CharFX_Hermit",HitTag=(TagName="FX.Character.Hermit.Hit"),DeathTag=(TagName="FX.Character.Hermit.Death"))</t>
-  </si>
-  <si>
-    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Hornet.DA_CharFX_Hornet",HitTag=(TagName="FX.Character.Hornet.Hit"),DeathTag=(TagName="FX.Character.Hornet.Death"))</t>
-  </si>
-  <si>
-    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Looter.DA_CharFX_Looter",HitTag=(TagName="FX.Character.Looter.Hit"),DeathTag=(TagName="FX.Character.Looter.Death"))</t>
-  </si>
-  <si>
-    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Maid.DA_CharFX_Maid",HitTag=(TagName="FX.Character.Maid.Hit"),DeathTag=(TagName="FX.Character.Maid.Death"))</t>
-  </si>
-  <si>
-    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Merry.DA_CharFX_Merry",HitTag=(TagName="FX.Character.Merry.Hit"),DeathTag=(TagName="FX.Character.Merry.Death"))</t>
-  </si>
-  <si>
-    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Muzzle.DA_CharFX_Muzzle",HitTag=(TagName="FX.Character.Muzzle.Hit"),DeathTag=(TagName="FX.Character.Muzzle.Death"))</t>
-  </si>
-  <si>
-    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Noble.DA_CharFX_Noble",HitTag=(TagName="FX.Character.Noble.Hit"),DeathTag=(TagName="FX.Character.Noble.Death"))</t>
-  </si>
-  <si>
-    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Nurse.DA_CharFX_Nurse",HitTag=(TagName="FX.Character.Nurse.Hit"),DeathTag=(TagName="FX.Character.Nurse.Death"))</t>
-  </si>
-  <si>
-    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Outsider.DA_CharFX_Outsider",HitTag=(TagName="FX.Character.Outsider.Hit"),DeathTag=(TagName="FX.Character.Outsider.Death"))</t>
-  </si>
-  <si>
-    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Pioneer.DA_CharFX_Pioneer",HitTag=(TagName="FX.Character.Pioneer.Hit"),DeathTag=(TagName="FX.Character.Pioneer.Death"))</t>
-  </si>
-  <si>
-    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Rogue.DA_CharFX_Rogue",HitTag=(TagName="FX.Character.Rogue.Hit"),DeathTag=(TagName="FX.Character.Rogue.Death"))</t>
-  </si>
-  <si>
-    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Tinker.DA_CharFX_Tinker",HitTag=(TagName="FX.Character.Tinker.Hit"),DeathTag=(TagName="FX.Character.Tinker.Death"))</t>
-  </si>
-  <si>
-    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Tuner.DA_CharFX_Tuner",HitTag=(TagName="FX.Character.Tuner.Hit"),DeathTag=(TagName="FX.Character.Tuner.Death"))</t>
-  </si>
-  <si>
-    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Weaver.DA_CharFX_Weaver",HitTag=(TagName="FX.Character.Weaver.Hit"),DeathTag=(TagName="FX.Character.Weaver.Death"))</t>
-  </si>
-  <si>
-    <t>(ReactionFXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Writer.DA_CharFX_Writer",HitTag=(TagName="FX.Character.Writer.Hit"),DeathTag=(TagName="FX.Character.Writer.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Anubis.DA_CharFX_Anubis",BasicAttackTag=(TagName="FX.Character.Anubis.BasicAttack"),SkillTag=(TagName="FX.Character.Anubis.WeaponSkill"),UltimateTag=(TagName="FX.Character.Anubis.Ultimate"),HitTag=(TagName="FX.Character.Anubis.Hit"),DeathTag=(TagName="FX.Character.Anubis.Death"))</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Army.DA_CharFX_Army",BasicAttackTag=(TagName="FX.Character.Army.BasicAttack"),SkillTag=(TagName="FX.Character.Army.WeaponSkill"),UltimateTag=(TagName="FX.Character.Army.Ultimate"),HitTag=(TagName="FX.Character.Army.Hit"),DeathTag=(TagName="FX.Character.Army.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Bard.DA_CharFX_Bard",BasicAttackTag=(TagName="FX.Character.Bard.BasicAttack"),SkillTag=(TagName="FX.Character.Bard.WeaponSkill"),UltimateTag=(TagName="FX.Character.Bard.Ultimate"),HitTag=(TagName="FX.Character.Bard.Hit"),DeathTag=(TagName="FX.Character.Bard.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Binder.DA_CharFX_Binder",BasicAttackTag=(TagName="FX.Character.Binder.BasicAttack"),SkillTag=(TagName="FX.Character.Binder.WeaponSkill"),UltimateTag=(TagName="FX.Character.Binder.Ultimate"),HitTag=(TagName="FX.Character.Binder.Hit"),DeathTag=(TagName="FX.Character.Binder.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Courier.DA_CharFX_Courier",BasicAttackTag=(TagName="FX.Character.Courier.BasicAttack"),SkillTag=(TagName="FX.Character.Courier.WeaponSkill"),UltimateTag=(TagName="FX.Character.Courier.Ultimate"),HitTag=(TagName="FX.Character.Courier.Hit"),DeathTag=(TagName="FX.Character.Courier.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Demonia.DA_CharFX_Demonia",BasicAttackTag=(TagName="FX.Character.Demonia.BasicAttack"),SkillTag=(TagName="FX.Character.Demonia.WeaponSkill"),UltimateTag=(TagName="FX.Character.Demonia.Ultimate"),HitTag=(TagName="FX.Character.Demonia.Hit"),DeathTag=(TagName="FX.Character.Demonia.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Enchanter.DA_CharFX_Enchanter",BasicAttackTag=(TagName="FX.Character.Enchanter.BasicAttack"),SkillTag=(TagName="FX.Character.Enchanter.WeaponSkill"),UltimateTag=(TagName="FX.Character.Enchanter.Ultimate"),HitTag=(TagName="FX.Character.Enchanter.Hit"),DeathTag=(TagName="FX.Character.Enchanter.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Guard.DA_CharFX_Guard",BasicAttackTag=(TagName="FX.Character.Guard.BasicAttack"),SkillTag=(TagName="FX.Character.Guard.WeaponSkill"),UltimateTag=(TagName="FX.Character.Guard.Ultimate"),HitTag=(TagName="FX.Character.Guard.Hit"),DeathTag=(TagName="FX.Character.Guard.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Hermit.DA_CharFX_Hermit",BasicAttackTag=(TagName="FX.Character.Hermit.BasicAttack"),SkillTag=(TagName="FX.Character.Hermit.WeaponSkill"),UltimateTag=(TagName="FX.Character.Hermit.Ultimate"),HitTag=(TagName="FX.Character.Hermit.Hit"),DeathTag=(TagName="FX.Character.Hermit.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Hornet.DA_CharFX_Hornet",BasicAttackTag=(TagName="FX.Character.Hornet.BasicAttack"),SkillTag=(TagName="FX.Character.Hornet.WeaponSkill"),UltimateTag=(TagName="FX.Character.Hornet.Ultimate"),HitTag=(TagName="FX.Character.Hornet.Hit"),DeathTag=(TagName="FX.Character.Hornet.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Looter.DA_CharFX_Looter",BasicAttackTag=(TagName="FX.Character.Looter.BasicAttack"),SkillTag=(TagName="FX.Character.Looter.WeaponSkill"),UltimateTag=(TagName="FX.Character.Looter.Ultimate"),HitTag=(TagName="FX.Character.Looter.Hit"),DeathTag=(TagName="FX.Character.Looter.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Maid.DA_CharFX_Maid",BasicAttackTag=(TagName="FX.Character.Maid.BasicAttack"),SkillTag=(TagName="FX.Character.Maid.WeaponSkill"),UltimateTag=(TagName="FX.Character.Maid.Ultimate"),HitTag=(TagName="FX.Character.Maid.Hit"),DeathTag=(TagName="FX.Character.Maid.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Merry.DA_CharFX_Merry",BasicAttackTag=(TagName="FX.Character.Merry.BasicAttack"),SkillTag=(TagName="FX.Character.Merry.WeaponSkill"),UltimateTag=(TagName="FX.Character.Merry.Ultimate"),HitTag=(TagName="FX.Character.Merry.Hit"),DeathTag=(TagName="FX.Character.Merry.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Muzzle.DA_CharFX_Muzzle",BasicAttackTag=(TagName="FX.Character.Muzzle.BasicAttack"),SkillTag=(TagName="FX.Character.Muzzle.WeaponSkill"),UltimateTag=(TagName="FX.Character.Muzzle.Ultimate"),HitTag=(TagName="FX.Character.Muzzle.Hit"),DeathTag=(TagName="FX.Character.Muzzle.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Noble.DA_CharFX_Noble",BasicAttackTag=(TagName="FX.Character.Noble.BasicAttack"),SkillTag=(TagName="FX.Character.Noble.WeaponSkill"),UltimateTag=(TagName="FX.Character.Noble.Ultimate"),HitTag=(TagName="FX.Character.Noble.Hit"),DeathTag=(TagName="FX.Character.Noble.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Nurse.DA_CharFX_Nurse",BasicAttackTag=(TagName="FX.Character.Nurse.BasicAttack"),SkillTag=(TagName="FX.Character.Nurse.WeaponSkill"),UltimateTag=(TagName="FX.Character.Nurse.Ultimate"),HitTag=(TagName="FX.Character.Nurse.Hit"),DeathTag=(TagName="FX.Character.Nurse.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Outsider.DA_CharFX_Outsider",BasicAttackTag=(TagName="FX.Character.Outsider.BasicAttack"),SkillTag=(TagName="FX.Character.Outsider.WeaponSkill"),UltimateTag=(TagName="FX.Character.Outsider.Ultimate"),HitTag=(TagName="FX.Character.Outsider.Hit"),DeathTag=(TagName="FX.Character.Outsider.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Pioneer.DA_CharFX_Pioneer",BasicAttackTag=(TagName="FX.Character.Pioneer.BasicAttack"),SkillTag=(TagName="FX.Character.Pioneer.WeaponSkill"),UltimateTag=(TagName="FX.Character.Pioneer.Ultimate"),HitTag=(TagName="FX.Character.Pioneer.Hit"),DeathTag=(TagName="FX.Character.Pioneer.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Rogue.DA_CharFX_Rogue",BasicAttackTag=(TagName="FX.Character.Rogue.BasicAttack"),SkillTag=(TagName="FX.Character.Rogue.WeaponSkill"),UltimateTag=(TagName="FX.Character.Rogue.Ultimate"),HitTag=(TagName="FX.Character.Rogue.Hit"),DeathTag=(TagName="FX.Character.Rogue.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Tinker.DA_CharFX_Tinker",BasicAttackTag=(TagName="FX.Character.Tinker.BasicAttack"),SkillTag=(TagName="FX.Character.Tinker.WeaponSkill"),UltimateTag=(TagName="FX.Character.Tinker.Ultimate"),HitTag=(TagName="FX.Character.Tinker.Hit"),DeathTag=(TagName="FX.Character.Tinker.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Tuner.DA_CharFX_Tuner",BasicAttackTag=(TagName="FX.Character.Tuner.BasicAttack"),SkillTag=(TagName="FX.Character.Tuner.WeaponSkill"),UltimateTag=(TagName="FX.Character.Tuner.Ultimate"),HitTag=(TagName="FX.Character.Tuner.Hit"),DeathTag=(TagName="FX.Character.Tuner.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Weaver.DA_CharFX_Weaver",BasicAttackTag=(TagName="FX.Character.Weaver.BasicAttack"),SkillTag=(TagName="FX.Character.Weaver.WeaponSkill"),UltimateTag=(TagName="FX.Character.Weaver.Ultimate"),HitTag=(TagName="FX.Character.Weaver.Hit"),DeathTag=(TagName="FX.Character.Weaver.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Writer.DA_CharFX_Writer",BasicAttackTag=(TagName="FX.Character.Writer.BasicAttack"),SkillTag=(TagName="FX.Character.Writer.WeaponSkill"),UltimateTag=(TagName="FX.Character.Writer.Ultimate"),HitTag=(TagName="FX.Character.Writer.Hit"),DeathTag=(TagName="FX.Character.Writer.Death"))</t>
   </si>
 </sst>
 </file>
@@ -1646,10 +1647,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q24"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="18.625" customWidth="1"/>
-    <col min="11" max="11" width="18.875" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -1727,140 +1724,140 @@
         <v>23</v>
       </c>
       <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" t="s">
         <v>24</v>
       </c>
-      <c r="I2" t="s">
-        <v>22</v>
-      </c>
       <c r="J2" t="s">
+        <v>213</v>
+      </c>
+      <c r="K2" t="s">
         <v>25</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>26</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>27</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>28</v>
       </c>
-      <c r="N2" t="s">
-        <v>22</v>
-      </c>
       <c r="O2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q2" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s">
         <v>30</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>31</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>32</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
         <v>33</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>34</v>
       </c>
-      <c r="F3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>35</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>36</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
+        <v>214</v>
+      </c>
+      <c r="K3" t="s">
         <v>37</v>
       </c>
-      <c r="J3" t="s">
+      <c r="L3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" t="s">
         <v>38</v>
       </c>
-      <c r="K3" t="s">
+      <c r="N3" t="s">
         <v>39</v>
       </c>
-      <c r="L3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3" t="s">
+      <c r="O3" t="s">
         <v>40</v>
       </c>
-      <c r="N3" t="s">
+      <c r="P3" t="s">
         <v>41</v>
       </c>
-      <c r="O3" t="s">
+      <c r="Q3" t="s">
         <v>42</v>
-      </c>
-      <c r="P3" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" t="s">
         <v>44</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>45</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>46</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
         <v>47</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" t="s">
+        <v>215</v>
+      </c>
+      <c r="K4" t="s">
         <v>48</v>
       </c>
-      <c r="F4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="L4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4" t="s">
         <v>49</v>
       </c>
-      <c r="H4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" t="s">
-        <v>25</v>
-      </c>
-      <c r="K4" t="s">
-        <v>193</v>
-      </c>
-      <c r="L4" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>50</v>
       </c>
-      <c r="N4" t="s">
-        <v>22</v>
-      </c>
       <c r="O4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q4" t="s">
-        <v>215</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
@@ -1877,113 +1874,113 @@
         <v>54</v>
       </c>
       <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
         <v>55</v>
       </c>
-      <c r="F5" t="s">
-        <v>22</v>
-      </c>
       <c r="G5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K5" t="s">
         <v>56</v>
       </c>
-      <c r="H5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" t="s">
-        <v>25</v>
-      </c>
-      <c r="K5" t="s">
-        <v>194</v>
-      </c>
       <c r="L5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M5" t="s">
         <v>57</v>
       </c>
       <c r="N5" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="O5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q5" t="s">
-        <v>216</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E6" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F6" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="G6" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="H6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" t="s">
         <v>24</v>
       </c>
-      <c r="I6" t="s">
-        <v>22</v>
-      </c>
       <c r="J6" t="s">
-        <v>25</v>
+        <v>217</v>
       </c>
       <c r="K6" t="s">
-        <v>195</v>
+        <v>64</v>
       </c>
       <c r="L6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N6" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="O6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q6" t="s">
-        <v>217</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E7" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="F7" t="s">
         <v>22</v>
@@ -1992,475 +1989,475 @@
         <v>23</v>
       </c>
       <c r="H7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" t="s">
         <v>24</v>
       </c>
-      <c r="I7" t="s">
-        <v>22</v>
-      </c>
       <c r="J7" t="s">
-        <v>25</v>
+        <v>218</v>
       </c>
       <c r="K7" t="s">
-        <v>196</v>
+        <v>71</v>
       </c>
       <c r="L7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="N7" t="s">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="O7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q7" t="s">
-        <v>218</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E8" t="s">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="F8" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="G8" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="H8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" t="s">
         <v>24</v>
       </c>
-      <c r="I8" t="s">
-        <v>22</v>
-      </c>
       <c r="J8" t="s">
-        <v>25</v>
+        <v>219</v>
       </c>
       <c r="K8" t="s">
-        <v>197</v>
+        <v>78</v>
       </c>
       <c r="L8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M8" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="N8" t="s">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="O8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q8" t="s">
-        <v>219</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E9" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="F9" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="G9" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="H9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" t="s">
         <v>24</v>
       </c>
-      <c r="I9" t="s">
-        <v>22</v>
-      </c>
       <c r="J9" t="s">
-        <v>25</v>
+        <v>220</v>
       </c>
       <c r="K9" t="s">
-        <v>198</v>
+        <v>85</v>
       </c>
       <c r="L9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M9" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="N9" t="s">
-        <v>22</v>
+        <v>87</v>
       </c>
       <c r="O9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q9" t="s">
-        <v>220</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D10" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E10" t="s">
-        <v>87</v>
+        <v>21</v>
       </c>
       <c r="F10" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="G10" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="H10" t="s">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="I10" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="J10" t="s">
-        <v>89</v>
+        <v>221</v>
       </c>
       <c r="K10" t="s">
-        <v>199</v>
+        <v>94</v>
       </c>
       <c r="L10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M10" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N10" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="O10" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="P10" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="Q10" t="s">
-        <v>221</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B11" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E11" t="s">
-        <v>98</v>
+        <v>21</v>
       </c>
       <c r="F11" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="G11" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="H11" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="I11" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="J11" t="s">
-        <v>100</v>
+        <v>222</v>
       </c>
       <c r="K11" t="s">
-        <v>200</v>
+        <v>106</v>
       </c>
       <c r="L11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M11" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="N11" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="O11" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="P11" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="Q11" t="s">
-        <v>222</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="B12" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="C12" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E12" t="s">
-        <v>109</v>
+        <v>21</v>
       </c>
       <c r="F12" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="G12" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="H12" t="s">
+        <v>21</v>
+      </c>
+      <c r="I12" t="s">
         <v>24</v>
       </c>
-      <c r="I12" t="s">
-        <v>22</v>
-      </c>
       <c r="J12" t="s">
-        <v>25</v>
+        <v>223</v>
       </c>
       <c r="K12" t="s">
-        <v>201</v>
+        <v>116</v>
       </c>
       <c r="L12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M12" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="N12" t="s">
-        <v>22</v>
+        <v>118</v>
       </c>
       <c r="O12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q12" t="s">
-        <v>223</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="B13" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="C13" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="D13" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="E13" t="s">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="F13" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="G13" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="H13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I13" t="s">
         <v>24</v>
       </c>
-      <c r="I13" t="s">
-        <v>22</v>
-      </c>
       <c r="J13" t="s">
-        <v>25</v>
+        <v>224</v>
       </c>
       <c r="K13" t="s">
-        <v>202</v>
+        <v>123</v>
       </c>
       <c r="L13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M13" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="N13" t="s">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="O13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q13" t="s">
-        <v>224</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="B14" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="C14" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="D14" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E14" t="s">
-        <v>121</v>
+        <v>21</v>
       </c>
       <c r="F14" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="G14" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="H14" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" t="s">
         <v>24</v>
       </c>
-      <c r="I14" t="s">
-        <v>22</v>
-      </c>
       <c r="J14" t="s">
-        <v>25</v>
+        <v>225</v>
       </c>
       <c r="K14" t="s">
-        <v>203</v>
+        <v>130</v>
       </c>
       <c r="L14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M14" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="N14" t="s">
-        <v>22</v>
+        <v>132</v>
       </c>
       <c r="O14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q14" t="s">
-        <v>225</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="B15" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="C15" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="D15" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="E15" t="s">
-        <v>127</v>
+        <v>21</v>
       </c>
       <c r="F15" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="G15" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="H15" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" t="s">
         <v>24</v>
       </c>
-      <c r="I15" t="s">
-        <v>22</v>
-      </c>
       <c r="J15" t="s">
-        <v>25</v>
+        <v>226</v>
       </c>
       <c r="K15" t="s">
-        <v>204</v>
+        <v>137</v>
       </c>
       <c r="L15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M15" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="N15" t="s">
-        <v>22</v>
+        <v>139</v>
       </c>
       <c r="O15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q15" t="s">
-        <v>226</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="B16" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="C16" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="D16" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="E16" t="s">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="F16" t="s">
         <v>22</v>
@@ -2469,463 +2466,462 @@
         <v>23</v>
       </c>
       <c r="H16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16" t="s">
         <v>24</v>
       </c>
-      <c r="I16" t="s">
-        <v>22</v>
-      </c>
       <c r="J16" t="s">
-        <v>25</v>
+        <v>227</v>
       </c>
       <c r="K16" t="s">
-        <v>205</v>
+        <v>144</v>
       </c>
       <c r="L16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M16" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="N16" t="s">
-        <v>22</v>
+        <v>146</v>
       </c>
       <c r="O16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q16" t="s">
-        <v>227</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="B17" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="C17" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="D17" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="E17" t="s">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="F17" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="G17" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="H17" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" t="s">
         <v>24</v>
       </c>
-      <c r="I17" t="s">
-        <v>22</v>
-      </c>
       <c r="J17" t="s">
-        <v>25</v>
+        <v>228</v>
       </c>
       <c r="K17" t="s">
-        <v>206</v>
+        <v>151</v>
       </c>
       <c r="L17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M17" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="N17" t="s">
-        <v>22</v>
+        <v>153</v>
       </c>
       <c r="O17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q17" t="s">
-        <v>228</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="B18" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="C18" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="D18" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="E18" t="s">
-        <v>145</v>
+        <v>21</v>
       </c>
       <c r="F18" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="G18" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="H18" t="s">
+        <v>21</v>
+      </c>
+      <c r="I18" t="s">
         <v>24</v>
       </c>
-      <c r="I18" t="s">
-        <v>22</v>
-      </c>
       <c r="J18" t="s">
-        <v>25</v>
+        <v>229</v>
       </c>
       <c r="K18" t="s">
-        <v>207</v>
+        <v>158</v>
       </c>
       <c r="L18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M18" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="N18" t="s">
-        <v>22</v>
+        <v>160</v>
       </c>
       <c r="O18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q18" t="s">
-        <v>229</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="B19" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="C19" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="D19" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="E19" t="s">
-        <v>151</v>
+        <v>21</v>
       </c>
       <c r="F19" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="G19" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="H19" t="s">
-        <v>24</v>
+        <v>165</v>
       </c>
       <c r="I19" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="J19" t="s">
-        <v>153</v>
+        <v>230</v>
       </c>
       <c r="K19" t="s">
-        <v>208</v>
+        <v>167</v>
       </c>
       <c r="L19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M19" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="N19" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="O19" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="P19" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="Q19" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="B20" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="C20" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="D20" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="E20" t="s">
-        <v>162</v>
+        <v>21</v>
       </c>
       <c r="F20" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="G20" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="H20" t="s">
+        <v>21</v>
+      </c>
+      <c r="I20" t="s">
         <v>24</v>
       </c>
-      <c r="I20" t="s">
-        <v>22</v>
-      </c>
       <c r="J20" t="s">
-        <v>25</v>
+        <v>231</v>
       </c>
       <c r="K20" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="L20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M20" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="N20" t="s">
-        <v>22</v>
+        <v>179</v>
       </c>
       <c r="O20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q20" t="s">
-        <v>231</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="B21" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="C21" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="D21" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="E21" t="s">
-        <v>168</v>
+        <v>21</v>
       </c>
       <c r="F21" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="G21" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="H21" t="s">
-        <v>24</v>
+        <v>184</v>
       </c>
       <c r="I21" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="J21" t="s">
-        <v>170</v>
+        <v>232</v>
       </c>
       <c r="K21" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="L21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M21" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="N21" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="O21" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="P21" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="Q21" t="s">
-        <v>232</v>
+        <v>191</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="B22" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="C22" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="D22" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="E22" t="s">
-        <v>179</v>
+        <v>21</v>
       </c>
       <c r="F22" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="G22" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="H22" t="s">
+        <v>21</v>
+      </c>
+      <c r="I22" t="s">
         <v>24</v>
       </c>
-      <c r="I22" t="s">
-        <v>22</v>
-      </c>
       <c r="J22" t="s">
-        <v>25</v>
+        <v>233</v>
       </c>
       <c r="K22" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="L22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M22" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="N22" t="s">
-        <v>22</v>
+        <v>198</v>
       </c>
       <c r="O22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q22" t="s">
-        <v>233</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="B23" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="C23" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="D23" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="E23" t="s">
-        <v>185</v>
+        <v>21</v>
       </c>
       <c r="F23" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="G23" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="H23" t="s">
+        <v>21</v>
+      </c>
+      <c r="I23" t="s">
         <v>24</v>
       </c>
-      <c r="I23" t="s">
-        <v>22</v>
-      </c>
       <c r="J23" t="s">
-        <v>25</v>
+        <v>234</v>
       </c>
       <c r="K23" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="L23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M23" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="N23" t="s">
-        <v>22</v>
+        <v>205</v>
       </c>
       <c r="O23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q23" t="s">
-        <v>234</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="B24" t="s">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="C24" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="D24" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="E24" t="s">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="F24" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="G24" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="H24" t="s">
+        <v>21</v>
+      </c>
+      <c r="I24" t="s">
         <v>24</v>
       </c>
-      <c r="I24" t="s">
-        <v>22</v>
-      </c>
       <c r="J24" t="s">
-        <v>25</v>
+        <v>235</v>
       </c>
       <c r="K24" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="L24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M24" t="s">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="N24" t="s">
-        <v>22</v>
+        <v>212</v>
       </c>
       <c r="O24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q24" t="s">
-        <v>235</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/DesignData/Excel_Masters/CharacterAssets_Master.xlsx
+++ b/DesignData/Excel_Masters/CharacterAssets_Master.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Documents\FinalGit\ProjectParadise\DesignData\Excel_Masters\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12285"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="28995" windowHeight="15675"/>
   </bookViews>
   <sheets>
     <sheet name="CharacterAssets" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="325">
   <si>
     <t>---</t>
   </si>
@@ -93,9 +93,6 @@
     <t>(AbilityClass=None,EffectClass=None,ProjectileClass=None)</t>
   </si>
   <si>
-    <t>()</t>
-  </si>
-  <si>
     <t>(TagName="FX.Character.Anubis.Ultimate")</t>
   </si>
   <si>
@@ -126,12 +123,6 @@
     <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_AreaUltimate.GA_AreaUltimate_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Buff_AttackPowerUp.GE_Buff_AttackPowerUp_C'",ProjectileClass=None)</t>
   </si>
   <si>
-    <t>/Game/Blueprints/Characters/Player/Army/AM_Army_Ultimate_Attack.AM_Army_Ultimate_Attack</t>
-  </si>
-  <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Army/AM_Army_Book_Attack.AM_Army_Book_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Army/AM_Army_Book_Skill.AM_Army_Book_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Army/AM_Army_Melee_Attack.AM_Army_Melee_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Army/AM_Army_Melee_Attack.AM_Army_Melee_Attack")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Army/AM_Army_Gun_Attack.AM_Army_Gun_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Army/AM_Army_Gun_Attack.AM_Army_Gun_Attack")))</t>
-  </si>
-  <si>
     <t>(TagName="FX.Character.Army.Ultimate")</t>
   </si>
   <si>
@@ -141,15 +132,6 @@
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Army.Icon_Army</t>
   </si>
   <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Player/Army/ABP_Base_Army.ABP_Base_Army_C'</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Player/Army/AM_Army_Damage.AM_Army_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Player/Army/AM_Army_Dead.AM_Army_Dead</t>
-  </si>
-  <si>
     <t>Char_Bard</t>
   </si>
   <si>
@@ -297,12 +279,6 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Hermit/Ani/Hermit_Base_Battle_Idle_Anim_Hermit_Battle_Idle.Hermit_Base_Battle_Idle_Anim_Hermit_Battle_Idle</t>
   </si>
   <si>
-    <t>/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Ultimate_Attack.AM_Hermit_Ultimate_Attack</t>
-  </si>
-  <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Book_Attack.AM_Hermit_Book_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Book_Attack.AM_Hermit_Book_Attack")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Melee_Attack.AM_Hermit_Melee_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Melee_Attack.AM_Hermit_Melee_Attack")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Gun_Attack.AM_Hermit_Gun_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Gun_Attack.AM_Hermit_Gun_Attack")))</t>
-  </si>
-  <si>
     <t>(TagName="FX.Character.Hermit.Ultimate")</t>
   </si>
   <si>
@@ -312,15 +288,6 @@
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Hermit.Icon_Hermit</t>
   </si>
   <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Player/Hermit/ABP_Base_Hermit.ABP_Base_Hermit_C'</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Damage.AM_Hermit_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Player/Hermit/AM_Hermit_Dead.AM_Hermit_Dead</t>
-  </si>
-  <si>
     <t>Char_Hornet</t>
   </si>
   <si>
@@ -333,12 +300,6 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Hornet/Ani/Hornet_Base_Battle_Idle.Hornet_Base_Battle_Idle</t>
   </si>
   <si>
-    <t>/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Ultimate.AM_Hornet_Ultimate</t>
-  </si>
-  <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Book_Attack.AM_Hornet_Book_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Book_Attack.AM_Hornet_Book_Attack")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Melee_Attack.AM_Hornet_Melee_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Melee_Attack.AM_Hornet_Melee_Attack")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Gun_Attack.AM_Hornet_Gun_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Gun_Attack.AM_Hornet_Gun_Attack")))</t>
-  </si>
-  <si>
     <t>(TagName="FX.Character.Hornet.Ultimate")</t>
   </si>
   <si>
@@ -348,15 +309,6 @@
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Hornet.Icon_Hornet</t>
   </si>
   <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Player/Hornet/ABP_Base_Hornet.ABP_Base_Hornet_C'</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Damage.AM_Hornet_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Player/Hornet/AM_Hornet_Dead.AM_Hornet_Dead</t>
-  </si>
-  <si>
     <t>Char_Looter</t>
   </si>
   <si>
@@ -516,12 +468,6 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Pioneer/Ani/Pioneer_Base_Battle_Idle.Pioneer_Base_Battle_Idle</t>
   </si>
   <si>
-    <t>/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Ultimate.AM_Pioneer_Ultimate</t>
-  </si>
-  <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Book_Attack.AM_Pioneer_Book_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Book_Attack.AM_Pioneer_Book_Attack")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Sword_Attack.AM_Pioneer_Sword_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Sword_Attack.AM_Pioneer_Sword_Attack")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Gun_Attack.AM_Pioneer_Gun_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Gun_Attack.AM_Pioneer_Gun_Attack")))</t>
-  </si>
-  <si>
     <t>(TagName="FX.Character.Pioneer.Ultimate")</t>
   </si>
   <si>
@@ -531,15 +477,6 @@
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Pioneer.Icon_Pioneer</t>
   </si>
   <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Player/Pioneer/ABP_Pioneer.ABP_Pioneer_C'</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Damage.AM_Pioneer_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Player/Pioneer/AM_Pioneer_Dead.AM_Pioneer_Dead</t>
-  </si>
-  <si>
     <t>Char_Rogue</t>
   </si>
   <si>
@@ -573,12 +510,6 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Tinker/Ani/Tinker_Base_Battle_Idle_Anim_Tinker_Base_Battle_Idle.Tinker_Base_Battle_Idle_Anim_Tinker_Base_Battle_Idle</t>
   </si>
   <si>
-    <t>/Game/Blueprints/Characters/Player/Tinker/AM_Ultimate_Attack.AM_Ultimate_Attack</t>
-  </si>
-  <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Tinker/AM_Book_Attack.AM_Book_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Tinker/AM_Book_Attack.AM_Book_Attack")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Tinker/AM_Melee_Attack.AM_Melee_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Tinker/AM_Melee_Blunt_Attack.AM_Melee_Blunt_Attack")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Player/Tinker/AM_Gun_Attack.AM_Gun_Attack",SkillMontage="/Game/Blueprints/Characters/Player/Tinker/AM_Gun_Attack.AM_Gun_Attack")))</t>
-  </si>
-  <si>
     <t>(TagName="FX.Character.Tinker.Ultimate")</t>
   </si>
   <si>
@@ -586,15 +517,6 @@
   </si>
   <si>
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Tinker.Icon_Tinker</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Player/Tinker/ABP_Base.ABP_Base_C'</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Player/Tinker/AM_Damage.AM_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Player/Tinker/AM_Dead.AM_Dead</t>
   </si>
   <si>
     <t>Char_Tuner</t>
@@ -728,6 +650,352 @@
   </si>
   <si>
     <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Writer.DA_CharFX_Writer",BasicAttackTag=(TagName="FX.Character.Writer.BasicAttack"),SkillTag=(TagName="FX.Character.Writer.WeaponSkill"),UltimateTag=(TagName="FX.Character.Writer.Ultimate"),HitTag=(TagName="FX.Character.Writer.Hit"),DeathTag=(TagName="FX.Character.Writer.Death"))</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Ultimate.AM_Anubis_Ultimate</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Ultimate.AM_Army_Ultimate</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Ultimate.AM_Bard_Ultimate</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Ultimate.AM_Binder_Ultimate</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Ultimate.AM_Courier_Ultimate</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Ultimate.AM_Demonia_Ultimate</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Ultimate.AM_Enchanter_Ultimate</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Ultimate.AM_Guard_Ultimate</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Ultimate.AM_Hermit_Ultimate</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Ultimate.AM_Hornet_Ultimate</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Ultimate.AM_Looter_Ultimate</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Ultimate.AM_Maid_Ultimate</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Ultimate.AM_Merry_Ultimate</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Ultimate.AM_Muzzle_Ultimate</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Ultimate.AM_Noble_Ultimate</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Ultimate.AM_Nurse_Ultimate</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Ultimate.AM_Outsider_Ultimate</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Ultimate.AM_Pioneer_Ultimate</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Ultimate.AM_Rogue_Ultimate</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Ultimate.AM_Tinker_Ultimate</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Ultimate.AM_Tuner_Ultimate</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Ultimate.AM_Weaver_Ultimate</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Ultimate.AM_Writer_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Book.AM_Anubis_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Book_Skill.AM_Anubis_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Gun.AM_Anubis_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Gun_Skill.AM_Anubis_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Melee.AM_Anubis_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Melee_Skill.AM_Anubis_Melee_Skill")))</t>
+  </si>
+  <si>
+    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Book.AM_Army_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Book_Skill.AM_Army_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Gun.AM_Army_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Gun_Skill.AM_Army_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Melee.AM_Army_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Melee_Skill.AM_Army_Melee_Skill")))</t>
+  </si>
+  <si>
+    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Book.AM_Bard_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Book_Skill.AM_Bard_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Gun.AM_Bard_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Gun_Skill.AM_Bard_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Melee.AM_Bard_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Melee_Skill.AM_Bard_Melee_Skill")))</t>
+  </si>
+  <si>
+    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Book.AM_Binder_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Book_Skill.AM_Binder_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Gun.AM_Binder_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Gun_Skill.AM_Binder_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Melee.AM_Binder_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Melee_Skill.AM_Binder_Melee_Skill")))</t>
+  </si>
+  <si>
+    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Book.AM_Courier_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Book_Skill.AM_Courier_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Gun.AM_Courier_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Gun_Skill.AM_Courier_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Melee.AM_Courier_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Melee_Skill.AM_Courier_Melee_Skill")))</t>
+  </si>
+  <si>
+    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Book.AM_Demonia_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Book_Skill.AM_Demonia_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Gun.AM_Demonia_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Gun_Skill.AM_Demonia_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Melee.AM_Demonia_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Melee_Skill.AM_Demonia_Melee_Skill")))</t>
+  </si>
+  <si>
+    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Book.AM_Enchanter_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Book_Skill.AM_Enchanter_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Gun.AM_Enchanter_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Gun_Skill.AM_Enchanter_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Melee.AM_Enchanter_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Melee_Skill.AM_Enchanter_Melee_Skill")))</t>
+  </si>
+  <si>
+    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Book.AM_Guard_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Book_Skill.AM_Guard_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Gun.AM_Guard_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Gun_Skill.AM_Guard_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Melee.AM_Guard_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Melee_Skill.AM_Guard_Melee_Skill")))</t>
+  </si>
+  <si>
+    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Book.AM_Hermit_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Book_Skill.AM_Hermit_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Gun.AM_Hermit_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Gun_Skill.AM_Hermit_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Melee.AM_Hermit_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Melee_Skill.AM_Hermit_Melee_Skill")))</t>
+  </si>
+  <si>
+    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Book.AM_Hornet_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Book_Skill.AM_Hornet_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Gun.AM_Hornet_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Gun_Skill.AM_Hornet_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Melee.AM_Hornet_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Melee_Skill.AM_Hornet_Melee_Skill")))</t>
+  </si>
+  <si>
+    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Book.AM_Looter_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Book_Skill.AM_Looter_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Gun.AM_Looter_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Gun_Skill.AM_Looter_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Melee.AM_Looter_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Melee_Skill.AM_Looter_Melee_Skill")))</t>
+  </si>
+  <si>
+    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Book.AM_Maid_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Book_Skill.AM_Maid_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Gun.AM_Maid_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Gun_Skill.AM_Maid_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Melee.AM_Maid_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Melee_Skill.AM_Maid_Melee_Skill")))</t>
+  </si>
+  <si>
+    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Book.AM_Merry_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Book_Skill.AM_Merry_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Gun.AM_Merry_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Gun_Skill.AM_Merry_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Melee.AM_Merry_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Melee_Skill.AM_Merry_Melee_Skill")))</t>
+  </si>
+  <si>
+    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Book.AM_Muzzle_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Book_Skill.AM_Muzzle_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Gun.AM_Muzzle_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Gun_Skill.AM_Muzzle_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Melee.AM_Muzzle_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Melee_Skill.AM_Muzzle_Melee_Skill")))</t>
+  </si>
+  <si>
+    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Book.AM_Noble_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Book_Skill.AM_Noble_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Gun.AM_Noble_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Gun_Skill.AM_Noble_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Melee.AM_Noble_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Melee_Skill.AM_Noble_Melee_Skill")))</t>
+  </si>
+  <si>
+    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Book.AM_Nurse_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Book_Skill.AM_Nurse_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Gun.AM_Nurse_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Gun_Skill.AM_Nurse_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Melee.AM_Nurse_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Melee_Skill.AM_Nurse_Melee_Skill")))</t>
+  </si>
+  <si>
+    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Book.AM_Outsider_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Book_Skill.AM_Outsider_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Gun.AM_Outsider_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Gun_Skill.AM_Outsider_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Melee.AM_Outsider_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Melee_Skill.AM_Outsider_Melee_Skill")))</t>
+  </si>
+  <si>
+    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Book.AM_Pioneer_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Book_Skill.AM_Pioneer_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Gun.AM_Pioneer_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Gun_Skill.AM_Pioneer_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Melee.AM_Pioneer_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Melee_Skill.AM_Pioneer_Melee_Skill")))</t>
+  </si>
+  <si>
+    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Book.AM_Rogue_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Book_Skill.AM_Rogue_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Gun.AM_Rogue_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Gun_Skill.AM_Rogue_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Melee.AM_Rogue_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Melee_Skill.AM_Rogue_Melee_Skill")))</t>
+  </si>
+  <si>
+    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Book.AM_Tinker_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Book_Skill.AM_Tinker_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Gun.AM_Tinker_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Gun_Skill.AM_Tinker_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Melee.AM_Tinker_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Melee_Skill.AM_Tinker_Melee_Skill")))</t>
+  </si>
+  <si>
+    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Book.AM_Tuner_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Book_Skill.AM_Tuner_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Gun.AM_Tuner_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Gun_Skill.AM_Tuner_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Melee.AM_Tuner_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Melee_Skill.AM_Tuner_Melee_Skill")))</t>
+  </si>
+  <si>
+    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Book.AM_Weaver_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Book_Skill.AM_Weaver_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Gun.AM_Weaver_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Gun_Skill.AM_Weaver_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Melee.AM_Weaver_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Melee_Skill.AM_Weaver_Melee_Skill")))</t>
+  </si>
+  <si>
+    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Book.AM_Writer_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Book_Skill.AM_Writer_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Gun.AM_Writer_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Gun_Skill.AM_Writer_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Melee.AM_Writer_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Melee_Skill.AM_Writer_Melee_Skill")))</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Anubis/ABP_Anubis.ABP_Anubis_C</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Army/ABP_Army.ABP_Army_C</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Bard/ABP_Bard.ABP_Bard_C</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Binder/ABP_Binder.ABP_Binder_C</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Courier/ABP_Courier.ABP_Courier_C</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Demonia/ABP_Demonia.ABP_Demonia_C</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Enchanter/ABP_Enchanter.ABP_Enchanter_C</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Guard/ABP_Guard.ABP_Guard_C</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Hermit/ABP_Hermit.ABP_Hermit_C</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Hornet/ABP_Hornet.ABP_Hornet_C</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Looter/ABP_Looter.ABP_Looter_C</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Maid/ABP_Maid.ABP_Maid_C</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Merry/ABP_Merry.ABP_Merry_C</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Muzzle/ABP_Muzzle.ABP_Muzzle_C</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Noble/ABP_Noble.ABP_Noble_C</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Nurse/ABP_Nurse.ABP_Nurse_C</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Outsider/ABP_Outsider.ABP_Outsider_C</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Pioneer/ABP_Pioneer.ABP_Pioneer_C</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Rogue/ABP_Rogue.ABP_Rogue_C</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Tinker/ABP_Tinker.ABP_Tinker_C</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Tuner/ABP_Tuner.ABP_Tuner_C</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Weaver/ABP_Weaver.ABP_Weaver_C</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Writer/ABP_Writer.ABP_Writer_C</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Damage.AM_Anubis_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Damage.AM_Army_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Damage.AM_Bard_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Damage.AM_Binder_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Damage.AM_Courier_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Damage.AM_Demonia_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Damage.AM_Enchanter_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Damage.AM_Guard_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Damage.AM_Hermit_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Damage.AM_Hornet_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Damage.AM_Looter_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Damage.AM_Maid_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Damage.AM_Merry_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Damage.AM_Muzzle_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Damage.AM_Noble_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Damage.AM_Nurse_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Damage.AM_Outsider_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Damage.AM_Pioneer_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Damage.AM_Rogue_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Damage.AM_Tinker_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Damage.AM_Tuner_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Damage.AM_Weaver_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Damage.AM_Writer_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Dead.AM_Army_Dead</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Dead.AM_Bard_Dead</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Dead.AM_Binder_Dead</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Dead.AM_Courier_Dead</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Dead.AM_Demonia_Dead</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Dead.AM_Enchanter_Dead</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Dead.AM_Guard_Dead</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Dead.AM_Hermit_Dead</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Dead.AM_Hornet_Dead</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Dead.AM_Looter_Dead</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Dead.AM_Maid_Dead</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Dead.AM_Merry_Dead</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Dead.AM_Muzzle_Dead</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Dead.AM_Noble_Dead</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Dead.AM_Nurse_Dead</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Dead.AM_Outsider_Dead</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Dead.AM_Pioneer_Dead</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Dead.AM_Rogue_Dead</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Dead.AM_Tinker_Dead</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Dead.AM_Tuner_Dead</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Dead.AM_Weaver_Dead</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Dead.AM_Writer_Dead</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Dead.AM_Anubis_Dead</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1724,260 +1992,260 @@
         <v>23</v>
       </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>210</v>
       </c>
       <c r="I2" t="s">
+        <v>233</v>
+      </c>
+      <c r="J2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K2" t="s">
         <v>24</v>
       </c>
-      <c r="J2" t="s">
-        <v>213</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>25</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>26</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>27</v>
       </c>
-      <c r="N2" t="s">
-        <v>28</v>
-      </c>
       <c r="O2" t="s">
-        <v>21</v>
+        <v>256</v>
       </c>
       <c r="P2" t="s">
-        <v>21</v>
+        <v>279</v>
       </c>
       <c r="Q2" t="s">
-        <v>21</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" t="s">
         <v>29</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>30</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>31</v>
-      </c>
-      <c r="D3" t="s">
-        <v>32</v>
       </c>
       <c r="E3" t="s">
         <v>21</v>
       </c>
       <c r="F3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" t="s">
         <v>33</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
+        <v>211</v>
+      </c>
+      <c r="I3" t="s">
+        <v>234</v>
+      </c>
+      <c r="J3" t="s">
+        <v>188</v>
+      </c>
+      <c r="K3" t="s">
         <v>34</v>
       </c>
-      <c r="H3" t="s">
+      <c r="L3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" t="s">
         <v>35</v>
       </c>
-      <c r="I3" t="s">
+      <c r="N3" t="s">
         <v>36</v>
       </c>
-      <c r="J3" t="s">
-        <v>214</v>
-      </c>
-      <c r="K3" t="s">
-        <v>37</v>
-      </c>
-      <c r="L3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N3" t="s">
-        <v>39</v>
-      </c>
       <c r="O3" t="s">
-        <v>40</v>
+        <v>257</v>
       </c>
       <c r="P3" t="s">
-        <v>41</v>
+        <v>280</v>
       </c>
       <c r="Q3" t="s">
-        <v>42</v>
+        <v>302</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
         <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G4" t="s">
         <v>23</v>
       </c>
       <c r="H4" t="s">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="I4" t="s">
-        <v>24</v>
+        <v>235</v>
       </c>
       <c r="J4" t="s">
-        <v>215</v>
+        <v>189</v>
       </c>
       <c r="K4" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="L4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M4" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="N4" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="O4" t="s">
-        <v>21</v>
+        <v>258</v>
       </c>
       <c r="P4" t="s">
-        <v>21</v>
+        <v>281</v>
       </c>
       <c r="Q4" t="s">
-        <v>21</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E5" t="s">
         <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="G5" t="s">
         <v>23</v>
       </c>
       <c r="H5" t="s">
-        <v>21</v>
+        <v>213</v>
       </c>
       <c r="I5" t="s">
-        <v>24</v>
+        <v>236</v>
       </c>
       <c r="J5" t="s">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="K5" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="L5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M5" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="N5" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="O5" t="s">
-        <v>21</v>
+        <v>259</v>
       </c>
       <c r="P5" t="s">
-        <v>21</v>
+        <v>282</v>
       </c>
       <c r="Q5" t="s">
-        <v>21</v>
+        <v>304</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
         <v>21</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G6" t="s">
         <v>23</v>
       </c>
       <c r="H6" t="s">
-        <v>21</v>
+        <v>214</v>
       </c>
       <c r="I6" t="s">
-        <v>24</v>
+        <v>237</v>
       </c>
       <c r="J6" t="s">
-        <v>217</v>
+        <v>191</v>
       </c>
       <c r="K6" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="L6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M6" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="N6" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="O6" t="s">
-        <v>21</v>
+        <v>260</v>
       </c>
       <c r="P6" t="s">
-        <v>21</v>
+        <v>283</v>
       </c>
       <c r="Q6" t="s">
-        <v>21</v>
+        <v>305</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E7" t="s">
         <v>21</v>
@@ -1989,472 +2257,472 @@
         <v>23</v>
       </c>
       <c r="H7" t="s">
-        <v>21</v>
+        <v>215</v>
       </c>
       <c r="I7" t="s">
-        <v>24</v>
+        <v>238</v>
       </c>
       <c r="J7" t="s">
-        <v>218</v>
+        <v>192</v>
       </c>
       <c r="K7" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="L7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M7" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="N7" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O7" t="s">
-        <v>21</v>
+        <v>261</v>
       </c>
       <c r="P7" t="s">
-        <v>21</v>
+        <v>284</v>
       </c>
       <c r="Q7" t="s">
-        <v>21</v>
+        <v>306</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D8" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E8" t="s">
         <v>21</v>
       </c>
       <c r="F8" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G8" t="s">
         <v>23</v>
       </c>
       <c r="H8" t="s">
-        <v>21</v>
+        <v>216</v>
       </c>
       <c r="I8" t="s">
-        <v>24</v>
+        <v>239</v>
       </c>
       <c r="J8" t="s">
-        <v>219</v>
+        <v>193</v>
       </c>
       <c r="K8" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="L8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M8" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="N8" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="O8" t="s">
-        <v>21</v>
+        <v>262</v>
       </c>
       <c r="P8" t="s">
-        <v>21</v>
+        <v>285</v>
       </c>
       <c r="Q8" t="s">
-        <v>21</v>
+        <v>307</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E9" t="s">
         <v>21</v>
       </c>
       <c r="F9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G9" t="s">
         <v>23</v>
       </c>
       <c r="H9" t="s">
-        <v>21</v>
+        <v>217</v>
       </c>
       <c r="I9" t="s">
-        <v>24</v>
+        <v>240</v>
       </c>
       <c r="J9" t="s">
-        <v>220</v>
+        <v>194</v>
       </c>
       <c r="K9" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="L9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M9" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="N9" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="O9" t="s">
-        <v>21</v>
+        <v>263</v>
       </c>
       <c r="P9" t="s">
-        <v>21</v>
+        <v>286</v>
       </c>
       <c r="Q9" t="s">
-        <v>21</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E10" t="s">
         <v>21</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="G10" t="s">
         <v>23</v>
       </c>
       <c r="H10" t="s">
-        <v>92</v>
+        <v>218</v>
       </c>
       <c r="I10" t="s">
-        <v>93</v>
+        <v>241</v>
       </c>
       <c r="J10" t="s">
-        <v>221</v>
+        <v>195</v>
       </c>
       <c r="K10" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="L10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M10" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="N10" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="O10" t="s">
-        <v>97</v>
+        <v>264</v>
       </c>
       <c r="P10" t="s">
-        <v>98</v>
+        <v>287</v>
       </c>
       <c r="Q10" t="s">
-        <v>99</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="B11" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="D11" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E11" t="s">
         <v>21</v>
       </c>
       <c r="F11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G11" t="s">
         <v>23</v>
       </c>
       <c r="H11" t="s">
-        <v>104</v>
+        <v>219</v>
       </c>
       <c r="I11" t="s">
-        <v>105</v>
+        <v>242</v>
       </c>
       <c r="J11" t="s">
-        <v>222</v>
+        <v>196</v>
       </c>
       <c r="K11" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="L11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M11" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="N11" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="O11" t="s">
-        <v>109</v>
+        <v>265</v>
       </c>
       <c r="P11" t="s">
-        <v>110</v>
+        <v>288</v>
       </c>
       <c r="Q11" t="s">
-        <v>111</v>
+        <v>310</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="B12" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="C12" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="D12" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="E12" t="s">
         <v>21</v>
       </c>
       <c r="F12" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G12" t="s">
         <v>23</v>
       </c>
       <c r="H12" t="s">
-        <v>21</v>
+        <v>220</v>
       </c>
       <c r="I12" t="s">
-        <v>24</v>
+        <v>243</v>
       </c>
       <c r="J12" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="K12" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="L12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M12" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="N12" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="O12" t="s">
-        <v>21</v>
+        <v>266</v>
       </c>
       <c r="P12" t="s">
-        <v>21</v>
+        <v>289</v>
       </c>
       <c r="Q12" t="s">
-        <v>21</v>
+        <v>311</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="B13" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="C13" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="D13" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="E13" t="s">
         <v>21</v>
       </c>
       <c r="F13" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="G13" t="s">
         <v>23</v>
       </c>
       <c r="H13" t="s">
-        <v>21</v>
+        <v>221</v>
       </c>
       <c r="I13" t="s">
-        <v>24</v>
+        <v>244</v>
       </c>
       <c r="J13" t="s">
-        <v>224</v>
+        <v>198</v>
       </c>
       <c r="K13" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="L13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M13" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="N13" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="O13" t="s">
-        <v>21</v>
+        <v>267</v>
       </c>
       <c r="P13" t="s">
-        <v>21</v>
+        <v>290</v>
       </c>
       <c r="Q13" t="s">
-        <v>21</v>
+        <v>312</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="B14" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="C14" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="D14" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="E14" t="s">
         <v>21</v>
       </c>
       <c r="F14" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G14" t="s">
         <v>23</v>
       </c>
       <c r="H14" t="s">
-        <v>21</v>
+        <v>222</v>
       </c>
       <c r="I14" t="s">
-        <v>24</v>
+        <v>245</v>
       </c>
       <c r="J14" t="s">
-        <v>225</v>
+        <v>199</v>
       </c>
       <c r="K14" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="L14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M14" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="N14" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="O14" t="s">
-        <v>21</v>
+        <v>268</v>
       </c>
       <c r="P14" t="s">
-        <v>21</v>
+        <v>291</v>
       </c>
       <c r="Q14" t="s">
-        <v>21</v>
+        <v>313</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="B15" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="C15" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="D15" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="E15" t="s">
         <v>21</v>
       </c>
       <c r="F15" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G15" t="s">
         <v>23</v>
       </c>
       <c r="H15" t="s">
-        <v>21</v>
+        <v>223</v>
       </c>
       <c r="I15" t="s">
-        <v>24</v>
+        <v>246</v>
       </c>
       <c r="J15" t="s">
-        <v>226</v>
+        <v>200</v>
       </c>
       <c r="K15" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="L15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M15" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="N15" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="O15" t="s">
-        <v>21</v>
+        <v>269</v>
       </c>
       <c r="P15" t="s">
-        <v>21</v>
+        <v>292</v>
       </c>
       <c r="Q15" t="s">
-        <v>21</v>
+        <v>314</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="B16" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="C16" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="D16" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="E16" t="s">
         <v>21</v>
@@ -2466,458 +2734,458 @@
         <v>23</v>
       </c>
       <c r="H16" t="s">
-        <v>21</v>
+        <v>224</v>
       </c>
       <c r="I16" t="s">
-        <v>24</v>
+        <v>247</v>
       </c>
       <c r="J16" t="s">
-        <v>227</v>
+        <v>201</v>
       </c>
       <c r="K16" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="L16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M16" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="N16" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="O16" t="s">
-        <v>21</v>
+        <v>270</v>
       </c>
       <c r="P16" t="s">
-        <v>21</v>
+        <v>293</v>
       </c>
       <c r="Q16" t="s">
-        <v>21</v>
+        <v>315</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="B17" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="C17" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="D17" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="E17" t="s">
         <v>21</v>
       </c>
       <c r="F17" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G17" t="s">
         <v>23</v>
       </c>
       <c r="H17" t="s">
-        <v>21</v>
+        <v>225</v>
       </c>
       <c r="I17" t="s">
-        <v>24</v>
+        <v>248</v>
       </c>
       <c r="J17" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="K17" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="L17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M17" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="N17" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="O17" t="s">
-        <v>21</v>
+        <v>271</v>
       </c>
       <c r="P17" t="s">
-        <v>21</v>
+        <v>294</v>
       </c>
       <c r="Q17" t="s">
-        <v>21</v>
+        <v>316</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="B18" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="C18" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D18" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="E18" t="s">
         <v>21</v>
       </c>
       <c r="F18" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="G18" t="s">
         <v>23</v>
       </c>
       <c r="H18" t="s">
-        <v>21</v>
+        <v>226</v>
       </c>
       <c r="I18" t="s">
-        <v>24</v>
+        <v>249</v>
       </c>
       <c r="J18" t="s">
-        <v>229</v>
+        <v>203</v>
       </c>
       <c r="K18" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="L18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M18" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="N18" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="O18" t="s">
-        <v>21</v>
+        <v>272</v>
       </c>
       <c r="P18" t="s">
-        <v>21</v>
+        <v>295</v>
       </c>
       <c r="Q18" t="s">
-        <v>21</v>
+        <v>317</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="B19" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="C19" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="D19" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="E19" t="s">
         <v>21</v>
       </c>
       <c r="F19" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G19" t="s">
         <v>23</v>
       </c>
       <c r="H19" t="s">
-        <v>165</v>
+        <v>227</v>
       </c>
       <c r="I19" t="s">
-        <v>166</v>
+        <v>250</v>
       </c>
       <c r="J19" t="s">
-        <v>230</v>
+        <v>204</v>
       </c>
       <c r="K19" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="L19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M19" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="N19" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="O19" t="s">
-        <v>170</v>
+        <v>273</v>
       </c>
       <c r="P19" t="s">
-        <v>171</v>
+        <v>296</v>
       </c>
       <c r="Q19" t="s">
-        <v>172</v>
+        <v>318</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
       <c r="B20" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="C20" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="D20" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="E20" t="s">
         <v>21</v>
       </c>
       <c r="F20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G20" t="s">
         <v>23</v>
       </c>
       <c r="H20" t="s">
-        <v>21</v>
+        <v>228</v>
       </c>
       <c r="I20" t="s">
-        <v>24</v>
+        <v>251</v>
       </c>
       <c r="J20" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
       <c r="K20" t="s">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="L20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M20" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="N20" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="O20" t="s">
-        <v>21</v>
+        <v>274</v>
       </c>
       <c r="P20" t="s">
-        <v>21</v>
+        <v>297</v>
       </c>
       <c r="Q20" t="s">
-        <v>21</v>
+        <v>319</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="B21" t="s">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="C21" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="D21" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="E21" t="s">
         <v>21</v>
       </c>
       <c r="F21" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="G21" t="s">
         <v>23</v>
       </c>
       <c r="H21" t="s">
-        <v>184</v>
+        <v>229</v>
       </c>
       <c r="I21" t="s">
-        <v>185</v>
+        <v>252</v>
       </c>
       <c r="J21" t="s">
-        <v>232</v>
+        <v>206</v>
       </c>
       <c r="K21" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="L21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M21" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="N21" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="O21" t="s">
-        <v>189</v>
+        <v>275</v>
       </c>
       <c r="P21" t="s">
-        <v>190</v>
+        <v>298</v>
       </c>
       <c r="Q21" t="s">
-        <v>191</v>
+        <v>320</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="B22" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="C22" t="s">
-        <v>194</v>
+        <v>168</v>
       </c>
       <c r="D22" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="E22" t="s">
         <v>21</v>
       </c>
       <c r="F22" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G22" t="s">
         <v>23</v>
       </c>
       <c r="H22" t="s">
-        <v>21</v>
+        <v>230</v>
       </c>
       <c r="I22" t="s">
-        <v>24</v>
+        <v>253</v>
       </c>
       <c r="J22" t="s">
-        <v>233</v>
+        <v>207</v>
       </c>
       <c r="K22" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="L22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M22" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="N22" t="s">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="O22" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="P22" t="s">
-        <v>21</v>
+        <v>299</v>
       </c>
       <c r="Q22" t="s">
-        <v>21</v>
+        <v>321</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="B23" t="s">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="C23" t="s">
-        <v>201</v>
+        <v>175</v>
       </c>
       <c r="D23" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="E23" t="s">
         <v>21</v>
       </c>
       <c r="F23" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G23" t="s">
         <v>23</v>
       </c>
       <c r="H23" t="s">
-        <v>21</v>
+        <v>231</v>
       </c>
       <c r="I23" t="s">
-        <v>24</v>
+        <v>254</v>
       </c>
       <c r="J23" t="s">
-        <v>234</v>
+        <v>208</v>
       </c>
       <c r="K23" t="s">
-        <v>203</v>
+        <v>177</v>
       </c>
       <c r="L23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M23" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="N23" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
       <c r="O23" t="s">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="P23" t="s">
-        <v>21</v>
+        <v>300</v>
       </c>
       <c r="Q23" t="s">
-        <v>21</v>
+        <v>322</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>206</v>
+        <v>180</v>
       </c>
       <c r="B24" t="s">
-        <v>207</v>
+        <v>181</v>
       </c>
       <c r="C24" t="s">
-        <v>208</v>
+        <v>182</v>
       </c>
       <c r="D24" t="s">
-        <v>209</v>
+        <v>183</v>
       </c>
       <c r="E24" t="s">
         <v>21</v>
       </c>
       <c r="F24" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G24" t="s">
         <v>23</v>
       </c>
       <c r="H24" t="s">
-        <v>21</v>
+        <v>232</v>
       </c>
       <c r="I24" t="s">
-        <v>24</v>
+        <v>255</v>
       </c>
       <c r="J24" t="s">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="K24" t="s">
-        <v>210</v>
+        <v>184</v>
       </c>
       <c r="L24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M24" t="s">
-        <v>211</v>
+        <v>185</v>
       </c>
       <c r="N24" t="s">
-        <v>212</v>
+        <v>186</v>
       </c>
       <c r="O24" t="s">
-        <v>21</v>
+        <v>278</v>
       </c>
       <c r="P24" t="s">
-        <v>21</v>
+        <v>301</v>
       </c>
       <c r="Q24" t="s">
-        <v>21</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>

--- a/DesignData/Excel_Masters/CharacterAssets_Master.xlsx
+++ b/DesignData/Excel_Masters/CharacterAssets_Master.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Documents\FinalGit\ProjectParadise\DesignData\Excel_Masters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="28995" windowHeight="15675"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22065" windowHeight="10050"/>
   </bookViews>
   <sheets>
     <sheet name="CharacterAssets" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="324">
   <si>
     <t>---</t>
   </si>
@@ -93,6 +93,15 @@
     <t>(AbilityClass=None,EffectClass=None,ProjectileClass=None)</t>
   </si>
   <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Ultimate.AM_Anubis_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Book.AM_Anubis_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Book_Skill.AM_Anubis_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Gun.AM_Anubis_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Gun_Skill.AM_Anubis_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Melee.AM_Anubis_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Melee_Skill.AM_Anubis_Melee_Skill")))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Anubis.DA_CharFX_Anubis",BasicAttackTag=(TagName="FX.Character.Anubis.BasicAttack"),SkillTag=(TagName="FX.Character.Anubis.WeaponSkill"),UltimateTag=(TagName="FX.Character.Anubis.Ultimate"),UltimateHitTag=(TagName="FX.Character.Anubis.UltimateHit"),HitTag=(TagName="FX.Character.Anubis.Hit"),DeathTag=(TagName="FX.Character.Anubis.Death"))</t>
+  </si>
+  <si>
     <t>(TagName="FX.Character.Anubis.Ultimate")</t>
   </si>
   <si>
@@ -105,6 +114,15 @@
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Anubis.Icon_Anubis</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Anubis/ABP_Anubis.ABP_Anubis_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Damage.AM_Anubis_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Dead.AM_Anubis_Dead</t>
+  </si>
+  <si>
     <t>Char_Army</t>
   </si>
   <si>
@@ -120,7 +138,16 @@
     <t>Common</t>
   </si>
   <si>
-    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_AreaUltimate.GA_AreaUltimate_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Buff_AttackPowerUp.GE_Buff_AttackPowerUp_C'",ProjectileClass=None)</t>
+    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_AreaUltimate.GA_AreaUltimate_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Heal_Ultimate.GE_Heal_Ultimate_C'",ProjectileClass=None)</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Ultimate.AM_Army_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Book.AM_Army_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Book_SKill.AM_Army_Book_SKill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Gun.AM_Army_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Gun_Skill.AM_Army_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Melee.AM_Army_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Melee_Skill.AM_Army_Melee_Skill")))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Army.DA_CharFX_Army",BasicAttackTag=(TagName="FX.Character.Army.BasicAttack"),SkillTag=(TagName="FX.Character.Army.WeaponSkill"),UltimateTag=(TagName="FX.Character.Army.Ultimate"),UltimateHitTag=(TagName="FX.Character.Army.UltimateHit"),HitTag=(TagName="FX.Character.Army.Hit"),DeathTag=(TagName="FX.Character.Army.Death"))</t>
   </si>
   <si>
     <t>(TagName="FX.Character.Army.Ultimate")</t>
@@ -132,6 +159,15 @@
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Army.Icon_Army</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Army/ABP_Army.ABP_Army_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Damage.AM_Army_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Dead.AM_Army_Dead</t>
+  </si>
+  <si>
     <t>Char_Bard</t>
   </si>
   <si>
@@ -147,6 +183,12 @@
     <t>Uncommon</t>
   </si>
   <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Ultimate.AM_Bard_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Book.AM_Bard_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Book_Skill.AM_Bard_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Gun.AM_Bard_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Gun_Skill.AM_Bard_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Melee.AM_Bard_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Melee_Skill.AM_Bard_Melee_Skill")))</t>
+  </si>
+  <si>
     <t>(TagName="FX.Character.Bard.Ultimate")</t>
   </si>
   <si>
@@ -156,6 +198,15 @@
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Bard.Icon_Bard</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Bard/ABP_Bard.ABP_Bard_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Damage.AM_Bard_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Dead.AM_Bard_Dead</t>
+  </si>
+  <si>
     <t>Char_Binder</t>
   </si>
   <si>
@@ -171,6 +222,12 @@
     <t>Epic</t>
   </si>
   <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Ultimate.AM_Binder_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Book.AM_Binder_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Book_Skill.AM_Binder_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Gun.AM_Binder_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Gun_Skill.AM_Binder_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Melee.AM_Binder_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Melee_Skill.AM_Binder_Melee_Skill")))</t>
+  </si>
+  <si>
     <t>(TagName="FX.Character.Binder.Ultimate")</t>
   </si>
   <si>
@@ -180,6 +237,15 @@
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Binder.Icon_Binder</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Binder/ABP_BInder.ABP_BInder_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Damage.AM_Binder_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Dead.AM_Binder_Dead</t>
+  </si>
+  <si>
     <t>Char_Courier</t>
   </si>
   <si>
@@ -195,6 +261,12 @@
     <t>Rare</t>
   </si>
   <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Ultimate.AM_Courier_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Book.AM_Courier_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Book_Skill.AM_Courier_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Gun.AM_Courier_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Gun_Skill.AM_Courier_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Melee.AM_Courier_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Melee_Skill.AM_Courier_Melee_Skill")))</t>
+  </si>
+  <si>
     <t>(TagName="FX.Character.Courier.Ultimate")</t>
   </si>
   <si>
@@ -204,6 +276,15 @@
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Courier.Icon_Courier</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Courier/ABP_Courier.ABP_Courier_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Damage.AM_Courier_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Dead.AM_Courier_Dead</t>
+  </si>
+  <si>
     <t>Char_Demonia</t>
   </si>
   <si>
@@ -216,6 +297,12 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Demonia/Ani/Demonia_Base_Battle_Idle.Demonia_Base_Battle_Idle</t>
   </si>
   <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Ultimate.AM_Demonia_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Book.AM_Demonia_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Book_Skill.AM_Demonia_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Gun.AM_Demonia_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Gun_Skill.AM_Demonia_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Melee.AM_Demonia_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Melee_Skill.AM_Demonia_Melee_Skill")))</t>
+  </si>
+  <si>
     <t>(TagName="FX.Character.Demonia.Ultimate")</t>
   </si>
   <si>
@@ -225,6 +312,15 @@
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Demonia.Icon_Demonia</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Demonia/ABP_Demonia.ABP_Demonia_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Damage.AM_Demonia_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Dead.AM_Demonia_Dead</t>
+  </si>
+  <si>
     <t>Char_Enchanter</t>
   </si>
   <si>
@@ -237,6 +333,12 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Enchanter/Ani/Enchanter_Base_Battle_Idle_Anim_Take_001.Enchanter_Base_Battle_Idle_Anim_Take_001</t>
   </si>
   <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Ultimate.AM_Enchanter_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Book.AM_Enchanter_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Book_Skill.AM_Enchanter_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Gun.AM_Enchanter_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Gun_Skill.AM_Enchanter_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Melee.AM_Enchanter_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Melee_Skill.AM_Enchanter_Melee_Skill")))</t>
+  </si>
+  <si>
     <t>(TagName="FX.Character.Enchanter.Ultimate")</t>
   </si>
   <si>
@@ -246,6 +348,15 @@
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Enchanter.Icon_Enchanter</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Enchanter/ABP_Enchanter.ABP_Enchanter_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Damage.AM_Enchanter_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Dead.AM_Enchanter_Dead</t>
+  </si>
+  <si>
     <t>Char_Guard</t>
   </si>
   <si>
@@ -258,6 +369,12 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Guard/Ani/Guard_Base_Battle_Idle.Guard_Base_Battle_Idle</t>
   </si>
   <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Ultimate.AM_Guard_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Book.AM_Guard_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Book_Skill.AM_Guard_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Gun.AM_Guard_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Gun_Skill.AM_Guard_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Melee.AM_Guard_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Melee_Skill.AM_Guard_Melee_Skill")))</t>
+  </si>
+  <si>
     <t>(TagName="FX.Character.Guard.Ultimate")</t>
   </si>
   <si>
@@ -267,6 +384,15 @@
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Guard.Icon_Guard</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Guard/ABP_Guard.ABP_Guard_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Damage.AM_Guard_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Dead.AM_Guard_Dead</t>
+  </si>
+  <si>
     <t>Char_Hermit</t>
   </si>
   <si>
@@ -279,6 +405,12 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Hermit/Ani/Hermit_Base_Battle_Idle_Anim_Hermit_Battle_Idle.Hermit_Base_Battle_Idle_Anim_Hermit_Battle_Idle</t>
   </si>
   <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Ultimate.AM_Hermit_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Book.AM_Hermit_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Book_Skill.AM_Hermit_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Gun.AM_Hermit_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Gun_Skill.AM_Hermit_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Melee.AM_Hermit_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Melee_Skill.AM_Hermit_Melee_Skill")))</t>
+  </si>
+  <si>
     <t>(TagName="FX.Character.Hermit.Ultimate")</t>
   </si>
   <si>
@@ -288,6 +420,15 @@
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Hermit.Icon_Hermit</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Hermit/ABP_Hermit.ABP_Hermit_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Damage.AM_Hermit_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Dead.AM_Hermit_Dead</t>
+  </si>
+  <si>
     <t>Char_Hornet</t>
   </si>
   <si>
@@ -300,6 +441,12 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Hornet/Ani/Hornet_Base_Battle_Idle.Hornet_Base_Battle_Idle</t>
   </si>
   <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Ultimate.AM_Hornet_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Book.AM_Hornet_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Book_Skill.AM_Hornet_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Gun.AM_Hornet_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Gun_Skill.AM_Hornet_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Melee.AM_Hornet_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Melee_Skill.AM_Hornet_Melee_Skill")))</t>
+  </si>
+  <si>
     <t>(TagName="FX.Character.Hornet.Ultimate")</t>
   </si>
   <si>
@@ -309,6 +456,15 @@
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Hornet.Icon_Hornet</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Hornet/ABP_Hornet.ABP_Hornet_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Damage.AM_Hornet_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Dead.AM_Hornet_Dead</t>
+  </si>
+  <si>
     <t>Char_Looter</t>
   </si>
   <si>
@@ -321,6 +477,12 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Looter/Ani/Looter_Base_Battle_Idle.Looter_Base_Battle_Idle</t>
   </si>
   <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Ultimate.AM_Looter_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Book.AM_Looter_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Book_Skill.AM_Looter_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Gun.AM_Looter_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Gun_Skill.AM_Looter_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Melee.AM_Looter_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Melee_Skill.AM_Looter_Melee_Skill")))</t>
+  </si>
+  <si>
     <t>(TagName="FX.Character.Looter.Ultimate")</t>
   </si>
   <si>
@@ -330,6 +492,12 @@
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Looter.Icon_Looter</t>
   </si>
   <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Damage.AM_Looter_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Dead.AM_Looter_Dead</t>
+  </si>
+  <si>
     <t>Char_Maid</t>
   </si>
   <si>
@@ -342,6 +510,12 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Maid/Ani/Maid_Base_Idle_Battle.Maid_Base_Idle_Battle</t>
   </si>
   <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Ultimate.AM_Maid_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Book.AM_Maid_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Book_Skill.AM_Maid_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Gun.AM_Maid_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Gun_Skill.AM_Maid_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Melee.AM_Maid_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Melee_Skill.AM_Maid_Melee_Skill")))</t>
+  </si>
+  <si>
     <t>(TagName="FX.Character.Maid.Ultimate")</t>
   </si>
   <si>
@@ -351,6 +525,15 @@
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Maid.Icon_Maid</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Maid/ABP_Maid.ABP_Maid_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Damage.AM_Maid_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Dead.AM_Maid_Dead</t>
+  </si>
+  <si>
     <t>Char_Merry</t>
   </si>
   <si>
@@ -363,6 +546,12 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Merry/Ani/Merry_Base_Battle_Idle.Merry_Base_Battle_Idle</t>
   </si>
   <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Ultimate.AM_Merry_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Book.AM_Merry_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Book_Skill.AM_Merry_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Gun.AM_Merry_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Gun_Skill.AM_Merry_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Melee.AM_Merry_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Melee_Skill.AM_Merry_Melee_Skill")))</t>
+  </si>
+  <si>
     <t>(TagName="FX.Character.Merry.Ultimate")</t>
   </si>
   <si>
@@ -372,6 +561,15 @@
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Merry.Icon_Merry</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Merry/ABP_Merry.ABP_Merry_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Damage.AM_Merry_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Dead.AM_Merry_Dead</t>
+  </si>
+  <si>
     <t>Char_Muzzle</t>
   </si>
   <si>
@@ -384,6 +582,12 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Muzzle/Ani/Muzzle_Base_Lobby_Idle_NoWeapon.Muzzle_Base_Lobby_Idle_NoWeapon</t>
   </si>
   <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Ultimate.AM_Muzzle_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Book.AM_Muzzle_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Book_Skill.AM_Muzzle_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Gun.AM_Muzzle_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Gun_Skill.AM_Muzzle_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Melee.AM_Muzzle_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Melee_Skill.AM_Muzzle_Melee_Skill")))</t>
+  </si>
+  <si>
     <t>(TagName="FX.Character.Muzzle.Ultimate")</t>
   </si>
   <si>
@@ -393,6 +597,15 @@
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Muzzle.Icon_Muzzle</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Muzzle/ABP_Muzzle.ABP_Muzzle_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Damage.AM_Muzzle_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Dead.AM_Muzzle_Dead</t>
+  </si>
+  <si>
     <t>Char_Noble</t>
   </si>
   <si>
@@ -405,6 +618,12 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Noble/Ani/Noble_Base_Battle_Idle_Anim_Take_0011.Noble_Base_Battle_Idle_Anim_Take_0011</t>
   </si>
   <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Ultimate.AM_Noble_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Book.AM_Noble_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Book_Skill.AM_Noble_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Gun.AM_Noble_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Gun_Skill.AM_Noble_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Melee.AM_Noble_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Melee_Skill.AM_Noble_Melee_Skill")))</t>
+  </si>
+  <si>
     <t>(TagName="FX.Character.Noble.Ultimate")</t>
   </si>
   <si>
@@ -414,6 +633,15 @@
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Noble.Icon_Noble</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Noble/ABP_Noble.ABP_Noble_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Damage.AM_Noble_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Dead.AM_Noble_Dead</t>
+  </si>
+  <si>
     <t>Char_Nurse</t>
   </si>
   <si>
@@ -426,6 +654,12 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Nurse/Ani/Nurse_Base_Battle_Idle.Nurse_Base_Battle_Idle</t>
   </si>
   <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Ultimate.AM_Nurse_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Book.AM_Nurse_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Book_Skill.AM_Nurse_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Gun.AM_Nurse_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Gun_Skill.AM_Nurse_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Melee.AM_Nurse_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Melee_Skill.AM_Nurse_Melee_Skill")))</t>
+  </si>
+  <si>
     <t>(TagName="FX.Character.Nurse.Ultimate")</t>
   </si>
   <si>
@@ -435,6 +669,15 @@
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Nurse.Icon_Nurse</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Nurse/ABP_Nurse.ABP_Nurse_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Damage.AM_Nurse_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Dead.AM_Nurse_Dead</t>
+  </si>
+  <si>
     <t>Char_Outsider</t>
   </si>
   <si>
@@ -447,6 +690,12 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Outsider/Ani/Outsider_Base_Battle_Idle.Outsider_Base_Battle_Idle</t>
   </si>
   <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Ultimate.AM_Outsider_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Book.AM_Outsider_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Book_Skill.AM_Outsider_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Gun.AM_Outsider_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Gun_Skill.AM_Outsider_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Melee.AM_Outsider_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Melee_Skill.AM_Outsider_Melee_Skill")))</t>
+  </si>
+  <si>
     <t>(TagName="FX.Character.Outsider.Ultimate")</t>
   </si>
   <si>
@@ -456,6 +705,15 @@
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Outsider.Icon_Outsider</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/OutSider/ABP_OutSider.ABP_OutSider_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Damage.AM_Outsider_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Dead.AM_Outsider_Dead</t>
+  </si>
+  <si>
     <t>Char_Pioneer</t>
   </si>
   <si>
@@ -468,6 +726,12 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Pioneer/Ani/Pioneer_Base_Battle_Idle.Pioneer_Base_Battle_Idle</t>
   </si>
   <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Ultimate.AM_Pioneer_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Book.AM_Pioneer_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Book_Skill.AM_Pioneer_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Gun.AM_Pioneer_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Gun_Skill.AM_Pioneer_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Melee.AM_Pioneer_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Melee_Skill.AM_Pioneer_Melee_Skill")))</t>
+  </si>
+  <si>
     <t>(TagName="FX.Character.Pioneer.Ultimate")</t>
   </si>
   <si>
@@ -477,6 +741,15 @@
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Pioneer.Icon_Pioneer</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Pioneer/ABP_Pioneer.ABP_Pioneer_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Damage.AM_Pioneer_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Dead.AM_Pioneer_Dead</t>
+  </si>
+  <si>
     <t>Char_Rogue</t>
   </si>
   <si>
@@ -489,6 +762,12 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Rogue/Ani/Rogue_Base_Battle_Idle_Anim_Rogue_Base_Battle_Idle.Rogue_Base_Battle_Idle_Anim_Rogue_Base_Battle_Idle</t>
   </si>
   <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Ultimate.AM_Rogue_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Book.AM_Rogue_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Book_Skill.AM_Rogue_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Gun.AM_Rogue_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Gun_Skill.AM_Rogue_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Melee.AM_Rogue_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Melee_Skill.AM_Rogue_Melee_Skill")))</t>
+  </si>
+  <si>
     <t>(TagName="FX.Character.Rogue.Ultimate")</t>
   </si>
   <si>
@@ -498,6 +777,15 @@
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Rogue.Icon_Rogue</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Rogue/ABP_Rogue.ABP_Rogue_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Damage.AM_Rogue_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Dead.AM_Rogue_Dead</t>
+  </si>
+  <si>
     <t>Char_Tinker</t>
   </si>
   <si>
@@ -510,6 +798,12 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Tinker/Ani/Tinker_Base_Battle_Idle_Anim_Tinker_Base_Battle_Idle.Tinker_Base_Battle_Idle_Anim_Tinker_Base_Battle_Idle</t>
   </si>
   <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Ultimate.AM_Tinker_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Book.AM_Tinker_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Book_Skill.AM_Tinker_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Gun.AM_Tinker_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Gun_Skill.AM_Tinker_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Melee.AM_Tinker_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Melee_Skill.AM_Tinker_Melee_Skill")))</t>
+  </si>
+  <si>
     <t>(TagName="FX.Character.Tinker.Ultimate")</t>
   </si>
   <si>
@@ -519,6 +813,15 @@
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Tinker.Icon_Tinker</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Tinker/ABP_Tinker.ABP_Tinker_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Damage.AM_Tinker_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Dead.AM_Tinker_Dead</t>
+  </si>
+  <si>
     <t>Char_Tuner</t>
   </si>
   <si>
@@ -531,6 +834,12 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Tuner/Ani/Tuner_Base_Battle_Idle.Tuner_Base_Battle_Idle</t>
   </si>
   <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Ultimate.AM_Tuner_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Book.AM_Tuner_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Book_Skill.AM_Tuner_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Gun.AM_Tuner_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Gun_Skill.AM_Tuner_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Melee.AM_Tuner_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Melee_Skill.AM_Tuner_Melee_Skill")))</t>
+  </si>
+  <si>
     <t>(TagName="FX.Character.Tuner.Ultimate")</t>
   </si>
   <si>
@@ -540,6 +849,15 @@
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Tuner.Icon_Tuner</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Tuner/ABP_Tuner.ABP_Tuner_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Damage.AM_Tuner_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Dead.AM_Tuner_Dead</t>
+  </si>
+  <si>
     <t>Char_Weaver</t>
   </si>
   <si>
@@ -552,6 +870,12 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Weaver/Ani/Weaver_Base_Battle_Idle_Anim_Take_001.Weaver_Base_Battle_Idle_Anim_Take_001</t>
   </si>
   <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Ultimate.AM_Weaver_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Book.AM_Weaver_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Book_Skill.AM_Weaver_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Gun.AM_Weaver_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Gun_Skill.AM_Weaver_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Melee.AM_Weaver_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Melee_Skill.AM_Weaver_Melee_Skill")))</t>
+  </si>
+  <si>
     <t>(TagName="FX.Character.Weaver.Ultimate")</t>
   </si>
   <si>
@@ -561,6 +885,15 @@
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Weaver.Icon_Weaver</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Weaver/ABP_Weaver.ABP_Weaver_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Damage.AM_Weaver_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Dead.AM_Weaver_Dead</t>
+  </si>
+  <si>
     <t>Char_Writer</t>
   </si>
   <si>
@@ -573,6 +906,12 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Writer/Ani/Writer_Base_Battle_Idle.Writer_Base_Battle_Idle</t>
   </si>
   <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Ultimate.AM_Writer_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Book.AM_Writer_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Book_Skill.AM_Writer_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Gun.AM_Writer_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Gun_Skill.AM_Writer_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Melee.AM_Writer_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Melee_Skill.AM_Writer_Melee_Skill")))</t>
+  </si>
+  <si>
     <t>(TagName="FX.Character.Writer.Ultimate")</t>
   </si>
   <si>
@@ -582,420 +921,77 @@
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Writer.Icon_Writer</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Anubis.DA_CharFX_Anubis",BasicAttackTag=(TagName="FX.Character.Anubis.BasicAttack"),SkillTag=(TagName="FX.Character.Anubis.WeaponSkill"),UltimateTag=(TagName="FX.Character.Anubis.Ultimate"),HitTag=(TagName="FX.Character.Anubis.Hit"),DeathTag=(TagName="FX.Character.Anubis.Death"))</t>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Writer/ABP_Writer.ABP_Writer_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Damage.AM_Writer_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Dead.AM_Writer_Dead</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Bard.DA_CharFX_Bard",BasicAttackTag=(TagName="FX.Character.Bard.BasicAttack"),SkillTag=(TagName="FX.Character.Bard.WeaponSkill"),UltimateTag=(TagName="FX.Character.Bard.Ultimate"),UltimateHitTag=(TagName="FX.Character.Bard.UltimateHit"),HitTag=(TagName="FX.Character.Bard.Hit"),DeathTag=(TagName="FX.Character.Bard.Death"))</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Army.DA_CharFX_Army",BasicAttackTag=(TagName="FX.Character.Army.BasicAttack"),SkillTag=(TagName="FX.Character.Army.WeaponSkill"),UltimateTag=(TagName="FX.Character.Army.Ultimate"),HitTag=(TagName="FX.Character.Army.Hit"),DeathTag=(TagName="FX.Character.Army.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Bard.DA_CharFX_Bard",BasicAttackTag=(TagName="FX.Character.Bard.BasicAttack"),SkillTag=(TagName="FX.Character.Bard.WeaponSkill"),UltimateTag=(TagName="FX.Character.Bard.Ultimate"),HitTag=(TagName="FX.Character.Bard.Hit"),DeathTag=(TagName="FX.Character.Bard.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Binder.DA_CharFX_Binder",BasicAttackTag=(TagName="FX.Character.Binder.BasicAttack"),SkillTag=(TagName="FX.Character.Binder.WeaponSkill"),UltimateTag=(TagName="FX.Character.Binder.Ultimate"),HitTag=(TagName="FX.Character.Binder.Hit"),DeathTag=(TagName="FX.Character.Binder.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Courier.DA_CharFX_Courier",BasicAttackTag=(TagName="FX.Character.Courier.BasicAttack"),SkillTag=(TagName="FX.Character.Courier.WeaponSkill"),UltimateTag=(TagName="FX.Character.Courier.Ultimate"),HitTag=(TagName="FX.Character.Courier.Hit"),DeathTag=(TagName="FX.Character.Courier.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Demonia.DA_CharFX_Demonia",BasicAttackTag=(TagName="FX.Character.Demonia.BasicAttack"),SkillTag=(TagName="FX.Character.Demonia.WeaponSkill"),UltimateTag=(TagName="FX.Character.Demonia.Ultimate"),HitTag=(TagName="FX.Character.Demonia.Hit"),DeathTag=(TagName="FX.Character.Demonia.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Enchanter.DA_CharFX_Enchanter",BasicAttackTag=(TagName="FX.Character.Enchanter.BasicAttack"),SkillTag=(TagName="FX.Character.Enchanter.WeaponSkill"),UltimateTag=(TagName="FX.Character.Enchanter.Ultimate"),HitTag=(TagName="FX.Character.Enchanter.Hit"),DeathTag=(TagName="FX.Character.Enchanter.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Guard.DA_CharFX_Guard",BasicAttackTag=(TagName="FX.Character.Guard.BasicAttack"),SkillTag=(TagName="FX.Character.Guard.WeaponSkill"),UltimateTag=(TagName="FX.Character.Guard.Ultimate"),HitTag=(TagName="FX.Character.Guard.Hit"),DeathTag=(TagName="FX.Character.Guard.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Hermit.DA_CharFX_Hermit",BasicAttackTag=(TagName="FX.Character.Hermit.BasicAttack"),SkillTag=(TagName="FX.Character.Hermit.WeaponSkill"),UltimateTag=(TagName="FX.Character.Hermit.Ultimate"),HitTag=(TagName="FX.Character.Hermit.Hit"),DeathTag=(TagName="FX.Character.Hermit.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Hornet.DA_CharFX_Hornet",BasicAttackTag=(TagName="FX.Character.Hornet.BasicAttack"),SkillTag=(TagName="FX.Character.Hornet.WeaponSkill"),UltimateTag=(TagName="FX.Character.Hornet.Ultimate"),HitTag=(TagName="FX.Character.Hornet.Hit"),DeathTag=(TagName="FX.Character.Hornet.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Looter.DA_CharFX_Looter",BasicAttackTag=(TagName="FX.Character.Looter.BasicAttack"),SkillTag=(TagName="FX.Character.Looter.WeaponSkill"),UltimateTag=(TagName="FX.Character.Looter.Ultimate"),HitTag=(TagName="FX.Character.Looter.Hit"),DeathTag=(TagName="FX.Character.Looter.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Maid.DA_CharFX_Maid",BasicAttackTag=(TagName="FX.Character.Maid.BasicAttack"),SkillTag=(TagName="FX.Character.Maid.WeaponSkill"),UltimateTag=(TagName="FX.Character.Maid.Ultimate"),HitTag=(TagName="FX.Character.Maid.Hit"),DeathTag=(TagName="FX.Character.Maid.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Merry.DA_CharFX_Merry",BasicAttackTag=(TagName="FX.Character.Merry.BasicAttack"),SkillTag=(TagName="FX.Character.Merry.WeaponSkill"),UltimateTag=(TagName="FX.Character.Merry.Ultimate"),HitTag=(TagName="FX.Character.Merry.Hit"),DeathTag=(TagName="FX.Character.Merry.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Muzzle.DA_CharFX_Muzzle",BasicAttackTag=(TagName="FX.Character.Muzzle.BasicAttack"),SkillTag=(TagName="FX.Character.Muzzle.WeaponSkill"),UltimateTag=(TagName="FX.Character.Muzzle.Ultimate"),HitTag=(TagName="FX.Character.Muzzle.Hit"),DeathTag=(TagName="FX.Character.Muzzle.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Noble.DA_CharFX_Noble",BasicAttackTag=(TagName="FX.Character.Noble.BasicAttack"),SkillTag=(TagName="FX.Character.Noble.WeaponSkill"),UltimateTag=(TagName="FX.Character.Noble.Ultimate"),HitTag=(TagName="FX.Character.Noble.Hit"),DeathTag=(TagName="FX.Character.Noble.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Nurse.DA_CharFX_Nurse",BasicAttackTag=(TagName="FX.Character.Nurse.BasicAttack"),SkillTag=(TagName="FX.Character.Nurse.WeaponSkill"),UltimateTag=(TagName="FX.Character.Nurse.Ultimate"),HitTag=(TagName="FX.Character.Nurse.Hit"),DeathTag=(TagName="FX.Character.Nurse.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Outsider.DA_CharFX_Outsider",BasicAttackTag=(TagName="FX.Character.Outsider.BasicAttack"),SkillTag=(TagName="FX.Character.Outsider.WeaponSkill"),UltimateTag=(TagName="FX.Character.Outsider.Ultimate"),HitTag=(TagName="FX.Character.Outsider.Hit"),DeathTag=(TagName="FX.Character.Outsider.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Pioneer.DA_CharFX_Pioneer",BasicAttackTag=(TagName="FX.Character.Pioneer.BasicAttack"),SkillTag=(TagName="FX.Character.Pioneer.WeaponSkill"),UltimateTag=(TagName="FX.Character.Pioneer.Ultimate"),HitTag=(TagName="FX.Character.Pioneer.Hit"),DeathTag=(TagName="FX.Character.Pioneer.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Rogue.DA_CharFX_Rogue",BasicAttackTag=(TagName="FX.Character.Rogue.BasicAttack"),SkillTag=(TagName="FX.Character.Rogue.WeaponSkill"),UltimateTag=(TagName="FX.Character.Rogue.Ultimate"),HitTag=(TagName="FX.Character.Rogue.Hit"),DeathTag=(TagName="FX.Character.Rogue.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Tinker.DA_CharFX_Tinker",BasicAttackTag=(TagName="FX.Character.Tinker.BasicAttack"),SkillTag=(TagName="FX.Character.Tinker.WeaponSkill"),UltimateTag=(TagName="FX.Character.Tinker.Ultimate"),HitTag=(TagName="FX.Character.Tinker.Hit"),DeathTag=(TagName="FX.Character.Tinker.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Tuner.DA_CharFX_Tuner",BasicAttackTag=(TagName="FX.Character.Tuner.BasicAttack"),SkillTag=(TagName="FX.Character.Tuner.WeaponSkill"),UltimateTag=(TagName="FX.Character.Tuner.Ultimate"),HitTag=(TagName="FX.Character.Tuner.Hit"),DeathTag=(TagName="FX.Character.Tuner.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Weaver.DA_CharFX_Weaver",BasicAttackTag=(TagName="FX.Character.Weaver.BasicAttack"),SkillTag=(TagName="FX.Character.Weaver.WeaponSkill"),UltimateTag=(TagName="FX.Character.Weaver.Ultimate"),HitTag=(TagName="FX.Character.Weaver.Hit"),DeathTag=(TagName="FX.Character.Weaver.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Writer.DA_CharFX_Writer",BasicAttackTag=(TagName="FX.Character.Writer.BasicAttack"),SkillTag=(TagName="FX.Character.Writer.WeaponSkill"),UltimateTag=(TagName="FX.Character.Writer.Ultimate"),HitTag=(TagName="FX.Character.Writer.Hit"),DeathTag=(TagName="FX.Character.Writer.Death"))</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Ultimate.AM_Anubis_Ultimate</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Ultimate.AM_Army_Ultimate</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Ultimate.AM_Bard_Ultimate</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Ultimate.AM_Binder_Ultimate</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Ultimate.AM_Courier_Ultimate</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Ultimate.AM_Demonia_Ultimate</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Ultimate.AM_Enchanter_Ultimate</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Ultimate.AM_Guard_Ultimate</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Ultimate.AM_Hermit_Ultimate</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Ultimate.AM_Hornet_Ultimate</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Ultimate.AM_Looter_Ultimate</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Ultimate.AM_Maid_Ultimate</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Ultimate.AM_Merry_Ultimate</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Ultimate.AM_Muzzle_Ultimate</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Ultimate.AM_Noble_Ultimate</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Ultimate.AM_Nurse_Ultimate</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Ultimate.AM_Outsider_Ultimate</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Ultimate.AM_Pioneer_Ultimate</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Ultimate.AM_Rogue_Ultimate</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Ultimate.AM_Tinker_Ultimate</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Ultimate.AM_Tuner_Ultimate</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Ultimate.AM_Weaver_Ultimate</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Ultimate.AM_Writer_Ultimate</t>
-  </si>
-  <si>
-    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Book.AM_Anubis_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Book_Skill.AM_Anubis_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Gun.AM_Anubis_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Gun_Skill.AM_Anubis_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Melee.AM_Anubis_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Melee_Skill.AM_Anubis_Melee_Skill")))</t>
-  </si>
-  <si>
-    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Book.AM_Army_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Book_Skill.AM_Army_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Gun.AM_Army_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Gun_Skill.AM_Army_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Melee.AM_Army_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Melee_Skill.AM_Army_Melee_Skill")))</t>
-  </si>
-  <si>
-    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Book.AM_Bard_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Book_Skill.AM_Bard_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Gun.AM_Bard_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Gun_Skill.AM_Bard_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Melee.AM_Bard_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Melee_Skill.AM_Bard_Melee_Skill")))</t>
-  </si>
-  <si>
-    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Book.AM_Binder_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Book_Skill.AM_Binder_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Gun.AM_Binder_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Gun_Skill.AM_Binder_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Melee.AM_Binder_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Melee_Skill.AM_Binder_Melee_Skill")))</t>
-  </si>
-  <si>
-    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Book.AM_Courier_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Book_Skill.AM_Courier_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Gun.AM_Courier_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Gun_Skill.AM_Courier_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Melee.AM_Courier_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Melee_Skill.AM_Courier_Melee_Skill")))</t>
-  </si>
-  <si>
-    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Book.AM_Demonia_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Book_Skill.AM_Demonia_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Gun.AM_Demonia_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Gun_Skill.AM_Demonia_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Melee.AM_Demonia_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Melee_Skill.AM_Demonia_Melee_Skill")))</t>
-  </si>
-  <si>
-    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Book.AM_Enchanter_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Book_Skill.AM_Enchanter_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Gun.AM_Enchanter_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Gun_Skill.AM_Enchanter_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Melee.AM_Enchanter_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Melee_Skill.AM_Enchanter_Melee_Skill")))</t>
-  </si>
-  <si>
-    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Book.AM_Guard_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Book_Skill.AM_Guard_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Gun.AM_Guard_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Gun_Skill.AM_Guard_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Melee.AM_Guard_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Melee_Skill.AM_Guard_Melee_Skill")))</t>
-  </si>
-  <si>
-    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Book.AM_Hermit_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Book_Skill.AM_Hermit_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Gun.AM_Hermit_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Gun_Skill.AM_Hermit_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Melee.AM_Hermit_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Melee_Skill.AM_Hermit_Melee_Skill")))</t>
-  </si>
-  <si>
-    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Book.AM_Hornet_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Book_Skill.AM_Hornet_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Gun.AM_Hornet_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Gun_Skill.AM_Hornet_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Melee.AM_Hornet_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Melee_Skill.AM_Hornet_Melee_Skill")))</t>
-  </si>
-  <si>
-    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Book.AM_Looter_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Book_Skill.AM_Looter_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Gun.AM_Looter_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Gun_Skill.AM_Looter_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Melee.AM_Looter_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Melee_Skill.AM_Looter_Melee_Skill")))</t>
-  </si>
-  <si>
-    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Book.AM_Maid_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Book_Skill.AM_Maid_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Gun.AM_Maid_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Gun_Skill.AM_Maid_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Melee.AM_Maid_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Melee_Skill.AM_Maid_Melee_Skill")))</t>
-  </si>
-  <si>
-    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Book.AM_Merry_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Book_Skill.AM_Merry_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Gun.AM_Merry_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Gun_Skill.AM_Merry_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Melee.AM_Merry_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Melee_Skill.AM_Merry_Melee_Skill")))</t>
-  </si>
-  <si>
-    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Book.AM_Muzzle_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Book_Skill.AM_Muzzle_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Gun.AM_Muzzle_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Gun_Skill.AM_Muzzle_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Melee.AM_Muzzle_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Melee_Skill.AM_Muzzle_Melee_Skill")))</t>
-  </si>
-  <si>
-    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Book.AM_Noble_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Book_Skill.AM_Noble_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Gun.AM_Noble_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Gun_Skill.AM_Noble_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Melee.AM_Noble_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Melee_Skill.AM_Noble_Melee_Skill")))</t>
-  </si>
-  <si>
-    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Book.AM_Nurse_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Book_Skill.AM_Nurse_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Gun.AM_Nurse_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Gun_Skill.AM_Nurse_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Melee.AM_Nurse_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Melee_Skill.AM_Nurse_Melee_Skill")))</t>
-  </si>
-  <si>
-    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Book.AM_Outsider_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Book_Skill.AM_Outsider_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Gun.AM_Outsider_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Gun_Skill.AM_Outsider_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Melee.AM_Outsider_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Melee_Skill.AM_Outsider_Melee_Skill")))</t>
-  </si>
-  <si>
-    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Book.AM_Pioneer_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Book_Skill.AM_Pioneer_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Gun.AM_Pioneer_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Gun_Skill.AM_Pioneer_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Melee.AM_Pioneer_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Melee_Skill.AM_Pioneer_Melee_Skill")))</t>
-  </si>
-  <si>
-    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Book.AM_Rogue_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Book_Skill.AM_Rogue_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Gun.AM_Rogue_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Gun_Skill.AM_Rogue_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Melee.AM_Rogue_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Melee_Skill.AM_Rogue_Melee_Skill")))</t>
-  </si>
-  <si>
-    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Book.AM_Tinker_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Book_Skill.AM_Tinker_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Gun.AM_Tinker_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Gun_Skill.AM_Tinker_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Melee.AM_Tinker_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Melee_Skill.AM_Tinker_Melee_Skill")))</t>
-  </si>
-  <si>
-    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Book.AM_Tuner_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Book_Skill.AM_Tuner_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Gun.AM_Tuner_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Gun_Skill.AM_Tuner_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Melee.AM_Tuner_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Melee_Skill.AM_Tuner_Melee_Skill")))</t>
-  </si>
-  <si>
-    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Book.AM_Weaver_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Book_Skill.AM_Weaver_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Gun.AM_Weaver_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Gun_Skill.AM_Weaver_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Melee.AM_Weaver_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Melee_Skill.AM_Weaver_Melee_Skill")))</t>
-  </si>
-  <si>
-    <t>((Book,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Book.AM_Writer_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Book_Skill.AM_Writer_Book_Skill")),(Gun,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Gun.AM_Writer_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Gun_Skill.AM_Writer_Gun_Skill")),(Melee,(BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Melee.AM_Writer_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Melee_Skill.AM_Writer_Melee_Skill")))</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Anubis/ABP_Anubis.ABP_Anubis_C</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Army/ABP_Army.ABP_Army_C</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Bard/ABP_Bard.ABP_Bard_C</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Binder/ABP_Binder.ABP_Binder_C</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Courier/ABP_Courier.ABP_Courier_C</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Demonia/ABP_Demonia.ABP_Demonia_C</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Enchanter/ABP_Enchanter.ABP_Enchanter_C</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Guard/ABP_Guard.ABP_Guard_C</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Hermit/ABP_Hermit.ABP_Hermit_C</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Hornet/ABP_Hornet.ABP_Hornet_C</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Looter/ABP_Looter.ABP_Looter_C</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Maid/ABP_Maid.ABP_Maid_C</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Merry/ABP_Merry.ABP_Merry_C</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Muzzle/ABP_Muzzle.ABP_Muzzle_C</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Noble/ABP_Noble.ABP_Noble_C</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Nurse/ABP_Nurse.ABP_Nurse_C</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Outsider/ABP_Outsider.ABP_Outsider_C</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Pioneer/ABP_Pioneer.ABP_Pioneer_C</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Rogue/ABP_Rogue.ABP_Rogue_C</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Tinker/ABP_Tinker.ABP_Tinker_C</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Tuner/ABP_Tuner.ABP_Tuner_C</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Weaver/ABP_Weaver.ABP_Weaver_C</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Writer/ABP_Writer.ABP_Writer_C</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Damage.AM_Anubis_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Damage.AM_Army_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Damage.AM_Bard_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Damage.AM_Binder_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Damage.AM_Courier_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Damage.AM_Demonia_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Damage.AM_Enchanter_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Damage.AM_Guard_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Damage.AM_Hermit_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Damage.AM_Hornet_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Damage.AM_Looter_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Damage.AM_Maid_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Damage.AM_Merry_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Damage.AM_Muzzle_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Damage.AM_Noble_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Damage.AM_Nurse_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Damage.AM_Outsider_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Damage.AM_Pioneer_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Damage.AM_Rogue_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Damage.AM_Tinker_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Damage.AM_Tuner_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Damage.AM_Weaver_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Damage.AM_Writer_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Dead.AM_Army_Dead</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Dead.AM_Bard_Dead</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Dead.AM_Binder_Dead</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Dead.AM_Courier_Dead</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Dead.AM_Demonia_Dead</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Dead.AM_Enchanter_Dead</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Dead.AM_Guard_Dead</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Dead.AM_Hermit_Dead</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Dead.AM_Hornet_Dead</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Dead.AM_Looter_Dead</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Dead.AM_Maid_Dead</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Dead.AM_Merry_Dead</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Dead.AM_Muzzle_Dead</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Dead.AM_Noble_Dead</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Dead.AM_Nurse_Dead</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Dead.AM_Outsider_Dead</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Dead.AM_Pioneer_Dead</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Dead.AM_Rogue_Dead</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Dead.AM_Tinker_Dead</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Dead.AM_Tuner_Dead</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Dead.AM_Weaver_Dead</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Dead.AM_Writer_Dead</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Dead.AM_Anubis_Dead</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Binder.DA_CharFX_Binder",BasicAttackTag=(TagName="FX.Character.Binder.BasicAttack"),SkillTag=(TagName="FX.Character.Binder.WeaponSkill"),UltimateTag=(TagName="FX.Character.Binder.Ultimate"),UltimateHitTag=(TagName="FX.Character.Binder.UltimateHit"),HitTag=(TagName="FX.Character.Binder.Hit"),DeathTag=(TagName="FX.Character.Binder.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Courier.DA_CharFX_Courier",BasicAttackTag=(TagName="FX.Character.Courier.BasicAttack"),SkillTag=(TagName="FX.Character.Courier.WeaponSkill"),UltimateTag=(TagName="FX.Character.Courier.Ultimate"),UltimateHitTag=(TagName="FX.Character.Courier.UltimateHit"),HitTag=(TagName="FX.Character.Courier.Hit"),DeathTag=(TagName="FX.Character.Courier.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Demonia.DA_CharFX_Demonia",BasicAttackTag=(TagName="FX.Character.Demonia.BasicAttack"),SkillTag=(TagName="FX.Character.Demonia.WeaponSkill"),UltimateTag=(TagName="FX.Character.Demonia.Ultimate"),UltimateHitTag=(TagName="FX.Character.Demonia.UltimateHit"),HitTag=(TagName="FX.Character.Demonia.Hit"),DeathTag=(TagName="FX.Character.Demonia.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Enchanter.DA_CharFX_Enchanter",BasicAttackTag=(TagName="FX.Character.Enchanter.BasicAttack"),SkillTag=(TagName="FX.Character.Enchanter.WeaponSkill"),UltimateTag=(TagName="FX.Character.Enchanter.Ultimate"),UltimateHitTag=(TagName="FX.Character.Enchanter.UltimateHit"),HitTag=(TagName="FX.Character.Enchanter.Hit"),DeathTag=(TagName="FX.Character.Enchanter.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Guard.DA_CharFX_Guard",BasicAttackTag=(TagName="FX.Character.Guard.BasicAttack"),SkillTag=(TagName="FX.Character.Guard.WeaponSkill"),UltimateTag=(TagName="FX.Character.Guard.Ultimate"),UltimateHitTag=(TagName="FX.Character.Guard.UltimateHit"),HitTag=(TagName="FX.Character.Guard.Hit"),DeathTag=(TagName="FX.Character.Guard.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Hermit.DA_CharFX_Hermit",BasicAttackTag=(TagName="FX.Character.Hermit.BasicAttack"),SkillTag=(TagName="FX.Character.Hermit.WeaponSkill"),UltimateTag=(TagName="FX.Character.Hermit.Ultimate"),UltimateHitTag=(TagName="FX.Character.Hermit.UltimateHit"),HitTag=(TagName="FX.Character.Hermit.Hit"),DeathTag=(TagName="FX.Character.Hermit.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Hornet.DA_CharFX_Hornet",BasicAttackTag=(TagName="FX.Character.Hornet.BasicAttack"),SkillTag=(TagName="FX.Character.Hornet.WeaponSkill"),UltimateTag=(TagName="FX.Character.Hornet.Ultimate"),UltimateHitTag=(TagName="FX.Character.Hornet.UltimateHit"),HitTag=(TagName="FX.Character.Hornet.Hit"),DeathTag=(TagName="FX.Character.Hornet.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Looter.DA_CharFX_Looter",BasicAttackTag=(TagName="FX.Character.Looter.BasicAttack"),SkillTag=(TagName="FX.Character.Looter.WeaponSkill"),UltimateTag=(TagName="FX.Character.Looter.Ultimate"),UltimateHitTag=(TagName="FX.Character.Looter.UltimateHit"),HitTag=(TagName="FX.Character.Looter.Hit"),DeathTag=(TagName="FX.Character.Looter.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Maid.DA_CharFX_Maid",BasicAttackTag=(TagName="FX.Character.Maid.BasicAttack"),SkillTag=(TagName="FX.Character.Maid.WeaponSkill"),UltimateTag=(TagName="FX.Character.Maid.Ultimate"),UltimateHitTag=(TagName="FX.Character.Maid.UltimateHit"),HitTag=(TagName="FX.Character.Maid.Hit"),DeathTag=(TagName="FX.Character.Maid.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Merry.DA_CharFX_Merry",BasicAttackTag=(TagName="FX.Character.Merry.BasicAttack"),SkillTag=(TagName="FX.Character.Merry.WeaponSkill"),UltimateTag=(TagName="FX.Character.Merry.Ultimate"),UltimateHitTag=(TagName="FX.Character.Merry.UltimateHit"),HitTag=(TagName="FX.Character.Merry.Hit"),DeathTag=(TagName="FX.Character.Merry.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Muzzle.DA_CharFX_Muzzle",BasicAttackTag=(TagName="FX.Character.Muzzle.BasicAttack"),SkillTag=(TagName="FX.Character.Muzzle.WeaponSkill"),UltimateTag=(TagName="FX.Character.Muzzle.Ultimate"),UltimateHitTag=(TagName="FX.Character.Muzzle.UltimateHit"),HitTag=(TagName="FX.Character.Muzzle.Hit"),DeathTag=(TagName="FX.Character.Muzzle.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Noble.DA_CharFX_Noble",BasicAttackTag=(TagName="FX.Character.Noble.BasicAttack"),SkillTag=(TagName="FX.Character.Noble.WeaponSkill"),UltimateTag=(TagName="FX.Character.Noble.Ultimate"),UltimateHitTag=(TagName="FX.Character.Noble.UltimateHit"),HitTag=(TagName="FX.Character.Noble.Hit"),DeathTag=(TagName="FX.Character.Noble.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Nurse.DA_CharFX_Nurse",BasicAttackTag=(TagName="FX.Character.Nurse.BasicAttack"),SkillTag=(TagName="FX.Character.Nurse.WeaponSkill"),UltimateTag=(TagName="FX.Character.Nurse.Ultimate"),UltimateHitTag=(TagName="FX.Character.Nurse.UltimateHit"),HitTag=(TagName="FX.Character.Nurse.Hit"),DeathTag=(TagName="FX.Character.Nurse.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Outsider.DA_CharFX_Outsider",BasicAttackTag=(TagName="FX.Character.Outsider.BasicAttack"),SkillTag=(TagName="FX.Character.Outsider.WeaponSkill"),UltimateTag=(TagName="FX.Character.Outsider.Ultimate"),UltimateHitTag=(TagName="FX.Character.Outsider.UltimateHit"),HitTag=(TagName="FX.Character.Outsider.Hit"),DeathTag=(TagName="FX.Character.Outsider.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Pioneer.DA_CharFX_Pioneer",BasicAttackTag=(TagName="FX.Character.Pioneer.BasicAttack"),SkillTag=(TagName="FX.Character.Pioneer.WeaponSkill"),UltimateTag=(TagName="FX.Character.Pioneer.Ultimate"),UltimateHitTag=(TagName="FX.Character.Pioneer.UltimateHit"),HitTag=(TagName="FX.Character.Pioneer.Hit"),DeathTag=(TagName="FX.Character.Pioneer.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Rogue.DA_CharFX_Rogue",BasicAttackTag=(TagName="FX.Character.Rogue.BasicAttack"),SkillTag=(TagName="FX.Character.Rogue.WeaponSkill"),UltimateTag=(TagName="FX.Character.Rogue.Ultimate"),UltimateHitTag=(TagName="FX.Character.Rogue.UltimateHit"),HitTag=(TagName="FX.Character.Rogue.Hit"),DeathTag=(TagName="FX.Character.Rogue.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Tinker.DA_CharFX_Tinker",BasicAttackTag=(TagName="FX.Character.Tinker.BasicAttack"),SkillTag=(TagName="FX.Character.Tinker.WeaponSkill"),UltimateTag=(TagName="FX.Character.Tinker.Ultimate"),UltimateHitTag=(TagName="FX.Character.Tinker.UltimateHit"),HitTag=(TagName="FX.Character.Tinker.Hit"),DeathTag=(TagName="FX.Character.Tinker.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Tuner.DA_CharFX_Tuner",BasicAttackTag=(TagName="FX.Character.Tuner.BasicAttack"),SkillTag=(TagName="FX.Character.Tuner.WeaponSkill"),UltimateTag=(TagName="FX.Character.Tuner.Ultimate"),UltimateHitTag=(TagName="FX.Character.Tuner.UltimateHit"),HitTag=(TagName="FX.Character.Tuner.Hit"),DeathTag=(TagName="FX.Character.Tuner.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Weaver.DA_CharFX_Weaver",BasicAttackTag=(TagName="FX.Character.Weaver.BasicAttack"),SkillTag=(TagName="FX.Character.Weaver.WeaponSkill"),UltimateTag=(TagName="FX.Character.Weaver.Ultimate"),UltimateHitTag=(TagName="FX.Character.Weaver.UltimateHit"),HitTag=(TagName="FX.Character.Weaver.Hit"),DeathTag=(TagName="FX.Character.Weaver.Death"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Writer.DA_CharFX_Writer",BasicAttackTag=(TagName="FX.Character.Writer.BasicAttack"),SkillTag=(TagName="FX.Character.Writer.WeaponSkill"),UltimateTag=(TagName="FX.Character.Writer.Ultimate"),UltimateHitTag=(TagName="FX.Character.Writer.UltimateHit"),HitTag=(TagName="FX.Character.Writer.Hit"),DeathTag=(TagName="FX.Character.Writer.Death"))</t>
   </si>
 </sst>
 </file>
@@ -1992,260 +1988,260 @@
         <v>23</v>
       </c>
       <c r="H2" t="s">
-        <v>210</v>
+        <v>24</v>
       </c>
       <c r="I2" t="s">
-        <v>233</v>
+        <v>25</v>
       </c>
       <c r="J2" t="s">
-        <v>187</v>
+        <v>26</v>
       </c>
       <c r="K2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="N2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="O2" t="s">
-        <v>256</v>
+        <v>31</v>
       </c>
       <c r="P2" t="s">
-        <v>279</v>
+        <v>32</v>
       </c>
       <c r="Q2" t="s">
-        <v>324</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
         <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H3" t="s">
-        <v>211</v>
+        <v>40</v>
       </c>
       <c r="I3" t="s">
-        <v>234</v>
+        <v>41</v>
       </c>
       <c r="J3" t="s">
-        <v>188</v>
+        <v>42</v>
       </c>
       <c r="K3" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="L3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M3" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="N3" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="O3" t="s">
-        <v>257</v>
+        <v>46</v>
       </c>
       <c r="P3" t="s">
-        <v>280</v>
+        <v>47</v>
       </c>
       <c r="Q3" t="s">
-        <v>302</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E4" t="s">
         <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="G4" t="s">
         <v>23</v>
       </c>
       <c r="H4" t="s">
-        <v>212</v>
+        <v>54</v>
       </c>
       <c r="I4" t="s">
-        <v>235</v>
+        <v>55</v>
       </c>
       <c r="J4" t="s">
-        <v>189</v>
+        <v>303</v>
       </c>
       <c r="K4" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="L4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M4" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="N4" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="O4" t="s">
-        <v>258</v>
+        <v>59</v>
       </c>
       <c r="P4" t="s">
-        <v>281</v>
+        <v>60</v>
       </c>
       <c r="Q4" t="s">
-        <v>303</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="B5" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E5" t="s">
         <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="G5" t="s">
         <v>23</v>
       </c>
       <c r="H5" t="s">
-        <v>213</v>
+        <v>67</v>
       </c>
       <c r="I5" t="s">
-        <v>236</v>
+        <v>68</v>
       </c>
       <c r="J5" t="s">
-        <v>190</v>
+        <v>304</v>
       </c>
       <c r="K5" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="L5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M5" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="N5" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="O5" t="s">
-        <v>259</v>
+        <v>72</v>
       </c>
       <c r="P5" t="s">
-        <v>282</v>
+        <v>73</v>
       </c>
       <c r="Q5" t="s">
-        <v>304</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="E6" t="s">
         <v>21</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="G6" t="s">
         <v>23</v>
       </c>
       <c r="H6" t="s">
-        <v>214</v>
+        <v>80</v>
       </c>
       <c r="I6" t="s">
-        <v>237</v>
+        <v>81</v>
       </c>
       <c r="J6" t="s">
-        <v>191</v>
+        <v>305</v>
       </c>
       <c r="K6" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="L6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M6" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="N6" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="O6" t="s">
-        <v>260</v>
+        <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>283</v>
+        <v>86</v>
       </c>
       <c r="Q6" t="s">
-        <v>305</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="E7" t="s">
         <v>21</v>
@@ -2257,472 +2253,472 @@
         <v>23</v>
       </c>
       <c r="H7" t="s">
-        <v>215</v>
+        <v>92</v>
       </c>
       <c r="I7" t="s">
-        <v>238</v>
+        <v>93</v>
       </c>
       <c r="J7" t="s">
-        <v>192</v>
+        <v>306</v>
       </c>
       <c r="K7" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="L7" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M7" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="N7" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="O7" t="s">
-        <v>261</v>
+        <v>97</v>
       </c>
       <c r="P7" t="s">
-        <v>284</v>
+        <v>98</v>
       </c>
       <c r="Q7" t="s">
-        <v>306</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="D8" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="E8" t="s">
         <v>21</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="G8" t="s">
         <v>23</v>
       </c>
       <c r="H8" t="s">
-        <v>216</v>
+        <v>104</v>
       </c>
       <c r="I8" t="s">
-        <v>239</v>
+        <v>105</v>
       </c>
       <c r="J8" t="s">
-        <v>193</v>
+        <v>307</v>
       </c>
       <c r="K8" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="L8" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M8" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="N8" t="s">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="O8" t="s">
-        <v>262</v>
+        <v>109</v>
       </c>
       <c r="P8" t="s">
-        <v>285</v>
+        <v>110</v>
       </c>
       <c r="Q8" t="s">
-        <v>307</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="D9" t="s">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="E9" t="s">
         <v>21</v>
       </c>
       <c r="F9" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G9" t="s">
         <v>23</v>
       </c>
       <c r="H9" t="s">
-        <v>217</v>
+        <v>116</v>
       </c>
       <c r="I9" t="s">
-        <v>240</v>
+        <v>117</v>
       </c>
       <c r="J9" t="s">
-        <v>194</v>
+        <v>308</v>
       </c>
       <c r="K9" t="s">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="L9" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M9" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="N9" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="O9" t="s">
-        <v>263</v>
+        <v>121</v>
       </c>
       <c r="P9" t="s">
-        <v>286</v>
+        <v>122</v>
       </c>
       <c r="Q9" t="s">
-        <v>308</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="D10" t="s">
-        <v>85</v>
+        <v>127</v>
       </c>
       <c r="E10" t="s">
         <v>21</v>
       </c>
       <c r="F10" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="G10" t="s">
         <v>23</v>
       </c>
       <c r="H10" t="s">
-        <v>218</v>
+        <v>128</v>
       </c>
       <c r="I10" t="s">
-        <v>241</v>
+        <v>129</v>
       </c>
       <c r="J10" t="s">
-        <v>195</v>
+        <v>309</v>
       </c>
       <c r="K10" t="s">
-        <v>86</v>
+        <v>130</v>
       </c>
       <c r="L10" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M10" t="s">
-        <v>87</v>
+        <v>131</v>
       </c>
       <c r="N10" t="s">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="O10" t="s">
-        <v>264</v>
+        <v>133</v>
       </c>
       <c r="P10" t="s">
-        <v>287</v>
+        <v>134</v>
       </c>
       <c r="Q10" t="s">
-        <v>309</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>89</v>
+        <v>136</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>137</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>138</v>
       </c>
       <c r="D11" t="s">
-        <v>92</v>
+        <v>139</v>
       </c>
       <c r="E11" t="s">
         <v>21</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G11" t="s">
         <v>23</v>
       </c>
       <c r="H11" t="s">
-        <v>219</v>
+        <v>140</v>
       </c>
       <c r="I11" t="s">
-        <v>242</v>
+        <v>141</v>
       </c>
       <c r="J11" t="s">
-        <v>196</v>
+        <v>310</v>
       </c>
       <c r="K11" t="s">
-        <v>93</v>
+        <v>142</v>
       </c>
       <c r="L11" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M11" t="s">
-        <v>94</v>
+        <v>143</v>
       </c>
       <c r="N11" t="s">
-        <v>95</v>
+        <v>144</v>
       </c>
       <c r="O11" t="s">
-        <v>265</v>
+        <v>145</v>
       </c>
       <c r="P11" t="s">
-        <v>288</v>
+        <v>146</v>
       </c>
       <c r="Q11" t="s">
-        <v>310</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>96</v>
+        <v>148</v>
       </c>
       <c r="B12" t="s">
-        <v>97</v>
+        <v>149</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="D12" t="s">
-        <v>99</v>
+        <v>151</v>
       </c>
       <c r="E12" t="s">
         <v>21</v>
       </c>
       <c r="F12" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="G12" t="s">
         <v>23</v>
       </c>
       <c r="H12" t="s">
-        <v>220</v>
+        <v>152</v>
       </c>
       <c r="I12" t="s">
-        <v>243</v>
+        <v>153</v>
       </c>
       <c r="J12" t="s">
-        <v>197</v>
+        <v>311</v>
       </c>
       <c r="K12" t="s">
-        <v>100</v>
+        <v>154</v>
       </c>
       <c r="L12" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M12" t="s">
-        <v>101</v>
+        <v>155</v>
       </c>
       <c r="N12" t="s">
-        <v>102</v>
+        <v>156</v>
       </c>
       <c r="O12" t="s">
-        <v>266</v>
+        <v>21</v>
       </c>
       <c r="P12" t="s">
-        <v>289</v>
+        <v>157</v>
       </c>
       <c r="Q12" t="s">
-        <v>311</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>103</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s">
-        <v>104</v>
+        <v>160</v>
       </c>
       <c r="C13" t="s">
-        <v>105</v>
+        <v>161</v>
       </c>
       <c r="D13" t="s">
-        <v>106</v>
+        <v>162</v>
       </c>
       <c r="E13" t="s">
         <v>21</v>
       </c>
       <c r="F13" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="G13" t="s">
         <v>23</v>
       </c>
       <c r="H13" t="s">
-        <v>221</v>
+        <v>163</v>
       </c>
       <c r="I13" t="s">
-        <v>244</v>
+        <v>164</v>
       </c>
       <c r="J13" t="s">
-        <v>198</v>
+        <v>312</v>
       </c>
       <c r="K13" t="s">
-        <v>107</v>
+        <v>165</v>
       </c>
       <c r="L13" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M13" t="s">
-        <v>108</v>
+        <v>166</v>
       </c>
       <c r="N13" t="s">
-        <v>109</v>
+        <v>167</v>
       </c>
       <c r="O13" t="s">
-        <v>267</v>
+        <v>168</v>
       </c>
       <c r="P13" t="s">
-        <v>290</v>
+        <v>169</v>
       </c>
       <c r="Q13" t="s">
-        <v>312</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>110</v>
+        <v>171</v>
       </c>
       <c r="B14" t="s">
-        <v>111</v>
+        <v>172</v>
       </c>
       <c r="C14" t="s">
-        <v>112</v>
+        <v>173</v>
       </c>
       <c r="D14" t="s">
-        <v>113</v>
+        <v>174</v>
       </c>
       <c r="E14" t="s">
         <v>21</v>
       </c>
       <c r="F14" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="G14" t="s">
         <v>23</v>
       </c>
       <c r="H14" t="s">
-        <v>222</v>
+        <v>175</v>
       </c>
       <c r="I14" t="s">
-        <v>245</v>
+        <v>176</v>
       </c>
       <c r="J14" t="s">
-        <v>199</v>
+        <v>313</v>
       </c>
       <c r="K14" t="s">
-        <v>114</v>
+        <v>177</v>
       </c>
       <c r="L14" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M14" t="s">
-        <v>115</v>
+        <v>178</v>
       </c>
       <c r="N14" t="s">
-        <v>116</v>
+        <v>179</v>
       </c>
       <c r="O14" t="s">
-        <v>268</v>
+        <v>180</v>
       </c>
       <c r="P14" t="s">
-        <v>291</v>
+        <v>181</v>
       </c>
       <c r="Q14" t="s">
-        <v>313</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>117</v>
+        <v>183</v>
       </c>
       <c r="B15" t="s">
-        <v>118</v>
+        <v>184</v>
       </c>
       <c r="C15" t="s">
-        <v>119</v>
+        <v>185</v>
       </c>
       <c r="D15" t="s">
-        <v>120</v>
+        <v>186</v>
       </c>
       <c r="E15" t="s">
         <v>21</v>
       </c>
       <c r="F15" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="G15" t="s">
         <v>23</v>
       </c>
       <c r="H15" t="s">
-        <v>223</v>
+        <v>187</v>
       </c>
       <c r="I15" t="s">
-        <v>246</v>
+        <v>188</v>
       </c>
       <c r="J15" t="s">
-        <v>200</v>
+        <v>314</v>
       </c>
       <c r="K15" t="s">
-        <v>121</v>
+        <v>189</v>
       </c>
       <c r="L15" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M15" t="s">
-        <v>122</v>
+        <v>190</v>
       </c>
       <c r="N15" t="s">
-        <v>123</v>
+        <v>191</v>
       </c>
       <c r="O15" t="s">
-        <v>269</v>
+        <v>192</v>
       </c>
       <c r="P15" t="s">
-        <v>292</v>
+        <v>193</v>
       </c>
       <c r="Q15" t="s">
-        <v>314</v>
+        <v>194</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>124</v>
+        <v>195</v>
       </c>
       <c r="B16" t="s">
-        <v>125</v>
+        <v>196</v>
       </c>
       <c r="C16" t="s">
-        <v>126</v>
+        <v>197</v>
       </c>
       <c r="D16" t="s">
-        <v>127</v>
+        <v>198</v>
       </c>
       <c r="E16" t="s">
         <v>21</v>
@@ -2734,458 +2730,458 @@
         <v>23</v>
       </c>
       <c r="H16" t="s">
-        <v>224</v>
+        <v>199</v>
       </c>
       <c r="I16" t="s">
-        <v>247</v>
+        <v>200</v>
       </c>
       <c r="J16" t="s">
+        <v>315</v>
+      </c>
+      <c r="K16" t="s">
         <v>201</v>
       </c>
-      <c r="K16" t="s">
-        <v>128</v>
-      </c>
       <c r="L16" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M16" t="s">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="N16" t="s">
-        <v>130</v>
+        <v>203</v>
       </c>
       <c r="O16" t="s">
-        <v>270</v>
+        <v>204</v>
       </c>
       <c r="P16" t="s">
-        <v>293</v>
+        <v>205</v>
       </c>
       <c r="Q16" t="s">
-        <v>315</v>
+        <v>206</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>131</v>
+        <v>207</v>
       </c>
       <c r="B17" t="s">
-        <v>132</v>
+        <v>208</v>
       </c>
       <c r="C17" t="s">
-        <v>133</v>
+        <v>209</v>
       </c>
       <c r="D17" t="s">
-        <v>134</v>
+        <v>210</v>
       </c>
       <c r="E17" t="s">
         <v>21</v>
       </c>
       <c r="F17" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="G17" t="s">
         <v>23</v>
       </c>
       <c r="H17" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="I17" t="s">
-        <v>248</v>
+        <v>212</v>
       </c>
       <c r="J17" t="s">
-        <v>202</v>
+        <v>316</v>
       </c>
       <c r="K17" t="s">
-        <v>135</v>
+        <v>213</v>
       </c>
       <c r="L17" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M17" t="s">
-        <v>136</v>
+        <v>214</v>
       </c>
       <c r="N17" t="s">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="O17" t="s">
-        <v>271</v>
+        <v>216</v>
       </c>
       <c r="P17" t="s">
-        <v>294</v>
+        <v>217</v>
       </c>
       <c r="Q17" t="s">
-        <v>316</v>
+        <v>218</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>138</v>
+        <v>219</v>
       </c>
       <c r="B18" t="s">
-        <v>139</v>
+        <v>220</v>
       </c>
       <c r="C18" t="s">
-        <v>140</v>
+        <v>221</v>
       </c>
       <c r="D18" t="s">
-        <v>141</v>
+        <v>222</v>
       </c>
       <c r="E18" t="s">
         <v>21</v>
       </c>
       <c r="F18" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="G18" t="s">
         <v>23</v>
       </c>
       <c r="H18" t="s">
+        <v>223</v>
+      </c>
+      <c r="I18" t="s">
+        <v>224</v>
+      </c>
+      <c r="J18" t="s">
+        <v>317</v>
+      </c>
+      <c r="K18" t="s">
+        <v>225</v>
+      </c>
+      <c r="L18" t="s">
+        <v>28</v>
+      </c>
+      <c r="M18" t="s">
         <v>226</v>
       </c>
-      <c r="I18" t="s">
-        <v>249</v>
-      </c>
-      <c r="J18" t="s">
-        <v>203</v>
-      </c>
-      <c r="K18" t="s">
-        <v>142</v>
-      </c>
-      <c r="L18" t="s">
-        <v>25</v>
-      </c>
-      <c r="M18" t="s">
-        <v>143</v>
-      </c>
       <c r="N18" t="s">
-        <v>144</v>
+        <v>227</v>
       </c>
       <c r="O18" t="s">
-        <v>272</v>
+        <v>228</v>
       </c>
       <c r="P18" t="s">
-        <v>295</v>
+        <v>229</v>
       </c>
       <c r="Q18" t="s">
-        <v>317</v>
+        <v>230</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>145</v>
+        <v>231</v>
       </c>
       <c r="B19" t="s">
-        <v>146</v>
+        <v>232</v>
       </c>
       <c r="C19" t="s">
-        <v>147</v>
+        <v>233</v>
       </c>
       <c r="D19" t="s">
-        <v>148</v>
+        <v>234</v>
       </c>
       <c r="E19" t="s">
         <v>21</v>
       </c>
       <c r="F19" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="G19" t="s">
         <v>23</v>
       </c>
       <c r="H19" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="I19" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="J19" t="s">
-        <v>204</v>
+        <v>318</v>
       </c>
       <c r="K19" t="s">
-        <v>149</v>
+        <v>237</v>
       </c>
       <c r="L19" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M19" t="s">
-        <v>150</v>
+        <v>238</v>
       </c>
       <c r="N19" t="s">
-        <v>151</v>
+        <v>239</v>
       </c>
       <c r="O19" t="s">
-        <v>273</v>
+        <v>240</v>
       </c>
       <c r="P19" t="s">
-        <v>296</v>
+        <v>241</v>
       </c>
       <c r="Q19" t="s">
-        <v>318</v>
+        <v>242</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>152</v>
+        <v>243</v>
       </c>
       <c r="B20" t="s">
-        <v>153</v>
+        <v>244</v>
       </c>
       <c r="C20" t="s">
-        <v>154</v>
+        <v>245</v>
       </c>
       <c r="D20" t="s">
-        <v>155</v>
+        <v>246</v>
       </c>
       <c r="E20" t="s">
         <v>21</v>
       </c>
       <c r="F20" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G20" t="s">
         <v>23</v>
       </c>
       <c r="H20" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="I20" t="s">
+        <v>248</v>
+      </c>
+      <c r="J20" t="s">
+        <v>319</v>
+      </c>
+      <c r="K20" t="s">
+        <v>249</v>
+      </c>
+      <c r="L20" t="s">
+        <v>28</v>
+      </c>
+      <c r="M20" t="s">
+        <v>250</v>
+      </c>
+      <c r="N20" t="s">
         <v>251</v>
       </c>
-      <c r="J20" t="s">
-        <v>205</v>
-      </c>
-      <c r="K20" t="s">
-        <v>156</v>
-      </c>
-      <c r="L20" t="s">
-        <v>25</v>
-      </c>
-      <c r="M20" t="s">
-        <v>157</v>
-      </c>
-      <c r="N20" t="s">
-        <v>158</v>
-      </c>
       <c r="O20" t="s">
-        <v>274</v>
+        <v>252</v>
       </c>
       <c r="P20" t="s">
-        <v>297</v>
+        <v>253</v>
       </c>
       <c r="Q20" t="s">
-        <v>319</v>
+        <v>254</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>159</v>
+        <v>255</v>
       </c>
       <c r="B21" t="s">
-        <v>160</v>
+        <v>256</v>
       </c>
       <c r="C21" t="s">
-        <v>161</v>
+        <v>257</v>
       </c>
       <c r="D21" t="s">
-        <v>162</v>
+        <v>258</v>
       </c>
       <c r="E21" t="s">
         <v>21</v>
       </c>
       <c r="F21" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="G21" t="s">
         <v>23</v>
       </c>
       <c r="H21" t="s">
-        <v>229</v>
+        <v>259</v>
       </c>
       <c r="I21" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="J21" t="s">
-        <v>206</v>
+        <v>320</v>
       </c>
       <c r="K21" t="s">
-        <v>163</v>
+        <v>261</v>
       </c>
       <c r="L21" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M21" t="s">
-        <v>164</v>
+        <v>262</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>263</v>
       </c>
       <c r="O21" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="P21" t="s">
-        <v>298</v>
+        <v>265</v>
       </c>
       <c r="Q21" t="s">
-        <v>320</v>
+        <v>266</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>166</v>
+        <v>267</v>
       </c>
       <c r="B22" t="s">
-        <v>167</v>
+        <v>268</v>
       </c>
       <c r="C22" t="s">
-        <v>168</v>
+        <v>269</v>
       </c>
       <c r="D22" t="s">
-        <v>169</v>
+        <v>270</v>
       </c>
       <c r="E22" t="s">
         <v>21</v>
       </c>
       <c r="F22" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="G22" t="s">
         <v>23</v>
       </c>
       <c r="H22" t="s">
-        <v>230</v>
+        <v>271</v>
       </c>
       <c r="I22" t="s">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="J22" t="s">
-        <v>207</v>
+        <v>321</v>
       </c>
       <c r="K22" t="s">
-        <v>170</v>
+        <v>273</v>
       </c>
       <c r="L22" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M22" t="s">
-        <v>171</v>
+        <v>274</v>
       </c>
       <c r="N22" t="s">
-        <v>172</v>
+        <v>275</v>
       </c>
       <c r="O22" t="s">
         <v>276</v>
       </c>
       <c r="P22" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="Q22" t="s">
-        <v>321</v>
+        <v>278</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="B23" t="s">
-        <v>174</v>
+        <v>280</v>
       </c>
       <c r="C23" t="s">
-        <v>175</v>
+        <v>281</v>
       </c>
       <c r="D23" t="s">
-        <v>176</v>
+        <v>282</v>
       </c>
       <c r="E23" t="s">
         <v>21</v>
       </c>
       <c r="F23" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="G23" t="s">
         <v>23</v>
       </c>
       <c r="H23" t="s">
-        <v>231</v>
+        <v>283</v>
       </c>
       <c r="I23" t="s">
-        <v>254</v>
+        <v>284</v>
       </c>
       <c r="J23" t="s">
-        <v>208</v>
+        <v>322</v>
       </c>
       <c r="K23" t="s">
-        <v>177</v>
+        <v>285</v>
       </c>
       <c r="L23" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M23" t="s">
-        <v>178</v>
+        <v>286</v>
       </c>
       <c r="N23" t="s">
-        <v>179</v>
+        <v>287</v>
       </c>
       <c r="O23" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="P23" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="Q23" t="s">
-        <v>322</v>
+        <v>290</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>180</v>
+        <v>291</v>
       </c>
       <c r="B24" t="s">
-        <v>181</v>
+        <v>292</v>
       </c>
       <c r="C24" t="s">
-        <v>182</v>
+        <v>293</v>
       </c>
       <c r="D24" t="s">
-        <v>183</v>
+        <v>294</v>
       </c>
       <c r="E24" t="s">
         <v>21</v>
       </c>
       <c r="F24" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="G24" t="s">
         <v>23</v>
       </c>
       <c r="H24" t="s">
-        <v>232</v>
+        <v>295</v>
       </c>
       <c r="I24" t="s">
-        <v>255</v>
+        <v>296</v>
       </c>
       <c r="J24" t="s">
-        <v>209</v>
+        <v>323</v>
       </c>
       <c r="K24" t="s">
-        <v>184</v>
+        <v>297</v>
       </c>
       <c r="L24" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M24" t="s">
-        <v>185</v>
+        <v>298</v>
       </c>
       <c r="N24" t="s">
-        <v>186</v>
+        <v>299</v>
       </c>
       <c r="O24" t="s">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="P24" t="s">
         <v>301</v>
       </c>
       <c r="Q24" t="s">
-        <v>323</v>
+        <v>302</v>
       </c>
     </row>
   </sheetData>

--- a/DesignData/Excel_Masters/CharacterAssets_Master.xlsx
+++ b/DesignData/Excel_Masters/CharacterAssets_Master.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnrealCpp\Paradise\DesignData\Excel_Masters\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="348">
   <si>
     <t>---</t>
   </si>
@@ -84,414 +84,477 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Anubis/Ani/Anubis_Base_Battle_Idle_Anim_Anubis_Base_Battle_Idle1.Anubis_Base_Battle_Idle_Anim_Anubis_Base_Battle_Idle1</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Anubis.Anubis</t>
+  </si>
+  <si>
+    <t>Legendary</t>
+  </si>
+  <si>
+    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_AreaUltimate.GA_AreaUltimate_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Ultimate.GE_Damage_Ultimate_C'",ProjectileClass=None)</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Ultimate.AM_Anubis_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Book.AM_Anubis_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Book_Skill.AM_Anubis_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Gun.AM_Anubis_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Gun_Skill.AM_Anubis_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Melee.AM_Anubis_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Melee_Skill.AM_Anubis_Melee_Skill")))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Anubis.DA_CharFX_Anubis",BasicAttackTag=(TagName="FX.Character.Anubis.BasicAttack"),SkillTag=(TagName="FX.Character.Anubis.WeaponSkill"),UltimateTag=(TagName="FX.Character.Anubis.Ultimate"),UltimateHitTag=(TagName="FX.Character.Anubis.UltimateHit"),HitTag=(TagName="FX.Character.Anubis.Hit"),DeathTag=(TagName="FX.Character.Anubis.Death"))</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Anubis.Ultimate")</t>
+  </si>
+  <si>
+    <t>(TagName="Unit.Faction.Friendly.Player")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Anubis/SKM_Anubis_Base.SKM_Anubis_Base</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Anubis.Icon_Anubis</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Anubis/ABP_Anubis.ABP_Anubis_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Damage.AM_Anubis_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Dead.AM_Anubis_Dead</t>
+  </si>
+  <si>
+    <t>Char_Army</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Army.Icon_Army</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Army.Icon_Army</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Army/Ani/Army_Base_Battle_Idle.Army_Base_Battle_Idle</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Army.Army</t>
+  </si>
+  <si>
+    <t>Common</t>
+  </si>
+  <si>
+    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_AreaUltimate.GA_AreaUltimate_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Heal_Ultimate.GE_Heal_Ultimate_C'",ProjectileClass=None)</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Ultimate.AM_Army_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Book.AM_Army_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Book_SKill.AM_Army_Book_SKill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Gun.AM_Army_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Gun_Skill.AM_Army_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Melee.AM_Army_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Melee_Skill.AM_Army_Melee_Skill")))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Army.DA_CharFX_Army",BasicAttackTag=(TagName="FX.Character.Army.BasicAttack"),SkillTag=(TagName="FX.Character.Army.WeaponSkill"),UltimateTag=(TagName="FX.Character.Army.Ultimate"),UltimateHitTag=(TagName="FX.Character.Army.UltimateHit"),HitTag=(TagName="FX.Character.Army.Hit"),DeathTag=(TagName="FX.Character.Army.Death"))</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Army.Ultimate")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Army/SKM_Army_Base.SKM_Army_Base</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Army.Icon_Army</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Army/ABP_Army.ABP_Army_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Damage.AM_Army_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Dead.AM_Army_Dead</t>
+  </si>
+  <si>
+    <t>Char_Bard</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Bard.Icon_Bard</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Bard.Icon_Bard</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Bard/Bard_Modify/Ani/Bard_Base_Battle_Idle.Bard_Base_Battle_Idle</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Bard.Bard</t>
+  </si>
+  <si>
+    <t>Uncommon</t>
+  </si>
+  <si>
+    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_ProjectileUtimate.GA_ProjectileUtimate_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Ultimate.GE_Damage_Ultimate_C'",ProjectileClass="/Script/Engine.BlueprintGeneratedClass'/Game/Blueprints/Object/Projectile/BP_Bullet.BP_Bullet_C'")</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Ultimate.AM_Bard_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Book.AM_Bard_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Book_Skill.AM_Bard_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Gun.AM_Bard_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Gun_Skill.AM_Bard_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Melee.AM_Bard_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Melee_Skill.AM_Bard_Melee_Skill")))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Bard.DA_CharFX_Bard",BasicAttackTag=(TagName="FX.Character.Bard.BasicAttack"),SkillTag=(TagName="FX.Character.Bard.WeaponSkill"),UltimateTag=(TagName="FX.Character.Bard.Ultimate"),UltimateHitTag=(TagName="FX.Character.Bard.UltimateHit"),HitTag=(TagName="FX.Character.Bard.Hit"),DeathTag=(TagName="FX.Character.Bard.Death"))</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Bard.Ultimate")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Bard/Bard_Modify/SKM_Bard_Base_Modified.SKM_Bard_Base_Modified</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Bard.Icon_Bard</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Bard/ABP_Bard.ABP_Bard_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Damage.AM_Bard_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Dead.AM_Bard_Dead</t>
+  </si>
+  <si>
+    <t>Char_Binder</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Binder.Icon_Binder</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Binder.Icon_Binder</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Binder/Ani/Binder_Base_Battle_Idle.Binder_Base_Battle_Idle</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Binder.Binder</t>
+  </si>
+  <si>
+    <t>Epic</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Ultimate.AM_Binder_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Book.AM_Binder_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Book_Skill.AM_Binder_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Gun.AM_Binder_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Gun_Skill.AM_Binder_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Melee.AM_Binder_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Melee_Skill.AM_Binder_Melee_Skill")))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Binder.DA_CharFX_Binder",BasicAttackTag=(TagName="FX.Character.Binder.BasicAttack"),SkillTag=(TagName="FX.Character.Binder.WeaponSkill"),UltimateTag=(TagName="FX.Character.Binder.Ultimate"),UltimateHitTag=(TagName="FX.Character.Binder.UltimateHit"),HitTag=(TagName="FX.Character.Binder.Hit"),DeathTag=(TagName="FX.Character.Binder.Death"))</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Binder.Ultimate")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Player/Binder/SKM_Binder_Base.SKM_Binder_Base</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Binder.Icon_Binder</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Binder/ABP_BInder.ABP_Binder_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Damage.AM_Binder_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Dead.AM_Binder_Dead</t>
+  </si>
+  <si>
+    <t>Char_Courier</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Courier.Icon_Courier</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Courier.Icon_Courier</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Courier/Ani/Courier_Base_Lobby_Idle_Anim_Take_0011.Courier_Base_Lobby_Idle_Anim_Take_0011</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Courier.Courier</t>
+  </si>
+  <si>
+    <t>Rare</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Ultimate.AM_Courier_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Book.AM_Courier_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Book_Skill.AM_Courier_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Gun.AM_Courier_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Gun_Skill.AM_Courier_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Melee.AM_Courier_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Melee_Skill.AM_Courier_Melee_Skill")))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Courier.DA_CharFX_Courier",BasicAttackTag=(TagName="FX.Character.Courier.BasicAttack"),SkillTag=(TagName="FX.Character.Courier.WeaponSkill"),UltimateTag=(TagName="FX.Character.Courier.Ultimate"),UltimateHitTag=(TagName="FX.Character.Courier.UltimateHit"),HitTag=(TagName="FX.Character.Courier.Hit"),DeathTag=(TagName="FX.Character.Courier.Death"))</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Courier.Ultimate")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Courier/SKM_Courier_Base2.SKM_Courier_Base2</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Courier.Icon_Courier</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Courier/ABP_Courier.ABP_Courier_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Damage.AM_Courier_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Dead.AM_Courier_Dead</t>
+  </si>
+  <si>
+    <t>Char_Demonia</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Demonia.Icon_Demonia</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Demonia.Icon_Demonia</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Demonia/Ani/Demonia_Base_Battle_Idle.Demonia_Base_Battle_Idle</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Demonia.Demonia</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Ultimate.AM_Demonia_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Book.AM_Demonia_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Book_Skill.AM_Demonia_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Gun.AM_Demonia_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Gun_Skill.AM_Demonia_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Melee.AM_Demonia_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Melee_Skill.AM_Demonia_Melee_Skill")))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Demonia.DA_CharFX_Demonia",BasicAttackTag=(TagName="FX.Character.Demonia.BasicAttack"),SkillTag=(TagName="FX.Character.Demonia.WeaponSkill"),UltimateTag=(TagName="FX.Character.Demonia.Ultimate"),UltimateHitTag=(TagName="FX.Character.Demonia.UltimateHit"),HitTag=(TagName="FX.Character.Demonia.Hit"),DeathTag=(TagName="FX.Character.Demonia.Death"))</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Demonia.Ultimate")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Demonia/SKM_Demonia_Base.SKM_Demonia_Base</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Demonia.Icon_Demonia</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Demonia/ABP_Demonia.ABP_Demonia_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Damage.AM_Demonia_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Dead.AM_Demonia_Dead</t>
+  </si>
+  <si>
+    <t>Char_Enchanter</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Enchanter.Icon_Enchanter</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Enchanter.Icon_Enchanter</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Enchanter/Ani/Enchanter_Base_Battle_Idle_Anim_Take_001.Enchanter_Base_Battle_Idle_Anim_Take_001</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Enchanter.Enchanter</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Ultimate.AM_Enchanter_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Book.AM_Enchanter_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Book_Skill.AM_Enchanter_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Gun.AM_Enchanter_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Gun_Skill.AM_Enchanter_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Melee.AM_Enchanter_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Melee_Skill.AM_Enchanter_Melee_Skill")))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Enchanter.DA_CharFX_Enchanter",BasicAttackTag=(TagName="FX.Character.Enchanter.BasicAttack"),SkillTag=(TagName="FX.Character.Enchanter.WeaponSkill"),UltimateTag=(TagName="FX.Character.Enchanter.Ultimate"),UltimateHitTag=(TagName="FX.Character.Enchanter.UltimateHit"),HitTag=(TagName="FX.Character.Enchanter.Hit"),DeathTag=(TagName="FX.Character.Enchanter.Death"))</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Enchanter.Ultimate")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Enchanter/SKM_Enchanter_Base.SKM_Enchanter_Base</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Enchanter.Icon_Enchanter</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Enchanter/ABP_Enchanter.ABP_Enchanter_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Damage.AM_Enchanter_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Dead.AM_Enchanter_Dead</t>
+  </si>
+  <si>
+    <t>Char_Guard</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Guard.Icon_Guard</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Guard.Icon_Guard</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Guard/Ani/Guard_Base_Battle_Idle.Guard_Base_Battle_Idle</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Guard.Guard</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Ultimate.AM_Guard_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Book.AM_Guard_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Book_Skill.AM_Guard_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Gun.AM_Guard_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Gun_Skill.AM_Guard_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Melee.AM_Guard_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Melee_Skill.AM_Guard_Melee_Skill")))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Guard.DA_CharFX_Guard",BasicAttackTag=(TagName="FX.Character.Guard.BasicAttack"),SkillTag=(TagName="FX.Character.Guard.WeaponSkill"),UltimateTag=(TagName="FX.Character.Guard.Ultimate"),UltimateHitTag=(TagName="FX.Character.Guard.UltimateHit"),HitTag=(TagName="FX.Character.Guard.Hit"),DeathTag=(TagName="FX.Character.Guard.Death"))</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Guard.Ultimate")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Guard/SKM_Guard_Base.SKM_Guard_Base</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Guard.Icon_Guard</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Guard/ABP_Guard.ABP_Guard_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Damage.AM_Guard_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Dead.AM_Guard_Dead</t>
+  </si>
+  <si>
+    <t>Char_Hermit</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Hermit.Icon_Hermit</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Hermit.Icon_Hermit</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Hermit/Ani/Hermit_Base_Battle_Idle_Anim_Hermit_Battle_Idle.Hermit_Base_Battle_Idle_Anim_Hermit_Battle_Idle</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Hermit.Hermit</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Ultimate.AM_Hermit_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Book.AM_Hermit_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Book_Skill.AM_Hermit_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Gun.AM_Hermit_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Gun_Skill.AM_Hermit_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Melee.AM_Hermit_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Melee_Skill.AM_Hermit_Melee_Skill")))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Hermit.DA_CharFX_Hermit",BasicAttackTag=(TagName="FX.Character.Hermit.BasicAttack"),SkillTag=(TagName="FX.Character.Hermit.WeaponSkill"),UltimateTag=(TagName="FX.Character.Hermit.Ultimate"),UltimateHitTag=(TagName="FX.Character.Hermit.UltimateHit"),HitTag=(TagName="FX.Character.Hermit.Hit"),DeathTag=(TagName="FX.Character.Hermit.Death"))</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Hermit.Ultimate")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Hermit/SKM_Hermit_Base.SKM_Hermit_Base</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Hermit.Icon_Hermit</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Hermit/ABP_Hermit.ABP_Hermit_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Damage.AM_Hermit_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Dead.AM_Hermit_Dead</t>
+  </si>
+  <si>
+    <t>Char_Hornet</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Hornet.Icon_Hornet</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Hornet.Icon_Hornet</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Hornet/Ani/Hornet_Base_Battle_Idle.Hornet_Base_Battle_Idle</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Hornet.Hornet</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Ultimate.AM_Hornet_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Book.AM_Hornet_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Book_Skill.AM_Hornet_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Gun.AM_Hornet_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Gun_Skill.AM_Hornet_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Melee.AM_Hornet_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Melee_Skill.AM_Hornet_Melee_Skill")))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Hornet.DA_CharFX_Hornet",BasicAttackTag=(TagName="FX.Character.Hornet.BasicAttack"),SkillTag=(TagName="FX.Character.Hornet.WeaponSkill"),UltimateTag=(TagName="FX.Character.Hornet.Ultimate"),UltimateHitTag=(TagName="FX.Character.Hornet.UltimateHit"),HitTag=(TagName="FX.Character.Hornet.Hit"),DeathTag=(TagName="FX.Character.Hornet.Death"))</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Hornet.Ultimate")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Hornet/SKM_Hornet_Base.SKM_Hornet_Base</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Hornet.Icon_Hornet</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Hornet/ABP_Hornet.ABP_Hornet_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Damage.AM_Hornet_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Dead.AM_Hornet_Dead</t>
+  </si>
+  <si>
+    <t>Char_Looter</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Looter.Icon_Looter</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Looter.Icon_Looter</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Looter/Ani/Looter_Base_Battle_Idle.Looter_Base_Battle_Idle</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Looter.Looter</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Ultimate.AM_Looter_Ultimate</t>
+  </si>
+  <si>
+    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Book.AM_Looter_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Book_Skill.AM_Looter_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Gun.AM_Looter_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Gun_Skill.AM_Looter_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Melee.AM_Looter_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Melee_Skill.AM_Looter_Melee_Skill")))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Looter.DA_CharFX_Looter",BasicAttackTag=(TagName="FX.Character.Looter.BasicAttack"),SkillTag=(TagName="FX.Character.Looter.WeaponSkill"),UltimateTag=(TagName="FX.Character.Looter.Ultimate"),UltimateHitTag=(TagName="FX.Character.Looter.UltimateHit"),HitTag=(TagName="FX.Character.Looter.Hit"),DeathTag=(TagName="FX.Character.Looter.Death"))</t>
+  </si>
+  <si>
+    <t>(TagName="FX.Character.Looter.Ultimate")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Looter/SKM_Looter_Base.SKM_Looter_Base</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Looter.Icon_Looter</t>
+  </si>
+  <si>
     <t>None</t>
   </si>
   <si>
-    <t>Legendary</t>
-  </si>
-  <si>
-    <t>(AbilityClass=None,EffectClass=None,ProjectileClass=None)</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Ultimate.AM_Anubis_Ultimate</t>
-  </si>
-  <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Book.AM_Anubis_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Book_Skill.AM_Anubis_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Gun.AM_Anubis_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Gun_Skill.AM_Anubis_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Melee.AM_Anubis_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Melee_Skill.AM_Anubis_Melee_Skill")))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Anubis.DA_CharFX_Anubis",BasicAttackTag=(TagName="FX.Character.Anubis.BasicAttack"),SkillTag=(TagName="FX.Character.Anubis.WeaponSkill"),UltimateTag=(TagName="FX.Character.Anubis.Ultimate"),UltimateHitTag=(TagName="FX.Character.Anubis.UltimateHit"),HitTag=(TagName="FX.Character.Anubis.Hit"),DeathTag=(TagName="FX.Character.Anubis.Death"))</t>
-  </si>
-  <si>
-    <t>(TagName="FX.Character.Anubis.Ultimate")</t>
-  </si>
-  <si>
-    <t>(TagName="Unit.Faction.Friendly.Player")</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Anubis/SKM_Anubis_Base.SKM_Anubis_Base</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Anubis.Icon_Anubis</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Anubis/ABP_Anubis.ABP_Anubis_C'</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Damage.AM_Anubis_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Dead.AM_Anubis_Dead</t>
-  </si>
-  <si>
-    <t>Char_Army</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Army.Icon_Army</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Army.Icon_Army</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Army/Ani/Army_Base_Battle_Idle.Army_Base_Battle_Idle</t>
-  </si>
-  <si>
-    <t>Common</t>
-  </si>
-  <si>
-    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_AreaUltimate.GA_AreaUltimate_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Heal_Ultimate.GE_Heal_Ultimate_C'",ProjectileClass=None)</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Ultimate.AM_Army_Ultimate</t>
-  </si>
-  <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Book.AM_Army_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Book_SKill.AM_Army_Book_SKill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Gun.AM_Army_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Gun_Skill.AM_Army_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Melee.AM_Army_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Melee_Skill.AM_Army_Melee_Skill")))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Army.DA_CharFX_Army",BasicAttackTag=(TagName="FX.Character.Army.BasicAttack"),SkillTag=(TagName="FX.Character.Army.WeaponSkill"),UltimateTag=(TagName="FX.Character.Army.Ultimate"),UltimateHitTag=(TagName="FX.Character.Army.UltimateHit"),HitTag=(TagName="FX.Character.Army.Hit"),DeathTag=(TagName="FX.Character.Army.Death"))</t>
-  </si>
-  <si>
-    <t>(TagName="FX.Character.Army.Ultimate")</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Army/SKM_Army_Base.SKM_Army_Base</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Army.Icon_Army</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Army/ABP_Army.ABP_Army_C'</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Damage.AM_Army_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Dead.AM_Army_Dead</t>
-  </si>
-  <si>
-    <t>Char_Bard</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Bard.Icon_Bard</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Bard.Icon_Bard</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Bard/Bard_Modify/Ani/Bard_Base_Battle_Idle.Bard_Base_Battle_Idle</t>
-  </si>
-  <si>
-    <t>Uncommon</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Ultimate.AM_Bard_Ultimate</t>
-  </si>
-  <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Book.AM_Bard_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Book_Skill.AM_Bard_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Gun.AM_Bard_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Gun_Skill.AM_Bard_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Melee.AM_Bard_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Melee_Skill.AM_Bard_Melee_Skill")))</t>
-  </si>
-  <si>
-    <t>(TagName="FX.Character.Bard.Ultimate")</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Bard/Bard_Modify/SKM_Bard_Base_Modified.SKM_Bard_Base_Modified</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Bard.Icon_Bard</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Bard/ABP_Bard.ABP_Bard_C'</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Damage.AM_Bard_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Dead.AM_Bard_Dead</t>
-  </si>
-  <si>
-    <t>Char_Binder</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Binder.Icon_Binder</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Binder.Icon_Binder</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Binder/Ani/Binder_Base_Battle_Idle.Binder_Base_Battle_Idle</t>
-  </si>
-  <si>
-    <t>Epic</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Ultimate.AM_Binder_Ultimate</t>
-  </si>
-  <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Book.AM_Binder_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Book_Skill.AM_Binder_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Gun.AM_Binder_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Gun_Skill.AM_Binder_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Melee.AM_Binder_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Melee_Skill.AM_Binder_Melee_Skill")))</t>
-  </si>
-  <si>
-    <t>(TagName="FX.Character.Binder.Ultimate")</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Player/Binder/SKM_Binder_Base.SKM_Binder_Base</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Binder.Icon_Binder</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Binder/ABP_BInder.ABP_BInder_C'</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Damage.AM_Binder_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Dead.AM_Binder_Dead</t>
-  </si>
-  <si>
-    <t>Char_Courier</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Courier.Icon_Courier</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Courier.Icon_Courier</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Courier/Ani/Courier_Base_Lobby_Idle_Anim_Take_0011.Courier_Base_Lobby_Idle_Anim_Take_0011</t>
-  </si>
-  <si>
-    <t>Rare</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Ultimate.AM_Courier_Ultimate</t>
-  </si>
-  <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Book.AM_Courier_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Book_Skill.AM_Courier_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Gun.AM_Courier_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Gun_Skill.AM_Courier_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Melee.AM_Courier_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Melee_Skill.AM_Courier_Melee_Skill")))</t>
-  </si>
-  <si>
-    <t>(TagName="FX.Character.Courier.Ultimate")</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Courier/SKM_Courier_Base2.SKM_Courier_Base2</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Courier.Icon_Courier</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Courier/ABP_Courier.ABP_Courier_C'</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Damage.AM_Courier_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Dead.AM_Courier_Dead</t>
-  </si>
-  <si>
-    <t>Char_Demonia</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Demonia.Icon_Demonia</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Demonia.Icon_Demonia</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Demonia/Ani/Demonia_Base_Battle_Idle.Demonia_Base_Battle_Idle</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Ultimate.AM_Demonia_Ultimate</t>
-  </si>
-  <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Book.AM_Demonia_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Book_Skill.AM_Demonia_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Gun.AM_Demonia_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Gun_Skill.AM_Demonia_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Melee.AM_Demonia_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Melee_Skill.AM_Demonia_Melee_Skill")))</t>
-  </si>
-  <si>
-    <t>(TagName="FX.Character.Demonia.Ultimate")</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Demonia/SKM_Demonia_Base.SKM_Demonia_Base</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Demonia.Icon_Demonia</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Demonia/ABP_Demonia.ABP_Demonia_C'</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Damage.AM_Demonia_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Dead.AM_Demonia_Dead</t>
-  </si>
-  <si>
-    <t>Char_Enchanter</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Enchanter.Icon_Enchanter</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Enchanter.Icon_Enchanter</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Enchanter/Ani/Enchanter_Base_Battle_Idle_Anim_Take_001.Enchanter_Base_Battle_Idle_Anim_Take_001</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Ultimate.AM_Enchanter_Ultimate</t>
-  </si>
-  <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Book.AM_Enchanter_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Book_Skill.AM_Enchanter_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Gun.AM_Enchanter_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Gun_Skill.AM_Enchanter_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Melee.AM_Enchanter_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Melee_Skill.AM_Enchanter_Melee_Skill")))</t>
-  </si>
-  <si>
-    <t>(TagName="FX.Character.Enchanter.Ultimate")</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Enchanter/SKM_Enchanter_Base.SKM_Enchanter_Base</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Enchanter.Icon_Enchanter</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Enchanter/ABP_Enchanter.ABP_Enchanter_C'</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Damage.AM_Enchanter_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Dead.AM_Enchanter_Dead</t>
-  </si>
-  <si>
-    <t>Char_Guard</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Guard.Icon_Guard</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Guard.Icon_Guard</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Guard/Ani/Guard_Base_Battle_Idle.Guard_Base_Battle_Idle</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Ultimate.AM_Guard_Ultimate</t>
-  </si>
-  <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Book.AM_Guard_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Book_Skill.AM_Guard_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Gun.AM_Guard_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Gun_Skill.AM_Guard_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Melee.AM_Guard_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Melee_Skill.AM_Guard_Melee_Skill")))</t>
-  </si>
-  <si>
-    <t>(TagName="FX.Character.Guard.Ultimate")</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Guard/SKM_Guard_Base.SKM_Guard_Base</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Guard.Icon_Guard</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Guard/ABP_Guard.ABP_Guard_C'</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Damage.AM_Guard_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Dead.AM_Guard_Dead</t>
-  </si>
-  <si>
-    <t>Char_Hermit</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Hermit.Icon_Hermit</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Hermit.Icon_Hermit</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Hermit/Ani/Hermit_Base_Battle_Idle_Anim_Hermit_Battle_Idle.Hermit_Base_Battle_Idle_Anim_Hermit_Battle_Idle</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Ultimate.AM_Hermit_Ultimate</t>
-  </si>
-  <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Book.AM_Hermit_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Book_Skill.AM_Hermit_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Gun.AM_Hermit_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Gun_Skill.AM_Hermit_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Melee.AM_Hermit_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Melee_Skill.AM_Hermit_Melee_Skill")))</t>
-  </si>
-  <si>
-    <t>(TagName="FX.Character.Hermit.Ultimate")</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Hermit/SKM_Hermit_Base.SKM_Hermit_Base</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Hermit.Icon_Hermit</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Hermit/ABP_Hermit.ABP_Hermit_C'</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Damage.AM_Hermit_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Dead.AM_Hermit_Dead</t>
-  </si>
-  <si>
-    <t>Char_Hornet</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Hornet.Icon_Hornet</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Hornet.Icon_Hornet</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Hornet/Ani/Hornet_Base_Battle_Idle.Hornet_Base_Battle_Idle</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Ultimate.AM_Hornet_Ultimate</t>
-  </si>
-  <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Book.AM_Hornet_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Book_Skill.AM_Hornet_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Gun.AM_Hornet_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Gun_Skill.AM_Hornet_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Melee.AM_Hornet_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Melee_Skill.AM_Hornet_Melee_Skill")))</t>
-  </si>
-  <si>
-    <t>(TagName="FX.Character.Hornet.Ultimate")</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Hornet/SKM_Hornet_Base.SKM_Hornet_Base</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Hornet.Icon_Hornet</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Hornet/ABP_Hornet.ABP_Hornet_C'</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Damage.AM_Hornet_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Dead.AM_Hornet_Dead</t>
-  </si>
-  <si>
-    <t>Char_Looter</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Looter.Icon_Looter</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Looter.Icon_Looter</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Looter/Ani/Looter_Base_Battle_Idle.Looter_Base_Battle_Idle</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Ultimate.AM_Looter_Ultimate</t>
-  </si>
-  <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Book.AM_Looter_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Book_Skill.AM_Looter_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Gun.AM_Looter_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Gun_Skill.AM_Looter_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Melee.AM_Looter_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Melee_Skill.AM_Looter_Melee_Skill")))</t>
-  </si>
-  <si>
-    <t>(TagName="FX.Character.Looter.Ultimate")</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Looter/SKM_Looter_Base.SKM_Looter_Base</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Looter.Icon_Looter</t>
-  </si>
-  <si>
     <t>/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Damage.AM_Looter_Damage</t>
   </si>
   <si>
@@ -510,12 +573,18 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Maid/Ani/Maid_Base_Idle_Battle.Maid_Base_Idle_Battle</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Maid.Maid</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Ultimate.AM_Maid_Ultimate</t>
   </si>
   <si>
     <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Book.AM_Maid_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Book_Skill.AM_Maid_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Gun.AM_Maid_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Gun_Skill.AM_Maid_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Melee.AM_Maid_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Melee_Skill.AM_Maid_Melee_Skill")))</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Maid.DA_CharFX_Maid",BasicAttackTag=(TagName="FX.Character.Maid.BasicAttack"),SkillTag=(TagName="FX.Character.Maid.WeaponSkill"),UltimateTag=(TagName="FX.Character.Maid.Ultimate"),UltimateHitTag=(TagName="FX.Character.Maid.UltimateHit"),HitTag=(TagName="FX.Character.Maid.Hit"),DeathTag=(TagName="FX.Character.Maid.Death"))</t>
+  </si>
+  <si>
     <t>(TagName="FX.Character.Maid.Ultimate")</t>
   </si>
   <si>
@@ -546,12 +615,18 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Merry/Ani/Merry_Base_Battle_Idle.Merry_Base_Battle_Idle</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Merry.Merry</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Ultimate.AM_Merry_Ultimate</t>
   </si>
   <si>
     <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Book.AM_Merry_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Book_Skill.AM_Merry_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Gun.AM_Merry_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Gun_Skill.AM_Merry_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Melee.AM_Merry_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Melee_Skill.AM_Merry_Melee_Skill")))</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Merry.DA_CharFX_Merry",BasicAttackTag=(TagName="FX.Character.Merry.BasicAttack"),SkillTag=(TagName="FX.Character.Merry.WeaponSkill"),UltimateTag=(TagName="FX.Character.Merry.Ultimate"),UltimateHitTag=(TagName="FX.Character.Merry.UltimateHit"),HitTag=(TagName="FX.Character.Merry.Hit"),DeathTag=(TagName="FX.Character.Merry.Death"))</t>
+  </si>
+  <si>
     <t>(TagName="FX.Character.Merry.Ultimate")</t>
   </si>
   <si>
@@ -582,12 +657,18 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Muzzle/Ani/Muzzle_Base_Lobby_Idle_NoWeapon.Muzzle_Base_Lobby_Idle_NoWeapon</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Muzzle.Muzzle</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Ultimate.AM_Muzzle_Ultimate</t>
   </si>
   <si>
     <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Book.AM_Muzzle_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Book_Skill.AM_Muzzle_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Gun.AM_Muzzle_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Gun_Skill.AM_Muzzle_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Melee.AM_Muzzle_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Melee_Skill.AM_Muzzle_Melee_Skill")))</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Muzzle.DA_CharFX_Muzzle",BasicAttackTag=(TagName="FX.Character.Muzzle.BasicAttack"),SkillTag=(TagName="FX.Character.Muzzle.WeaponSkill"),UltimateTag=(TagName="FX.Character.Muzzle.Ultimate"),UltimateHitTag=(TagName="FX.Character.Muzzle.UltimateHit"),HitTag=(TagName="FX.Character.Muzzle.Hit"),DeathTag=(TagName="FX.Character.Muzzle.Death"))</t>
+  </si>
+  <si>
     <t>(TagName="FX.Character.Muzzle.Ultimate")</t>
   </si>
   <si>
@@ -618,12 +699,18 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Noble/Ani/Noble_Base_Battle_Idle_Anim_Take_0011.Noble_Base_Battle_Idle_Anim_Take_0011</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Noble.Noble</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Ultimate.AM_Noble_Ultimate</t>
   </si>
   <si>
     <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Book.AM_Noble_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Book_Skill.AM_Noble_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Gun.AM_Noble_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Gun_Skill.AM_Noble_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Melee.AM_Noble_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Melee_Skill.AM_Noble_Melee_Skill")))</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Noble.DA_CharFX_Noble",BasicAttackTag=(TagName="FX.Character.Noble.BasicAttack"),SkillTag=(TagName="FX.Character.Noble.WeaponSkill"),UltimateTag=(TagName="FX.Character.Noble.Ultimate"),UltimateHitTag=(TagName="FX.Character.Noble.UltimateHit"),HitTag=(TagName="FX.Character.Noble.Hit"),DeathTag=(TagName="FX.Character.Noble.Death"))</t>
+  </si>
+  <si>
     <t>(TagName="FX.Character.Noble.Ultimate")</t>
   </si>
   <si>
@@ -654,12 +741,18 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Nurse/Ani/Nurse_Base_Battle_Idle.Nurse_Base_Battle_Idle</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Nurse.Nurse</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Ultimate.AM_Nurse_Ultimate</t>
   </si>
   <si>
     <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Book.AM_Nurse_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Book_Skill.AM_Nurse_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Gun.AM_Nurse_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Gun_Skill.AM_Nurse_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Melee.AM_Nurse_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Melee_Skill.AM_Nurse_Melee_Skill")))</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Nurse.DA_CharFX_Nurse",BasicAttackTag=(TagName="FX.Character.Nurse.BasicAttack"),SkillTag=(TagName="FX.Character.Nurse.WeaponSkill"),UltimateTag=(TagName="FX.Character.Nurse.Ultimate"),UltimateHitTag=(TagName="FX.Character.Nurse.UltimateHit"),HitTag=(TagName="FX.Character.Nurse.Hit"),DeathTag=(TagName="FX.Character.Nurse.Death"))</t>
+  </si>
+  <si>
     <t>(TagName="FX.Character.Nurse.Ultimate")</t>
   </si>
   <si>
@@ -690,12 +783,18 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Outsider/Ani/Outsider_Base_Battle_Idle.Outsider_Base_Battle_Idle</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Outsider.Outsider</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Ultimate.AM_Outsider_Ultimate</t>
   </si>
   <si>
     <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Book.AM_Outsider_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Book_Skill.AM_Outsider_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Gun.AM_Outsider_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Gun_Skill.AM_Outsider_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Melee.AM_Outsider_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Melee_Skill.AM_Outsider_Melee_Skill")))</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Outsider.DA_CharFX_Outsider",BasicAttackTag=(TagName="FX.Character.Outsider.BasicAttack"),SkillTag=(TagName="FX.Character.Outsider.WeaponSkill"),UltimateTag=(TagName="FX.Character.Outsider.Ultimate"),UltimateHitTag=(TagName="FX.Character.Outsider.UltimateHit"),HitTag=(TagName="FX.Character.Outsider.Hit"),DeathTag=(TagName="FX.Character.Outsider.Death"))</t>
+  </si>
+  <si>
     <t>(TagName="FX.Character.Outsider.Ultimate")</t>
   </si>
   <si>
@@ -726,12 +825,18 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Pioneer/Ani/Pioneer_Base_Battle_Idle.Pioneer_Base_Battle_Idle</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Pioneer.Pioneer</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Ultimate.AM_Pioneer_Ultimate</t>
   </si>
   <si>
     <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Book.AM_Pioneer_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Book_Skill.AM_Pioneer_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Gun.AM_Pioneer_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Gun_Skill.AM_Pioneer_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Melee.AM_Pioneer_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Melee_Skill.AM_Pioneer_Melee_Skill")))</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Pioneer.DA_CharFX_Pioneer",BasicAttackTag=(TagName="FX.Character.Pioneer.BasicAttack"),SkillTag=(TagName="FX.Character.Pioneer.WeaponSkill"),UltimateTag=(TagName="FX.Character.Pioneer.Ultimate"),UltimateHitTag=(TagName="FX.Character.Pioneer.UltimateHit"),HitTag=(TagName="FX.Character.Pioneer.Hit"),DeathTag=(TagName="FX.Character.Pioneer.Death"))</t>
+  </si>
+  <si>
     <t>(TagName="FX.Character.Pioneer.Ultimate")</t>
   </si>
   <si>
@@ -762,12 +867,18 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Rogue/Ani/Rogue_Base_Battle_Idle_Anim_Rogue_Base_Battle_Idle.Rogue_Base_Battle_Idle_Anim_Rogue_Base_Battle_Idle</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Rogue.Rogue</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Ultimate.AM_Rogue_Ultimate</t>
   </si>
   <si>
     <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Book.AM_Rogue_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Book_Skill.AM_Rogue_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Gun.AM_Rogue_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Gun_Skill.AM_Rogue_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Melee.AM_Rogue_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Melee_Skill.AM_Rogue_Melee_Skill")))</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Rogue.DA_CharFX_Rogue",BasicAttackTag=(TagName="FX.Character.Rogue.BasicAttack"),SkillTag=(TagName="FX.Character.Rogue.WeaponSkill"),UltimateTag=(TagName="FX.Character.Rogue.Ultimate"),UltimateHitTag=(TagName="FX.Character.Rogue.UltimateHit"),HitTag=(TagName="FX.Character.Rogue.Hit"),DeathTag=(TagName="FX.Character.Rogue.Death"))</t>
+  </si>
+  <si>
     <t>(TagName="FX.Character.Rogue.Ultimate")</t>
   </si>
   <si>
@@ -798,12 +909,18 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Tinker/Ani/Tinker_Base_Battle_Idle_Anim_Tinker_Base_Battle_Idle.Tinker_Base_Battle_Idle_Anim_Tinker_Base_Battle_Idle</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Tinker.Tinker</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Ultimate.AM_Tinker_Ultimate</t>
   </si>
   <si>
     <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Book.AM_Tinker_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Book_Skill.AM_Tinker_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Gun.AM_Tinker_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Gun_Skill.AM_Tinker_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Melee.AM_Tinker_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Melee_Skill.AM_Tinker_Melee_Skill")))</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Tinker.DA_CharFX_Tinker",BasicAttackTag=(TagName="FX.Character.Tinker.BasicAttack"),SkillTag=(TagName="FX.Character.Tinker.WeaponSkill"),UltimateTag=(TagName="FX.Character.Tinker.Ultimate"),UltimateHitTag=(TagName="FX.Character.Tinker.UltimateHit"),HitTag=(TagName="FX.Character.Tinker.Hit"),DeathTag=(TagName="FX.Character.Tinker.Death"))</t>
+  </si>
+  <si>
     <t>(TagName="FX.Character.Tinker.Ultimate")</t>
   </si>
   <si>
@@ -834,12 +951,18 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Tuner/Ani/Tuner_Base_Battle_Idle.Tuner_Base_Battle_Idle</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Tuner.Tuner</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Ultimate.AM_Tuner_Ultimate</t>
   </si>
   <si>
     <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Book.AM_Tuner_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Book_Skill.AM_Tuner_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Gun.AM_Tuner_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Gun_Skill.AM_Tuner_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Melee.AM_Tuner_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Melee_Skill.AM_Tuner_Melee_Skill")))</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Tuner.DA_CharFX_Tuner",BasicAttackTag=(TagName="FX.Character.Tuner.BasicAttack"),SkillTag=(TagName="FX.Character.Tuner.WeaponSkill"),UltimateTag=(TagName="FX.Character.Tuner.Ultimate"),UltimateHitTag=(TagName="FX.Character.Tuner.UltimateHit"),HitTag=(TagName="FX.Character.Tuner.Hit"),DeathTag=(TagName="FX.Character.Tuner.Death"))</t>
+  </si>
+  <si>
     <t>(TagName="FX.Character.Tuner.Ultimate")</t>
   </si>
   <si>
@@ -870,12 +993,18 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Weaver/Ani/Weaver_Base_Battle_Idle_Anim_Take_001.Weaver_Base_Battle_Idle_Anim_Take_001</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Weaver.Weaver</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Ultimate.AM_Weaver_Ultimate</t>
   </si>
   <si>
     <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Book.AM_Weaver_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Book_Skill.AM_Weaver_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Gun.AM_Weaver_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Gun_Skill.AM_Weaver_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Melee.AM_Weaver_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Melee_Skill.AM_Weaver_Melee_Skill")))</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Weaver.DA_CharFX_Weaver",BasicAttackTag=(TagName="FX.Character.Weaver.BasicAttack"),SkillTag=(TagName="FX.Character.Weaver.WeaponSkill"),UltimateTag=(TagName="FX.Character.Weaver.Ultimate"),UltimateHitTag=(TagName="FX.Character.Weaver.UltimateHit"),HitTag=(TagName="FX.Character.Weaver.Hit"),DeathTag=(TagName="FX.Character.Weaver.Death"))</t>
+  </si>
+  <si>
     <t>(TagName="FX.Character.Weaver.Ultimate")</t>
   </si>
   <si>
@@ -906,12 +1035,18 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Writer/Ani/Writer_Base_Battle_Idle.Writer_Base_Battle_Idle</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Writer.Writer</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Ultimate.AM_Writer_Ultimate</t>
   </si>
   <si>
     <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Book.AM_Writer_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Book_Skill.AM_Writer_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Gun.AM_Writer_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Gun_Skill.AM_Writer_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Melee.AM_Writer_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Melee_Skill.AM_Writer_Melee_Skill")))</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Writer.DA_CharFX_Writer",BasicAttackTag=(TagName="FX.Character.Writer.BasicAttack"),SkillTag=(TagName="FX.Character.Writer.WeaponSkill"),UltimateTag=(TagName="FX.Character.Writer.Ultimate"),UltimateHitTag=(TagName="FX.Character.Writer.UltimateHit"),HitTag=(TagName="FX.Character.Writer.Hit"),DeathTag=(TagName="FX.Character.Writer.Death"))</t>
+  </si>
+  <si>
     <t>(TagName="FX.Character.Writer.Ultimate")</t>
   </si>
   <si>
@@ -928,70 +1063,6 @@
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Dead.AM_Writer_Dead</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Bard.DA_CharFX_Bard",BasicAttackTag=(TagName="FX.Character.Bard.BasicAttack"),SkillTag=(TagName="FX.Character.Bard.WeaponSkill"),UltimateTag=(TagName="FX.Character.Bard.Ultimate"),UltimateHitTag=(TagName="FX.Character.Bard.UltimateHit"),HitTag=(TagName="FX.Character.Bard.Hit"),DeathTag=(TagName="FX.Character.Bard.Death"))</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Binder.DA_CharFX_Binder",BasicAttackTag=(TagName="FX.Character.Binder.BasicAttack"),SkillTag=(TagName="FX.Character.Binder.WeaponSkill"),UltimateTag=(TagName="FX.Character.Binder.Ultimate"),UltimateHitTag=(TagName="FX.Character.Binder.UltimateHit"),HitTag=(TagName="FX.Character.Binder.Hit"),DeathTag=(TagName="FX.Character.Binder.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Courier.DA_CharFX_Courier",BasicAttackTag=(TagName="FX.Character.Courier.BasicAttack"),SkillTag=(TagName="FX.Character.Courier.WeaponSkill"),UltimateTag=(TagName="FX.Character.Courier.Ultimate"),UltimateHitTag=(TagName="FX.Character.Courier.UltimateHit"),HitTag=(TagName="FX.Character.Courier.Hit"),DeathTag=(TagName="FX.Character.Courier.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Demonia.DA_CharFX_Demonia",BasicAttackTag=(TagName="FX.Character.Demonia.BasicAttack"),SkillTag=(TagName="FX.Character.Demonia.WeaponSkill"),UltimateTag=(TagName="FX.Character.Demonia.Ultimate"),UltimateHitTag=(TagName="FX.Character.Demonia.UltimateHit"),HitTag=(TagName="FX.Character.Demonia.Hit"),DeathTag=(TagName="FX.Character.Demonia.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Enchanter.DA_CharFX_Enchanter",BasicAttackTag=(TagName="FX.Character.Enchanter.BasicAttack"),SkillTag=(TagName="FX.Character.Enchanter.WeaponSkill"),UltimateTag=(TagName="FX.Character.Enchanter.Ultimate"),UltimateHitTag=(TagName="FX.Character.Enchanter.UltimateHit"),HitTag=(TagName="FX.Character.Enchanter.Hit"),DeathTag=(TagName="FX.Character.Enchanter.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Guard.DA_CharFX_Guard",BasicAttackTag=(TagName="FX.Character.Guard.BasicAttack"),SkillTag=(TagName="FX.Character.Guard.WeaponSkill"),UltimateTag=(TagName="FX.Character.Guard.Ultimate"),UltimateHitTag=(TagName="FX.Character.Guard.UltimateHit"),HitTag=(TagName="FX.Character.Guard.Hit"),DeathTag=(TagName="FX.Character.Guard.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Hermit.DA_CharFX_Hermit",BasicAttackTag=(TagName="FX.Character.Hermit.BasicAttack"),SkillTag=(TagName="FX.Character.Hermit.WeaponSkill"),UltimateTag=(TagName="FX.Character.Hermit.Ultimate"),UltimateHitTag=(TagName="FX.Character.Hermit.UltimateHit"),HitTag=(TagName="FX.Character.Hermit.Hit"),DeathTag=(TagName="FX.Character.Hermit.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Hornet.DA_CharFX_Hornet",BasicAttackTag=(TagName="FX.Character.Hornet.BasicAttack"),SkillTag=(TagName="FX.Character.Hornet.WeaponSkill"),UltimateTag=(TagName="FX.Character.Hornet.Ultimate"),UltimateHitTag=(TagName="FX.Character.Hornet.UltimateHit"),HitTag=(TagName="FX.Character.Hornet.Hit"),DeathTag=(TagName="FX.Character.Hornet.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Looter.DA_CharFX_Looter",BasicAttackTag=(TagName="FX.Character.Looter.BasicAttack"),SkillTag=(TagName="FX.Character.Looter.WeaponSkill"),UltimateTag=(TagName="FX.Character.Looter.Ultimate"),UltimateHitTag=(TagName="FX.Character.Looter.UltimateHit"),HitTag=(TagName="FX.Character.Looter.Hit"),DeathTag=(TagName="FX.Character.Looter.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Maid.DA_CharFX_Maid",BasicAttackTag=(TagName="FX.Character.Maid.BasicAttack"),SkillTag=(TagName="FX.Character.Maid.WeaponSkill"),UltimateTag=(TagName="FX.Character.Maid.Ultimate"),UltimateHitTag=(TagName="FX.Character.Maid.UltimateHit"),HitTag=(TagName="FX.Character.Maid.Hit"),DeathTag=(TagName="FX.Character.Maid.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Merry.DA_CharFX_Merry",BasicAttackTag=(TagName="FX.Character.Merry.BasicAttack"),SkillTag=(TagName="FX.Character.Merry.WeaponSkill"),UltimateTag=(TagName="FX.Character.Merry.Ultimate"),UltimateHitTag=(TagName="FX.Character.Merry.UltimateHit"),HitTag=(TagName="FX.Character.Merry.Hit"),DeathTag=(TagName="FX.Character.Merry.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Muzzle.DA_CharFX_Muzzle",BasicAttackTag=(TagName="FX.Character.Muzzle.BasicAttack"),SkillTag=(TagName="FX.Character.Muzzle.WeaponSkill"),UltimateTag=(TagName="FX.Character.Muzzle.Ultimate"),UltimateHitTag=(TagName="FX.Character.Muzzle.UltimateHit"),HitTag=(TagName="FX.Character.Muzzle.Hit"),DeathTag=(TagName="FX.Character.Muzzle.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Noble.DA_CharFX_Noble",BasicAttackTag=(TagName="FX.Character.Noble.BasicAttack"),SkillTag=(TagName="FX.Character.Noble.WeaponSkill"),UltimateTag=(TagName="FX.Character.Noble.Ultimate"),UltimateHitTag=(TagName="FX.Character.Noble.UltimateHit"),HitTag=(TagName="FX.Character.Noble.Hit"),DeathTag=(TagName="FX.Character.Noble.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Nurse.DA_CharFX_Nurse",BasicAttackTag=(TagName="FX.Character.Nurse.BasicAttack"),SkillTag=(TagName="FX.Character.Nurse.WeaponSkill"),UltimateTag=(TagName="FX.Character.Nurse.Ultimate"),UltimateHitTag=(TagName="FX.Character.Nurse.UltimateHit"),HitTag=(TagName="FX.Character.Nurse.Hit"),DeathTag=(TagName="FX.Character.Nurse.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Outsider.DA_CharFX_Outsider",BasicAttackTag=(TagName="FX.Character.Outsider.BasicAttack"),SkillTag=(TagName="FX.Character.Outsider.WeaponSkill"),UltimateTag=(TagName="FX.Character.Outsider.Ultimate"),UltimateHitTag=(TagName="FX.Character.Outsider.UltimateHit"),HitTag=(TagName="FX.Character.Outsider.Hit"),DeathTag=(TagName="FX.Character.Outsider.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Pioneer.DA_CharFX_Pioneer",BasicAttackTag=(TagName="FX.Character.Pioneer.BasicAttack"),SkillTag=(TagName="FX.Character.Pioneer.WeaponSkill"),UltimateTag=(TagName="FX.Character.Pioneer.Ultimate"),UltimateHitTag=(TagName="FX.Character.Pioneer.UltimateHit"),HitTag=(TagName="FX.Character.Pioneer.Hit"),DeathTag=(TagName="FX.Character.Pioneer.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Rogue.DA_CharFX_Rogue",BasicAttackTag=(TagName="FX.Character.Rogue.BasicAttack"),SkillTag=(TagName="FX.Character.Rogue.WeaponSkill"),UltimateTag=(TagName="FX.Character.Rogue.Ultimate"),UltimateHitTag=(TagName="FX.Character.Rogue.UltimateHit"),HitTag=(TagName="FX.Character.Rogue.Hit"),DeathTag=(TagName="FX.Character.Rogue.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Tinker.DA_CharFX_Tinker",BasicAttackTag=(TagName="FX.Character.Tinker.BasicAttack"),SkillTag=(TagName="FX.Character.Tinker.WeaponSkill"),UltimateTag=(TagName="FX.Character.Tinker.Ultimate"),UltimateHitTag=(TagName="FX.Character.Tinker.UltimateHit"),HitTag=(TagName="FX.Character.Tinker.Hit"),DeathTag=(TagName="FX.Character.Tinker.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Tuner.DA_CharFX_Tuner",BasicAttackTag=(TagName="FX.Character.Tuner.BasicAttack"),SkillTag=(TagName="FX.Character.Tuner.WeaponSkill"),UltimateTag=(TagName="FX.Character.Tuner.Ultimate"),UltimateHitTag=(TagName="FX.Character.Tuner.UltimateHit"),HitTag=(TagName="FX.Character.Tuner.Hit"),DeathTag=(TagName="FX.Character.Tuner.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Weaver.DA_CharFX_Weaver",BasicAttackTag=(TagName="FX.Character.Weaver.BasicAttack"),SkillTag=(TagName="FX.Character.Weaver.WeaponSkill"),UltimateTag=(TagName="FX.Character.Weaver.Ultimate"),UltimateHitTag=(TagName="FX.Character.Weaver.UltimateHit"),HitTag=(TagName="FX.Character.Weaver.Hit"),DeathTag=(TagName="FX.Character.Weaver.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Writer.DA_CharFX_Writer",BasicAttackTag=(TagName="FX.Character.Writer.BasicAttack"),SkillTag=(TagName="FX.Character.Writer.WeaponSkill"),UltimateTag=(TagName="FX.Character.Writer.Ultimate"),UltimateHitTag=(TagName="FX.Character.Writer.UltimateHit"),HitTag=(TagName="FX.Character.Writer.Hit"),DeathTag=(TagName="FX.Character.Writer.Death"))</t>
   </si>
 </sst>
 </file>
@@ -2032,219 +2103,219 @@
         <v>37</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="F3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L3" t="s">
         <v>28</v>
       </c>
       <c r="M3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G4" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="H4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J4" t="s">
-        <v>303</v>
+        <v>59</v>
       </c>
       <c r="K4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L4" t="s">
         <v>28</v>
       </c>
       <c r="M4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="N4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="O4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="P4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="Q4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G5" t="s">
         <v>23</v>
       </c>
       <c r="H5" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="I5" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="J5" t="s">
-        <v>304</v>
+        <v>74</v>
       </c>
       <c r="K5" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="L5" t="s">
         <v>28</v>
       </c>
       <c r="M5" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="N5" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="O5" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="P5" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="Q5" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="F6" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G6" t="s">
         <v>23</v>
       </c>
       <c r="H6" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I6" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="J6" t="s">
-        <v>305</v>
+        <v>89</v>
       </c>
       <c r="K6" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L6" t="s">
         <v>28</v>
       </c>
       <c r="M6" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="N6" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="O6" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="P6" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="Q6" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="F7" t="s">
         <v>22</v>
@@ -2253,475 +2324,475 @@
         <v>23</v>
       </c>
       <c r="H7" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="I7" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="J7" t="s">
-        <v>306</v>
+        <v>103</v>
       </c>
       <c r="K7" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="L7" t="s">
         <v>28</v>
       </c>
       <c r="M7" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="N7" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="O7" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="P7" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="Q7" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="B8" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="D8" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="E8" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="F8" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G8" t="s">
         <v>23</v>
       </c>
       <c r="H8" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="I8" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="J8" t="s">
-        <v>307</v>
+        <v>117</v>
       </c>
       <c r="K8" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="L8" t="s">
         <v>28</v>
       </c>
       <c r="M8" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="N8" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="O8" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="P8" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="Q8" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="B9" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="C9" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="D9" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="E9" t="s">
-        <v>21</v>
+        <v>128</v>
       </c>
       <c r="F9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G9" t="s">
         <v>23</v>
       </c>
       <c r="H9" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="I9" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="J9" t="s">
-        <v>308</v>
+        <v>131</v>
       </c>
       <c r="K9" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="L9" t="s">
         <v>28</v>
       </c>
       <c r="M9" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="N9" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="O9" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="P9" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="Q9" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="B10" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="C10" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="D10" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="E10" t="s">
-        <v>21</v>
+        <v>142</v>
       </c>
       <c r="F10" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G10" t="s">
         <v>23</v>
       </c>
       <c r="H10" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="I10" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="J10" t="s">
-        <v>309</v>
+        <v>145</v>
       </c>
       <c r="K10" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="L10" t="s">
         <v>28</v>
       </c>
       <c r="M10" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="N10" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="O10" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="P10" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="Q10" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="B11" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="C11" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="D11" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="E11" t="s">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="F11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G11" t="s">
         <v>23</v>
       </c>
       <c r="H11" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="I11" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="J11" t="s">
-        <v>310</v>
+        <v>159</v>
       </c>
       <c r="K11" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="L11" t="s">
         <v>28</v>
       </c>
       <c r="M11" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="N11" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="O11" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="P11" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="Q11" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="B12" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="C12" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="D12" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="E12" t="s">
-        <v>21</v>
+        <v>170</v>
       </c>
       <c r="F12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G12" t="s">
         <v>23</v>
       </c>
       <c r="H12" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="I12" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="J12" t="s">
-        <v>311</v>
+        <v>173</v>
       </c>
       <c r="K12" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="L12" t="s">
         <v>28</v>
       </c>
       <c r="M12" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="O12" t="s">
-        <v>21</v>
+        <v>177</v>
       </c>
       <c r="P12" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="Q12" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="B13" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="C13" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="D13" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="E13" t="s">
-        <v>21</v>
+        <v>184</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G13" t="s">
         <v>23</v>
       </c>
       <c r="H13" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="I13" t="s">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="J13" t="s">
-        <v>312</v>
+        <v>187</v>
       </c>
       <c r="K13" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="L13" t="s">
         <v>28</v>
       </c>
       <c r="M13" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="N13" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="O13" t="s">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="P13" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="Q13" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="B14" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="C14" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="D14" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="E14" t="s">
-        <v>21</v>
+        <v>198</v>
       </c>
       <c r="F14" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G14" t="s">
         <v>23</v>
       </c>
       <c r="H14" t="s">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="I14" t="s">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="J14" t="s">
-        <v>313</v>
+        <v>201</v>
       </c>
       <c r="K14" t="s">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="L14" t="s">
         <v>28</v>
       </c>
       <c r="M14" t="s">
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="N14" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="O14" t="s">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="P14" t="s">
-        <v>181</v>
+        <v>206</v>
       </c>
       <c r="Q14" t="s">
-        <v>182</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>183</v>
+        <v>208</v>
       </c>
       <c r="B15" t="s">
-        <v>184</v>
+        <v>209</v>
       </c>
       <c r="C15" t="s">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="D15" t="s">
-        <v>186</v>
+        <v>211</v>
       </c>
       <c r="E15" t="s">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="F15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G15" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="H15" t="s">
-        <v>187</v>
+        <v>213</v>
       </c>
       <c r="I15" t="s">
-        <v>188</v>
+        <v>214</v>
       </c>
       <c r="J15" t="s">
-        <v>314</v>
+        <v>215</v>
       </c>
       <c r="K15" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="L15" t="s">
         <v>28</v>
       </c>
       <c r="M15" t="s">
-        <v>190</v>
+        <v>217</v>
       </c>
       <c r="N15" t="s">
-        <v>191</v>
+        <v>218</v>
       </c>
       <c r="O15" t="s">
-        <v>192</v>
+        <v>219</v>
       </c>
       <c r="P15" t="s">
-        <v>193</v>
+        <v>220</v>
       </c>
       <c r="Q15" t="s">
-        <v>194</v>
+        <v>221</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="B16" t="s">
-        <v>196</v>
+        <v>223</v>
       </c>
       <c r="C16" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="D16" t="s">
-        <v>198</v>
+        <v>225</v>
       </c>
       <c r="E16" t="s">
-        <v>21</v>
+        <v>226</v>
       </c>
       <c r="F16" t="s">
         <v>22</v>
@@ -2730,458 +2801,458 @@
         <v>23</v>
       </c>
       <c r="H16" t="s">
-        <v>199</v>
+        <v>227</v>
       </c>
       <c r="I16" t="s">
-        <v>200</v>
+        <v>228</v>
       </c>
       <c r="J16" t="s">
-        <v>315</v>
+        <v>229</v>
       </c>
       <c r="K16" t="s">
-        <v>201</v>
+        <v>230</v>
       </c>
       <c r="L16" t="s">
         <v>28</v>
       </c>
       <c r="M16" t="s">
-        <v>202</v>
+        <v>231</v>
       </c>
       <c r="N16" t="s">
-        <v>203</v>
+        <v>232</v>
       </c>
       <c r="O16" t="s">
-        <v>204</v>
+        <v>233</v>
       </c>
       <c r="P16" t="s">
-        <v>205</v>
+        <v>234</v>
       </c>
       <c r="Q16" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>207</v>
+        <v>236</v>
       </c>
       <c r="B17" t="s">
-        <v>208</v>
+        <v>237</v>
       </c>
       <c r="C17" t="s">
-        <v>209</v>
+        <v>238</v>
       </c>
       <c r="D17" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="E17" t="s">
-        <v>21</v>
+        <v>240</v>
       </c>
       <c r="F17" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G17" t="s">
         <v>23</v>
       </c>
       <c r="H17" t="s">
-        <v>211</v>
+        <v>241</v>
       </c>
       <c r="I17" t="s">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="J17" t="s">
-        <v>316</v>
+        <v>243</v>
       </c>
       <c r="K17" t="s">
-        <v>213</v>
+        <v>244</v>
       </c>
       <c r="L17" t="s">
         <v>28</v>
       </c>
       <c r="M17" t="s">
-        <v>214</v>
+        <v>245</v>
       </c>
       <c r="N17" t="s">
-        <v>215</v>
+        <v>246</v>
       </c>
       <c r="O17" t="s">
-        <v>216</v>
+        <v>247</v>
       </c>
       <c r="P17" t="s">
-        <v>217</v>
+        <v>248</v>
       </c>
       <c r="Q17" t="s">
-        <v>218</v>
+        <v>249</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>219</v>
+        <v>250</v>
       </c>
       <c r="B18" t="s">
-        <v>220</v>
+        <v>251</v>
       </c>
       <c r="C18" t="s">
-        <v>221</v>
+        <v>252</v>
       </c>
       <c r="D18" t="s">
-        <v>222</v>
+        <v>253</v>
       </c>
       <c r="E18" t="s">
-        <v>21</v>
+        <v>254</v>
       </c>
       <c r="F18" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G18" t="s">
         <v>23</v>
       </c>
       <c r="H18" t="s">
-        <v>223</v>
+        <v>255</v>
       </c>
       <c r="I18" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="J18" t="s">
-        <v>317</v>
+        <v>257</v>
       </c>
       <c r="K18" t="s">
-        <v>225</v>
+        <v>258</v>
       </c>
       <c r="L18" t="s">
         <v>28</v>
       </c>
       <c r="M18" t="s">
-        <v>226</v>
+        <v>259</v>
       </c>
       <c r="N18" t="s">
-        <v>227</v>
+        <v>260</v>
       </c>
       <c r="O18" t="s">
-        <v>228</v>
+        <v>261</v>
       </c>
       <c r="P18" t="s">
-        <v>229</v>
+        <v>262</v>
       </c>
       <c r="Q18" t="s">
-        <v>230</v>
+        <v>263</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>231</v>
+        <v>264</v>
       </c>
       <c r="B19" t="s">
-        <v>232</v>
+        <v>265</v>
       </c>
       <c r="C19" t="s">
-        <v>233</v>
+        <v>266</v>
       </c>
       <c r="D19" t="s">
-        <v>234</v>
+        <v>267</v>
       </c>
       <c r="E19" t="s">
-        <v>21</v>
+        <v>268</v>
       </c>
       <c r="F19" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G19" t="s">
         <v>23</v>
       </c>
       <c r="H19" t="s">
-        <v>235</v>
+        <v>269</v>
       </c>
       <c r="I19" t="s">
-        <v>236</v>
+        <v>270</v>
       </c>
       <c r="J19" t="s">
-        <v>318</v>
+        <v>271</v>
       </c>
       <c r="K19" t="s">
-        <v>237</v>
+        <v>272</v>
       </c>
       <c r="L19" t="s">
         <v>28</v>
       </c>
       <c r="M19" t="s">
-        <v>238</v>
+        <v>273</v>
       </c>
       <c r="N19" t="s">
-        <v>239</v>
+        <v>274</v>
       </c>
       <c r="O19" t="s">
-        <v>240</v>
+        <v>275</v>
       </c>
       <c r="P19" t="s">
-        <v>241</v>
+        <v>276</v>
       </c>
       <c r="Q19" t="s">
-        <v>242</v>
+        <v>277</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>243</v>
+        <v>278</v>
       </c>
       <c r="B20" t="s">
-        <v>244</v>
+        <v>279</v>
       </c>
       <c r="C20" t="s">
-        <v>245</v>
+        <v>280</v>
       </c>
       <c r="D20" t="s">
-        <v>246</v>
+        <v>281</v>
       </c>
       <c r="E20" t="s">
-        <v>21</v>
+        <v>282</v>
       </c>
       <c r="F20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G20" t="s">
         <v>23</v>
       </c>
       <c r="H20" t="s">
-        <v>247</v>
+        <v>283</v>
       </c>
       <c r="I20" t="s">
-        <v>248</v>
+        <v>284</v>
       </c>
       <c r="J20" t="s">
-        <v>319</v>
+        <v>285</v>
       </c>
       <c r="K20" t="s">
-        <v>249</v>
+        <v>286</v>
       </c>
       <c r="L20" t="s">
         <v>28</v>
       </c>
       <c r="M20" t="s">
-        <v>250</v>
+        <v>287</v>
       </c>
       <c r="N20" t="s">
-        <v>251</v>
+        <v>288</v>
       </c>
       <c r="O20" t="s">
-        <v>252</v>
+        <v>289</v>
       </c>
       <c r="P20" t="s">
-        <v>253</v>
+        <v>290</v>
       </c>
       <c r="Q20" t="s">
-        <v>254</v>
+        <v>291</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>255</v>
+        <v>292</v>
       </c>
       <c r="B21" t="s">
-        <v>256</v>
+        <v>293</v>
       </c>
       <c r="C21" t="s">
-        <v>257</v>
+        <v>294</v>
       </c>
       <c r="D21" t="s">
-        <v>258</v>
+        <v>295</v>
       </c>
       <c r="E21" t="s">
-        <v>21</v>
+        <v>296</v>
       </c>
       <c r="F21" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G21" t="s">
         <v>23</v>
       </c>
       <c r="H21" t="s">
-        <v>259</v>
+        <v>297</v>
       </c>
       <c r="I21" t="s">
-        <v>260</v>
+        <v>298</v>
       </c>
       <c r="J21" t="s">
-        <v>320</v>
+        <v>299</v>
       </c>
       <c r="K21" t="s">
-        <v>261</v>
+        <v>300</v>
       </c>
       <c r="L21" t="s">
         <v>28</v>
       </c>
       <c r="M21" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="N21" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="O21" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="P21" t="s">
-        <v>265</v>
+        <v>304</v>
       </c>
       <c r="Q21" t="s">
-        <v>266</v>
+        <v>305</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>267</v>
+        <v>306</v>
       </c>
       <c r="B22" t="s">
-        <v>268</v>
+        <v>307</v>
       </c>
       <c r="C22" t="s">
-        <v>269</v>
+        <v>308</v>
       </c>
       <c r="D22" t="s">
-        <v>270</v>
+        <v>309</v>
       </c>
       <c r="E22" t="s">
-        <v>21</v>
+        <v>310</v>
       </c>
       <c r="F22" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G22" t="s">
         <v>23</v>
       </c>
       <c r="H22" t="s">
-        <v>271</v>
+        <v>311</v>
       </c>
       <c r="I22" t="s">
-        <v>272</v>
+        <v>312</v>
       </c>
       <c r="J22" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="K22" t="s">
-        <v>273</v>
+        <v>314</v>
       </c>
       <c r="L22" t="s">
         <v>28</v>
       </c>
       <c r="M22" t="s">
-        <v>274</v>
+        <v>315</v>
       </c>
       <c r="N22" t="s">
-        <v>275</v>
+        <v>316</v>
       </c>
       <c r="O22" t="s">
-        <v>276</v>
+        <v>317</v>
       </c>
       <c r="P22" t="s">
-        <v>277</v>
+        <v>318</v>
       </c>
       <c r="Q22" t="s">
-        <v>278</v>
+        <v>319</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>279</v>
+        <v>320</v>
       </c>
       <c r="B23" t="s">
-        <v>280</v>
+        <v>321</v>
       </c>
       <c r="C23" t="s">
-        <v>281</v>
+        <v>322</v>
       </c>
       <c r="D23" t="s">
-        <v>282</v>
+        <v>323</v>
       </c>
       <c r="E23" t="s">
-        <v>21</v>
+        <v>324</v>
       </c>
       <c r="F23" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G23" t="s">
         <v>23</v>
       </c>
       <c r="H23" t="s">
-        <v>283</v>
+        <v>325</v>
       </c>
       <c r="I23" t="s">
-        <v>284</v>
+        <v>326</v>
       </c>
       <c r="J23" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="K23" t="s">
-        <v>285</v>
+        <v>328</v>
       </c>
       <c r="L23" t="s">
         <v>28</v>
       </c>
       <c r="M23" t="s">
-        <v>286</v>
+        <v>329</v>
       </c>
       <c r="N23" t="s">
-        <v>287</v>
+        <v>330</v>
       </c>
       <c r="O23" t="s">
-        <v>288</v>
+        <v>331</v>
       </c>
       <c r="P23" t="s">
-        <v>289</v>
+        <v>332</v>
       </c>
       <c r="Q23" t="s">
-        <v>290</v>
+        <v>333</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>291</v>
+        <v>334</v>
       </c>
       <c r="B24" t="s">
-        <v>292</v>
+        <v>335</v>
       </c>
       <c r="C24" t="s">
-        <v>293</v>
+        <v>336</v>
       </c>
       <c r="D24" t="s">
-        <v>294</v>
+        <v>337</v>
       </c>
       <c r="E24" t="s">
-        <v>21</v>
+        <v>338</v>
       </c>
       <c r="F24" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G24" t="s">
         <v>23</v>
       </c>
       <c r="H24" t="s">
-        <v>295</v>
+        <v>339</v>
       </c>
       <c r="I24" t="s">
-        <v>296</v>
+        <v>340</v>
       </c>
       <c r="J24" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="K24" t="s">
-        <v>297</v>
+        <v>342</v>
       </c>
       <c r="L24" t="s">
         <v>28</v>
       </c>
       <c r="M24" t="s">
-        <v>298</v>
+        <v>343</v>
       </c>
       <c r="N24" t="s">
-        <v>299</v>
+        <v>344</v>
       </c>
       <c r="O24" t="s">
-        <v>300</v>
+        <v>345</v>
       </c>
       <c r="P24" t="s">
-        <v>301</v>
+        <v>346</v>
       </c>
       <c r="Q24" t="s">
-        <v>302</v>
+        <v>347</v>
       </c>
     </row>
   </sheetData>

--- a/DesignData/Excel_Masters/CharacterAssets_Master.xlsx
+++ b/DesignData/Excel_Masters/CharacterAssets_Master.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22065" windowHeight="10050"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22065" windowHeight="10035"/>
   </bookViews>
   <sheets>
     <sheet name="CharacterAssets" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="351">
   <si>
     <t>---</t>
   </si>
@@ -33,6 +33,12 @@
     <t>IdleAnim</t>
   </si>
   <si>
+    <t>RunAnim</t>
+  </si>
+  <si>
+    <t>DefaultWeaponID</t>
+  </si>
+  <si>
     <t>UltimateIcon</t>
   </si>
   <si>
@@ -75,7 +81,7 @@
     <t>Char_Anubis</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Anubis.Icon_Anubis</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Anubis.Anubis</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Anubis.Icon_Anubis</t>
@@ -84,7 +90,10 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Anubis/Ani/Anubis_Base_Battle_Idle_Anim_Anubis_Base_Battle_Idle1.Anubis_Base_Battle_Idle_Anim_Anubis_Base_Battle_Idle1</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Cards/Anubis.Anubis</t>
+    <t>None</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/CharacterSkills/Icon_PassiveSkill/Icon_PassiveSkill_Anubis.Icon_PassiveSkill_Anubis</t>
   </si>
   <si>
     <t>Legendary</t>
@@ -96,7 +105,7 @@
     <t>/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Ultimate.AM_Anubis_Ultimate</t>
   </si>
   <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Book.AM_Anubis_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Book_Skill.AM_Anubis_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Gun.AM_Anubis_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Gun_Skill.AM_Anubis_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Melee.AM_Anubis_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Melee_Skill.AM_Anubis_Melee_Skill")))</t>
+    <t>((Magic, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Book.AM_Anubis_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Book_Skill.AM_Anubis_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Gun.AM_Anubis_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Gun_Skill.AM_Anubis_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Melee.AM_Anubis_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Anubis/AM_Anubis_Melee_Skill.AM_Anubis_Melee_Skill")))</t>
   </si>
   <si>
     <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Anubis.DA_CharFX_Anubis",BasicAttackTag=(TagName="FX.Character.Anubis.BasicAttack"),SkillTag=(TagName="FX.Character.Anubis.WeaponSkill"),UltimateTag=(TagName="FX.Character.Anubis.Ultimate"),UltimateHitTag=(TagName="FX.Character.Anubis.UltimateHit"),HitTag=(TagName="FX.Character.Anubis.Hit"),DeathTag=(TagName="FX.Character.Anubis.Death"))</t>
@@ -108,7 +117,7 @@
     <t>(TagName="Unit.Faction.Friendly.Player")</t>
   </si>
   <si>
-    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Anubis/SKM_Anubis_Base.SKM_Anubis_Base</t>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Anubis/Anubis_Modify/SKM_Anubis_Base_Modified.SKM_Anubis_Base_Modified</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Anubis.Icon_Anubis</t>
@@ -126,7 +135,7 @@
     <t>Char_Army</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Army.Icon_Army</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Army.Army</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Army.Icon_Army</t>
@@ -135,7 +144,7 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Army/Ani/Army_Base_Battle_Idle.Army_Base_Battle_Idle</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Cards/Army.Army</t>
+    <t>/Game/External_Assets/UI/Character/CharacterSkills/Icon_PassiveSkill/Icon_PassiveSkill_Army.Icon_PassiveSkill_Army</t>
   </si>
   <si>
     <t>Common</t>
@@ -147,7 +156,7 @@
     <t>/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Ultimate.AM_Army_Ultimate</t>
   </si>
   <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Book.AM_Army_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Book_SKill.AM_Army_Book_SKill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Gun.AM_Army_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Gun_Skill.AM_Army_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Melee.AM_Army_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Melee_Skill.AM_Army_Melee_Skill")))</t>
+    <t>((Magic, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Book.AM_Army_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Book_SKill.AM_Army_Book_SKill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Gun.AM_Army_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Gun_Skill.AM_Army_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Melee.AM_Army_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Army/AM_Army_Melee_Skill.AM_Army_Melee_Skill")))</t>
   </si>
   <si>
     <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Army.DA_CharFX_Army",BasicAttackTag=(TagName="FX.Character.Army.BasicAttack"),SkillTag=(TagName="FX.Character.Army.WeaponSkill"),UltimateTag=(TagName="FX.Character.Army.Ultimate"),UltimateHitTag=(TagName="FX.Character.Army.UltimateHit"),HitTag=(TagName="FX.Character.Army.Hit"),DeathTag=(TagName="FX.Character.Army.Death"))</t>
@@ -174,7 +183,7 @@
     <t>Char_Bard</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Bard.Icon_Bard</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Bard.Bard</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Bard.Icon_Bard</t>
@@ -183,7 +192,7 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Bard/Bard_Modify/Ani/Bard_Base_Battle_Idle.Bard_Base_Battle_Idle</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Cards/Bard.Bard</t>
+    <t>/Game/External_Assets/UI/Character/CharacterSkills/Icon_PassiveSkill/Icon_PassiveSkill_Bard.Icon_PassiveSkill_Bard</t>
   </si>
   <si>
     <t>Uncommon</t>
@@ -195,7 +204,7 @@
     <t>/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Ultimate.AM_Bard_Ultimate</t>
   </si>
   <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Book.AM_Bard_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Book_Skill.AM_Bard_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Gun.AM_Bard_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Gun_Skill.AM_Bard_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Melee.AM_Bard_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Melee_Skill.AM_Bard_Melee_Skill")))</t>
+    <t>((Magic, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Book.AM_Bard_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Book_Skill.AM_Bard_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Gun.AM_Bard_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Gun_Skill.AM_Bard_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Melee.AM_Bard_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Bard/AM_Bard_Melee_Skill.AM_Bard_Melee_Skill")))</t>
   </si>
   <si>
     <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Bard.DA_CharFX_Bard",BasicAttackTag=(TagName="FX.Character.Bard.BasicAttack"),SkillTag=(TagName="FX.Character.Bard.WeaponSkill"),UltimateTag=(TagName="FX.Character.Bard.Ultimate"),UltimateHitTag=(TagName="FX.Character.Bard.UltimateHit"),HitTag=(TagName="FX.Character.Bard.Hit"),DeathTag=(TagName="FX.Character.Bard.Death"))</t>
@@ -222,7 +231,7 @@
     <t>Char_Binder</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Binder.Icon_Binder</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Binder.Binder</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Binder.Icon_Binder</t>
@@ -231,7 +240,7 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Binder/Ani/Binder_Base_Battle_Idle.Binder_Base_Battle_Idle</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Cards/Binder.Binder</t>
+    <t>/Game/External_Assets/UI/Character/CharacterSkills/Icon_PassiveSkill/Icon_PassiveSkill_Binder.Icon_PassiveSkill_Binder</t>
   </si>
   <si>
     <t>Epic</t>
@@ -240,7 +249,7 @@
     <t>/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Ultimate.AM_Binder_Ultimate</t>
   </si>
   <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Book.AM_Binder_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Book_Skill.AM_Binder_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Gun.AM_Binder_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Gun_Skill.AM_Binder_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Melee.AM_Binder_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Melee_Skill.AM_Binder_Melee_Skill")))</t>
+    <t>((Magic, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Book.AM_Binder_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Book_Skill.AM_Binder_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Gun.AM_Binder_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Gun_Skill.AM_Binder_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Melee.AM_Binder_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Binder/AM_Binder_Melee_Skill.AM_Binder_Melee_Skill")))</t>
   </si>
   <si>
     <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Binder.DA_CharFX_Binder",BasicAttackTag=(TagName="FX.Character.Binder.BasicAttack"),SkillTag=(TagName="FX.Character.Binder.WeaponSkill"),UltimateTag=(TagName="FX.Character.Binder.Ultimate"),UltimateHitTag=(TagName="FX.Character.Binder.UltimateHit"),HitTag=(TagName="FX.Character.Binder.Hit"),DeathTag=(TagName="FX.Character.Binder.Death"))</t>
@@ -249,7 +258,7 @@
     <t>(TagName="FX.Character.Binder.Ultimate")</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Player/Binder/SKM_Binder_Base.SKM_Binder_Base</t>
+    <t>/Game/External_Assets/ScaledPlayerMesh/Char_Binder/Binder_Modify/SKM_Binder_Base_Modified.SKM_Binder_Base_Modified</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Binder.Icon_Binder</t>
@@ -267,7 +276,7 @@
     <t>Char_Courier</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Courier.Icon_Courier</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Courier.Courier</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Courier.Icon_Courier</t>
@@ -276,7 +285,7 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Courier/Ani/Courier_Base_Lobby_Idle_Anim_Take_0011.Courier_Base_Lobby_Idle_Anim_Take_0011</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Cards/Courier.Courier</t>
+    <t>/Game/External_Assets/UI/Character/CharacterSkills/Icon_PassiveSkill/Icon_PassiveSkill_Courier.Icon_PassiveSkill_Courier</t>
   </si>
   <si>
     <t>Rare</t>
@@ -285,7 +294,7 @@
     <t>/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Ultimate.AM_Courier_Ultimate</t>
   </si>
   <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Book.AM_Courier_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Book_Skill.AM_Courier_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Gun.AM_Courier_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Gun_Skill.AM_Courier_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Melee.AM_Courier_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Melee_Skill.AM_Courier_Melee_Skill")))</t>
+    <t>((Magic, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Book.AM_Courier_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Book_Skill.AM_Courier_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Gun.AM_Courier_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Gun_Skill.AM_Courier_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Melee.AM_Courier_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Courier/AM_Courier_Melee_Skill.AM_Courier_Melee_Skill")))</t>
   </si>
   <si>
     <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Courier.DA_CharFX_Courier",BasicAttackTag=(TagName="FX.Character.Courier.BasicAttack"),SkillTag=(TagName="FX.Character.Courier.WeaponSkill"),UltimateTag=(TagName="FX.Character.Courier.Ultimate"),UltimateHitTag=(TagName="FX.Character.Courier.UltimateHit"),HitTag=(TagName="FX.Character.Courier.Hit"),DeathTag=(TagName="FX.Character.Courier.Death"))</t>
@@ -312,7 +321,7 @@
     <t>Char_Demonia</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Demonia.Icon_Demonia</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Demonia.Demonia</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Demonia.Icon_Demonia</t>
@@ -321,13 +330,13 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Demonia/Ani/Demonia_Base_Battle_Idle.Demonia_Base_Battle_Idle</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Cards/Demonia.Demonia</t>
+    <t>/Game/External_Assets/UI/Character/CharacterSkills/Icon_PassiveSkill/Icon_PassiveSkill_Demonia.Icon_PassiveSkill_Demonia</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Ultimate.AM_Demonia_Ultimate</t>
   </si>
   <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Book.AM_Demonia_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Book_Skill.AM_Demonia_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Gun.AM_Demonia_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Gun_Skill.AM_Demonia_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Melee.AM_Demonia_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Melee_Skill.AM_Demonia_Melee_Skill")))</t>
+    <t>((Magic, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Book.AM_Demonia_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Book_Skill.AM_Demonia_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Gun.AM_Demonia_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Gun_Skill.AM_Demonia_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Melee.AM_Demonia_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Demonia/AM_Demonia_Melee_Skill.AM_Demonia_Melee_Skill")))</t>
   </si>
   <si>
     <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Demonia.DA_CharFX_Demonia",BasicAttackTag=(TagName="FX.Character.Demonia.BasicAttack"),SkillTag=(TagName="FX.Character.Demonia.WeaponSkill"),UltimateTag=(TagName="FX.Character.Demonia.Ultimate"),UltimateHitTag=(TagName="FX.Character.Demonia.UltimateHit"),HitTag=(TagName="FX.Character.Demonia.Hit"),DeathTag=(TagName="FX.Character.Demonia.Death"))</t>
@@ -354,7 +363,7 @@
     <t>Char_Enchanter</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Enchanter.Icon_Enchanter</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Enchanter.Enchanter</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Enchanter.Icon_Enchanter</t>
@@ -363,13 +372,13 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Enchanter/Ani/Enchanter_Base_Battle_Idle_Anim_Take_001.Enchanter_Base_Battle_Idle_Anim_Take_001</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Cards/Enchanter.Enchanter</t>
+    <t>/Game/External_Assets/UI/Character/CharacterSkills/Icon_PassiveSkill/Icon_PassiveSkill_Enchanter.Icon_PassiveSkill_Enchanter</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Ultimate.AM_Enchanter_Ultimate</t>
   </si>
   <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Book.AM_Enchanter_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Book_Skill.AM_Enchanter_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Gun.AM_Enchanter_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Gun_Skill.AM_Enchanter_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Melee.AM_Enchanter_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Melee_Skill.AM_Enchanter_Melee_Skill")))</t>
+    <t>((Magic, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Book.AM_Enchanter_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Book_Skill.AM_Enchanter_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Gun.AM_Enchanter_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Gun_Skill.AM_Enchanter_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Melee.AM_Enchanter_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Enchanter/AM_Enchanter_Melee_Skill.AM_Enchanter_Melee_Skill")))</t>
   </si>
   <si>
     <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Enchanter.DA_CharFX_Enchanter",BasicAttackTag=(TagName="FX.Character.Enchanter.BasicAttack"),SkillTag=(TagName="FX.Character.Enchanter.WeaponSkill"),UltimateTag=(TagName="FX.Character.Enchanter.Ultimate"),UltimateHitTag=(TagName="FX.Character.Enchanter.UltimateHit"),HitTag=(TagName="FX.Character.Enchanter.Hit"),DeathTag=(TagName="FX.Character.Enchanter.Death"))</t>
@@ -396,7 +405,7 @@
     <t>Char_Guard</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Guard.Icon_Guard</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Guard.Guard</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Guard.Icon_Guard</t>
@@ -405,13 +414,13 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Guard/Ani/Guard_Base_Battle_Idle.Guard_Base_Battle_Idle</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Cards/Guard.Guard</t>
+    <t>/Game/External_Assets/UI/Character/CharacterSkills/Icon_PassiveSkill/Icon_PassiveSkill_Guard.Icon_PassiveSkill_Guard</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Ultimate.AM_Guard_Ultimate</t>
   </si>
   <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Book.AM_Guard_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Book_Skill.AM_Guard_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Gun.AM_Guard_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Gun_Skill.AM_Guard_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Melee.AM_Guard_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Melee_Skill.AM_Guard_Melee_Skill")))</t>
+    <t>((Magic, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Book.AM_Guard_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Book_Skill.AM_Guard_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Gun.AM_Guard_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Gun_Skill.AM_Guard_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Melee.AM_Guard_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Guard/AM_Guard_Melee_Skill.AM_Guard_Melee_Skill")))</t>
   </si>
   <si>
     <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Guard.DA_CharFX_Guard",BasicAttackTag=(TagName="FX.Character.Guard.BasicAttack"),SkillTag=(TagName="FX.Character.Guard.WeaponSkill"),UltimateTag=(TagName="FX.Character.Guard.Ultimate"),UltimateHitTag=(TagName="FX.Character.Guard.UltimateHit"),HitTag=(TagName="FX.Character.Guard.Hit"),DeathTag=(TagName="FX.Character.Guard.Death"))</t>
@@ -438,7 +447,7 @@
     <t>Char_Hermit</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Hermit.Icon_Hermit</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Hermit.Hermit</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Hermit.Icon_Hermit</t>
@@ -447,13 +456,13 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Hermit/Ani/Hermit_Base_Battle_Idle_Anim_Hermit_Battle_Idle.Hermit_Base_Battle_Idle_Anim_Hermit_Battle_Idle</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Cards/Hermit.Hermit</t>
+    <t>/Game/External_Assets/UI/Character/CharacterSkills/Icon_PassiveSkill/Icon_PassiveSkill_Hermit.Icon_PassiveSkill_Hermit</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Ultimate.AM_Hermit_Ultimate</t>
   </si>
   <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Book.AM_Hermit_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Book_Skill.AM_Hermit_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Gun.AM_Hermit_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Gun_Skill.AM_Hermit_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Melee.AM_Hermit_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Melee_Skill.AM_Hermit_Melee_Skill")))</t>
+    <t>((Magic, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Book.AM_Hermit_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Book_Skill.AM_Hermit_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Gun.AM_Hermit_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Gun_Skill.AM_Hermit_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Melee.AM_Hermit_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hermit/AM_Hermit_Melee_Skill.AM_Hermit_Melee_Skill")))</t>
   </si>
   <si>
     <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Hermit.DA_CharFX_Hermit",BasicAttackTag=(TagName="FX.Character.Hermit.BasicAttack"),SkillTag=(TagName="FX.Character.Hermit.WeaponSkill"),UltimateTag=(TagName="FX.Character.Hermit.Ultimate"),UltimateHitTag=(TagName="FX.Character.Hermit.UltimateHit"),HitTag=(TagName="FX.Character.Hermit.Hit"),DeathTag=(TagName="FX.Character.Hermit.Death"))</t>
@@ -480,7 +489,7 @@
     <t>Char_Hornet</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Hornet.Icon_Hornet</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Hornet.Hornet</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Hornet.Icon_Hornet</t>
@@ -489,13 +498,13 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Hornet/Ani/Hornet_Base_Battle_Idle.Hornet_Base_Battle_Idle</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Cards/Hornet.Hornet</t>
+    <t>/Game/External_Assets/UI/Character/CharacterSkills/Icon_PassiveSkill/Icon_PassiveSkill_Hornet.Icon_PassiveSkill_Hornet</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Ultimate.AM_Hornet_Ultimate</t>
   </si>
   <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Book.AM_Hornet_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Book_Skill.AM_Hornet_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Gun.AM_Hornet_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Gun_Skill.AM_Hornet_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Melee.AM_Hornet_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Melee_Skill.AM_Hornet_Melee_Skill")))</t>
+    <t>((Magic, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Book.AM_Hornet_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Book_Skill.AM_Hornet_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Gun.AM_Hornet_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Gun_Skill.AM_Hornet_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Melee.AM_Hornet_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Hornet/AM_Hornet_Melee_Skill.AM_Hornet_Melee_Skill")))</t>
   </si>
   <si>
     <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Hornet.DA_CharFX_Hornet",BasicAttackTag=(TagName="FX.Character.Hornet.BasicAttack"),SkillTag=(TagName="FX.Character.Hornet.WeaponSkill"),UltimateTag=(TagName="FX.Character.Hornet.Ultimate"),UltimateHitTag=(TagName="FX.Character.Hornet.UltimateHit"),HitTag=(TagName="FX.Character.Hornet.Hit"),DeathTag=(TagName="FX.Character.Hornet.Death"))</t>
@@ -522,7 +531,7 @@
     <t>Char_Looter</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Looter.Icon_Looter</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Looter.Looter</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Looter.Icon_Looter</t>
@@ -531,13 +540,13 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Looter/Ani/Looter_Base_Battle_Idle.Looter_Base_Battle_Idle</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Cards/Looter.Looter</t>
+    <t>/Game/External_Assets/UI/Character/CharacterSkills/Icon_PassiveSkill/Icon_PassiveSkill_Looter.Icon_PassiveSkill_Looter</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Ultimate.AM_Looter_Ultimate</t>
   </si>
   <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Book.AM_Looter_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Book_Skill.AM_Looter_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Gun.AM_Looter_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Gun_Skill.AM_Looter_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Melee.AM_Looter_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Melee_Skill.AM_Looter_Melee_Skill")))</t>
+    <t>((Magic, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Book.AM_Looter_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Book_Skill.AM_Looter_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Gun.AM_Looter_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Gun_Skill.AM_Looter_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Melee.AM_Looter_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Melee_Skill.AM_Looter_Melee_Skill")))</t>
   </si>
   <si>
     <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Looter.DA_CharFX_Looter",BasicAttackTag=(TagName="FX.Character.Looter.BasicAttack"),SkillTag=(TagName="FX.Character.Looter.WeaponSkill"),UltimateTag=(TagName="FX.Character.Looter.Ultimate"),UltimateHitTag=(TagName="FX.Character.Looter.UltimateHit"),HitTag=(TagName="FX.Character.Looter.Hit"),DeathTag=(TagName="FX.Character.Looter.Death"))</t>
@@ -552,7 +561,7 @@
     <t>/Game/External_Assets/UI/Character/AvatarThumb/Icon_Looter.Icon_Looter</t>
   </si>
   <si>
-    <t>None</t>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Char_Player/Looter/ABP_Looter.ABP_Looter_C'</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Char_Player/Looter/AM_Looter_Damage.AM_Looter_Damage</t>
@@ -564,7 +573,7 @@
     <t>Char_Maid</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Maid.Icon_Maid</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Maid.Maid</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Maid.Icon_Maid</t>
@@ -573,13 +582,13 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Maid/Ani/Maid_Base_Idle_Battle.Maid_Base_Idle_Battle</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Cards/Maid.Maid</t>
+    <t>/Game/External_Assets/UI/Character/CharacterSkills/Icon_PassiveSkill/Icon_PassiveSkill_Maid.Icon_PassiveSkill_Maid</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Ultimate.AM_Maid_Ultimate</t>
   </si>
   <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Book.AM_Maid_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Book_Skill.AM_Maid_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Gun.AM_Maid_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Gun_Skill.AM_Maid_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Melee.AM_Maid_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Melee_Skill.AM_Maid_Melee_Skill")))</t>
+    <t>((Magic, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Book.AM_Maid_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Book_Skill.AM_Maid_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Gun.AM_Maid_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Gun_Skill.AM_Maid_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Melee.AM_Maid_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Maid/AM_Maid_Melee_Skill.AM_Maid_Melee_Skill")))</t>
   </si>
   <si>
     <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Maid.DA_CharFX_Maid",BasicAttackTag=(TagName="FX.Character.Maid.BasicAttack"),SkillTag=(TagName="FX.Character.Maid.WeaponSkill"),UltimateTag=(TagName="FX.Character.Maid.Ultimate"),UltimateHitTag=(TagName="FX.Character.Maid.UltimateHit"),HitTag=(TagName="FX.Character.Maid.Hit"),DeathTag=(TagName="FX.Character.Maid.Death"))</t>
@@ -606,7 +615,7 @@
     <t>Char_Merry</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Merry.Icon_Merry</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Merry.Merry</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Merry.Icon_Merry</t>
@@ -615,13 +624,13 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Merry/Ani/Merry_Base_Battle_Idle.Merry_Base_Battle_Idle</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Cards/Merry.Merry</t>
+    <t>/Game/External_Assets/UI/Character/CharacterSkills/Icon_PassiveSkill/Icon_PassiveSkill_Merry.Icon_PassiveSkill_Merry</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Ultimate.AM_Merry_Ultimate</t>
   </si>
   <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Book.AM_Merry_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Book_Skill.AM_Merry_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Gun.AM_Merry_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Gun_Skill.AM_Merry_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Melee.AM_Merry_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Melee_Skill.AM_Merry_Melee_Skill")))</t>
+    <t>((Magic, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Book.AM_Merry_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Book_Skill.AM_Merry_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Gun.AM_Merry_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Gun_Skill.AM_Merry_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Melee.AM_Merry_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Merry/AM_Merry_Melee_Skill.AM_Merry_Melee_Skill")))</t>
   </si>
   <si>
     <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Merry.DA_CharFX_Merry",BasicAttackTag=(TagName="FX.Character.Merry.BasicAttack"),SkillTag=(TagName="FX.Character.Merry.WeaponSkill"),UltimateTag=(TagName="FX.Character.Merry.Ultimate"),UltimateHitTag=(TagName="FX.Character.Merry.UltimateHit"),HitTag=(TagName="FX.Character.Merry.Hit"),DeathTag=(TagName="FX.Character.Merry.Death"))</t>
@@ -648,7 +657,7 @@
     <t>Char_Muzzle</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Muzzle.Icon_Muzzle</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Muzzle.Muzzle</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Muzzle.Icon_Muzzle</t>
@@ -657,13 +666,13 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Muzzle/Ani/Muzzle_Base_Lobby_Idle_NoWeapon.Muzzle_Base_Lobby_Idle_NoWeapon</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Cards/Muzzle.Muzzle</t>
+    <t>/Game/External_Assets/UI/Character/CharacterSkills/Icon_PassiveSkill/Icon_PassiveSkill_Muzzle.Icon_PassiveSkill_Muzzle</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Ultimate.AM_Muzzle_Ultimate</t>
   </si>
   <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Book.AM_Muzzle_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Book_Skill.AM_Muzzle_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Gun.AM_Muzzle_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Gun_Skill.AM_Muzzle_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Melee.AM_Muzzle_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Melee_Skill.AM_Muzzle_Melee_Skill")))</t>
+    <t>((Magic, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Book.AM_Muzzle_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Book_Skill.AM_Muzzle_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Gun.AM_Muzzle_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Gun_Skill.AM_Muzzle_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Melee.AM_Muzzle_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Muzzle/AM_Muzzle_Melee_Skill.AM_Muzzle_Melee_Skill")))</t>
   </si>
   <si>
     <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Muzzle.DA_CharFX_Muzzle",BasicAttackTag=(TagName="FX.Character.Muzzle.BasicAttack"),SkillTag=(TagName="FX.Character.Muzzle.WeaponSkill"),UltimateTag=(TagName="FX.Character.Muzzle.Ultimate"),UltimateHitTag=(TagName="FX.Character.Muzzle.UltimateHit"),HitTag=(TagName="FX.Character.Muzzle.Hit"),DeathTag=(TagName="FX.Character.Muzzle.Death"))</t>
@@ -690,7 +699,7 @@
     <t>Char_Noble</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Noble.Icon_Noble</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Noble.Noble</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Noble.Icon_Noble</t>
@@ -699,13 +708,13 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Noble/Ani/Noble_Base_Battle_Idle_Anim_Take_0011.Noble_Base_Battle_Idle_Anim_Take_0011</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Cards/Noble.Noble</t>
+    <t>/Game/External_Assets/UI/Character/CharacterSkills/Icon_PassiveSkill/Icon_PassiveSkill_Noble.Icon_PassiveSkill_Noble</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Ultimate.AM_Noble_Ultimate</t>
   </si>
   <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Book.AM_Noble_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Book_Skill.AM_Noble_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Gun.AM_Noble_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Gun_Skill.AM_Noble_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Melee.AM_Noble_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Melee_Skill.AM_Noble_Melee_Skill")))</t>
+    <t>((Magic, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Book.AM_Noble_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Book_Skill.AM_Noble_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Gun.AM_Noble_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Gun_Skill.AM_Noble_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Melee.AM_Noble_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Noble/AM_Noble_Melee_Skill.AM_Noble_Melee_Skill")))</t>
   </si>
   <si>
     <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Noble.DA_CharFX_Noble",BasicAttackTag=(TagName="FX.Character.Noble.BasicAttack"),SkillTag=(TagName="FX.Character.Noble.WeaponSkill"),UltimateTag=(TagName="FX.Character.Noble.Ultimate"),UltimateHitTag=(TagName="FX.Character.Noble.UltimateHit"),HitTag=(TagName="FX.Character.Noble.Hit"),DeathTag=(TagName="FX.Character.Noble.Death"))</t>
@@ -732,7 +741,7 @@
     <t>Char_Nurse</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Nurse.Icon_Nurse</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Nurse.Nurse</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Nurse.Icon_Nurse</t>
@@ -741,13 +750,13 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Nurse/Ani/Nurse_Base_Battle_Idle.Nurse_Base_Battle_Idle</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Cards/Nurse.Nurse</t>
+    <t>/Game/External_Assets/UI/Character/CharacterSkills/Icon_PassiveSkill/Icon_PassiveSkill_Nurse.Icon_PassiveSkill_Nurse</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Ultimate.AM_Nurse_Ultimate</t>
   </si>
   <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Book.AM_Nurse_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Book_Skill.AM_Nurse_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Gun.AM_Nurse_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Gun_Skill.AM_Nurse_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Melee.AM_Nurse_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Melee_Skill.AM_Nurse_Melee_Skill")))</t>
+    <t>((Magic, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Book.AM_Nurse_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Book_Skill.AM_Nurse_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Gun.AM_Nurse_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Gun_Skill.AM_Nurse_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Melee.AM_Nurse_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Nurse/AM_Nurse_Melee_Skill.AM_Nurse_Melee_Skill")))</t>
   </si>
   <si>
     <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Nurse.DA_CharFX_Nurse",BasicAttackTag=(TagName="FX.Character.Nurse.BasicAttack"),SkillTag=(TagName="FX.Character.Nurse.WeaponSkill"),UltimateTag=(TagName="FX.Character.Nurse.Ultimate"),UltimateHitTag=(TagName="FX.Character.Nurse.UltimateHit"),HitTag=(TagName="FX.Character.Nurse.Hit"),DeathTag=(TagName="FX.Character.Nurse.Death"))</t>
@@ -774,7 +783,7 @@
     <t>Char_Outsider</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Outsider.Icon_Outsider</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Outsider.Outsider</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Outsider.Icon_Outsider</t>
@@ -783,13 +792,13 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Outsider/Ani/Outsider_Base_Battle_Idle.Outsider_Base_Battle_Idle</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Cards/Outsider.Outsider</t>
+    <t>/Game/External_Assets/UI/Character/CharacterSkills/Icon_PassiveSkill/Icon_PassiveSkill_Outsider.Icon_PassiveSkill_Outsider</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Ultimate.AM_Outsider_Ultimate</t>
   </si>
   <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Book.AM_Outsider_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Book_Skill.AM_Outsider_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Gun.AM_Outsider_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Gun_Skill.AM_Outsider_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Melee.AM_Outsider_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Melee_Skill.AM_Outsider_Melee_Skill")))</t>
+    <t>((Magic, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Book.AM_Outsider_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Book_Skill.AM_Outsider_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Gun.AM_Outsider_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Gun_Skill.AM_Outsider_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Melee.AM_Outsider_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Outsider/AM_Outsider_Melee_Skill.AM_Outsider_Melee_Skill")))</t>
   </si>
   <si>
     <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Outsider.DA_CharFX_Outsider",BasicAttackTag=(TagName="FX.Character.Outsider.BasicAttack"),SkillTag=(TagName="FX.Character.Outsider.WeaponSkill"),UltimateTag=(TagName="FX.Character.Outsider.Ultimate"),UltimateHitTag=(TagName="FX.Character.Outsider.UltimateHit"),HitTag=(TagName="FX.Character.Outsider.Hit"),DeathTag=(TagName="FX.Character.Outsider.Death"))</t>
@@ -816,7 +825,7 @@
     <t>Char_Pioneer</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Pioneer.Icon_Pioneer</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Pioneer.Pioneer</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Pioneer.Icon_Pioneer</t>
@@ -825,13 +834,13 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Pioneer/Ani/Pioneer_Base_Battle_Idle.Pioneer_Base_Battle_Idle</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Cards/Pioneer.Pioneer</t>
+    <t>/Game/External_Assets/UI/Character/CharacterSkills/Icon_PassiveSkill/Icon_PassiveSkill_Pioneer.Icon_PassiveSkill_Pioneer</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Ultimate.AM_Pioneer_Ultimate</t>
   </si>
   <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Book.AM_Pioneer_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Book_Skill.AM_Pioneer_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Gun.AM_Pioneer_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Gun_Skill.AM_Pioneer_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Melee.AM_Pioneer_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Melee_Skill.AM_Pioneer_Melee_Skill")))</t>
+    <t>((Magic, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Book.AM_Pioneer_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Book_Skill.AM_Pioneer_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Gun.AM_Pioneer_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Gun_Skill.AM_Pioneer_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Melee.AM_Pioneer_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Pioneer/AM_Pioneer_Melee_Skill.AM_Pioneer_Melee_Skill")))</t>
   </si>
   <si>
     <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Pioneer.DA_CharFX_Pioneer",BasicAttackTag=(TagName="FX.Character.Pioneer.BasicAttack"),SkillTag=(TagName="FX.Character.Pioneer.WeaponSkill"),UltimateTag=(TagName="FX.Character.Pioneer.Ultimate"),UltimateHitTag=(TagName="FX.Character.Pioneer.UltimateHit"),HitTag=(TagName="FX.Character.Pioneer.Hit"),DeathTag=(TagName="FX.Character.Pioneer.Death"))</t>
@@ -858,7 +867,7 @@
     <t>Char_Rogue</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Rogue.Icon_Rogue</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Rogue.Rogue</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Rogue.Icon_Rogue</t>
@@ -867,13 +876,13 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Rogue/Ani/Rogue_Base_Battle_Idle_Anim_Rogue_Base_Battle_Idle.Rogue_Base_Battle_Idle_Anim_Rogue_Base_Battle_Idle</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Cards/Rogue.Rogue</t>
+    <t>/Game/External_Assets/UI/Character/CharacterSkills/Icon_PassiveSkill/Icon_PassiveSkill_Rogue.Icon_PassiveSkill_Rogue</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Ultimate.AM_Rogue_Ultimate</t>
   </si>
   <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Book.AM_Rogue_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Book_Skill.AM_Rogue_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Gun.AM_Rogue_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Gun_Skill.AM_Rogue_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Melee.AM_Rogue_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Melee_Skill.AM_Rogue_Melee_Skill")))</t>
+    <t>((Magic, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Book.AM_Rogue_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Book_Skill.AM_Rogue_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Gun.AM_Rogue_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Gun_Skill.AM_Rogue_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Melee.AM_Rogue_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Rogue/AM_Rogue_Melee_Skill.AM_Rogue_Melee_Skill")))</t>
   </si>
   <si>
     <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Rogue.DA_CharFX_Rogue",BasicAttackTag=(TagName="FX.Character.Rogue.BasicAttack"),SkillTag=(TagName="FX.Character.Rogue.WeaponSkill"),UltimateTag=(TagName="FX.Character.Rogue.Ultimate"),UltimateHitTag=(TagName="FX.Character.Rogue.UltimateHit"),HitTag=(TagName="FX.Character.Rogue.Hit"),DeathTag=(TagName="FX.Character.Rogue.Death"))</t>
@@ -900,7 +909,7 @@
     <t>Char_Tinker</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Tinker.Icon_Tinker</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Tinker.Tinker</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Tinker.Icon_Tinker</t>
@@ -909,13 +918,13 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Tinker/Ani/Tinker_Base_Battle_Idle_Anim_Tinker_Base_Battle_Idle.Tinker_Base_Battle_Idle_Anim_Tinker_Base_Battle_Idle</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Cards/Tinker.Tinker</t>
+    <t>/Game/External_Assets/UI/Character/CharacterSkills/Icon_PassiveSkill/Icon_PassiveSkill_Tinker.Icon_PassiveSkill_Tinker</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Ultimate.AM_Tinker_Ultimate</t>
   </si>
   <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Book.AM_Tinker_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Book_Skill.AM_Tinker_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Gun.AM_Tinker_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Gun_Skill.AM_Tinker_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Melee.AM_Tinker_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Melee_Skill.AM_Tinker_Melee_Skill")))</t>
+    <t>((Magic, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Book.AM_Tinker_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Book_Skill.AM_Tinker_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Gun.AM_Tinker_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Gun_Skill.AM_Tinker_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Melee.AM_Tinker_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Tinker/AM_Tinker_Melee_Skill.AM_Tinker_Melee_Skill")))</t>
   </si>
   <si>
     <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Tinker.DA_CharFX_Tinker",BasicAttackTag=(TagName="FX.Character.Tinker.BasicAttack"),SkillTag=(TagName="FX.Character.Tinker.WeaponSkill"),UltimateTag=(TagName="FX.Character.Tinker.Ultimate"),UltimateHitTag=(TagName="FX.Character.Tinker.UltimateHit"),HitTag=(TagName="FX.Character.Tinker.Hit"),DeathTag=(TagName="FX.Character.Tinker.Death"))</t>
@@ -942,7 +951,7 @@
     <t>Char_Tuner</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Tuner.Icon_Tuner</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Tuner.Tuner</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Tuner.Icon_Tuner</t>
@@ -951,13 +960,13 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Tuner/Ani/Tuner_Base_Battle_Idle.Tuner_Base_Battle_Idle</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Cards/Tuner.Tuner</t>
+    <t>/Game/External_Assets/UI/Character/CharacterSkills/Icon_PassiveSkill/Icon_PassiveSkill_Tuner.Icon_PassiveSkill_Tuner</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Ultimate.AM_Tuner_Ultimate</t>
   </si>
   <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Book.AM_Tuner_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Book_Skill.AM_Tuner_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Gun.AM_Tuner_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Gun_Skill.AM_Tuner_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Melee.AM_Tuner_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Melee_Skill.AM_Tuner_Melee_Skill")))</t>
+    <t>((Magic, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Book.AM_Tuner_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Book_Skill.AM_Tuner_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Gun.AM_Tuner_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Gun_Skill.AM_Tuner_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Melee.AM_Tuner_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Tuner/AM_Tuner_Melee_Skill.AM_Tuner_Melee_Skill")))</t>
   </si>
   <si>
     <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Tuner.DA_CharFX_Tuner",BasicAttackTag=(TagName="FX.Character.Tuner.BasicAttack"),SkillTag=(TagName="FX.Character.Tuner.WeaponSkill"),UltimateTag=(TagName="FX.Character.Tuner.Ultimate"),UltimateHitTag=(TagName="FX.Character.Tuner.UltimateHit"),HitTag=(TagName="FX.Character.Tuner.Hit"),DeathTag=(TagName="FX.Character.Tuner.Death"))</t>
@@ -984,7 +993,7 @@
     <t>Char_Weaver</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Weaver.Icon_Weaver</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Weaver.Weaver</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Weaver.Icon_Weaver</t>
@@ -993,13 +1002,13 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Weaver/Ani/Weaver_Base_Battle_Idle_Anim_Take_001.Weaver_Base_Battle_Idle_Anim_Take_001</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Cards/Weaver.Weaver</t>
+    <t>/Game/External_Assets/UI/Character/CharacterSkills/Icon_PassiveSkill/Icon_PassiveSkill_Weaver.Icon_PassiveSkill_Weaver</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Ultimate.AM_Weaver_Ultimate</t>
   </si>
   <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Book.AM_Weaver_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Book_Skill.AM_Weaver_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Gun.AM_Weaver_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Gun_Skill.AM_Weaver_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Melee.AM_Weaver_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Melee_Skill.AM_Weaver_Melee_Skill")))</t>
+    <t>((Magic, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Book.AM_Weaver_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Book_Skill.AM_Weaver_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Gun.AM_Weaver_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Gun_Skill.AM_Weaver_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Melee.AM_Weaver_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Weaver/AM_Weaver_Melee_Skill.AM_Weaver_Melee_Skill")))</t>
   </si>
   <si>
     <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Weaver.DA_CharFX_Weaver",BasicAttackTag=(TagName="FX.Character.Weaver.BasicAttack"),SkillTag=(TagName="FX.Character.Weaver.WeaponSkill"),UltimateTag=(TagName="FX.Character.Weaver.Ultimate"),UltimateHitTag=(TagName="FX.Character.Weaver.UltimateHit"),HitTag=(TagName="FX.Character.Weaver.Hit"),DeathTag=(TagName="FX.Character.Weaver.Death"))</t>
@@ -1026,7 +1035,7 @@
     <t>Char_Writer</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Portrait/Icon_Writer.Icon_Writer</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Cards/Writer.Writer</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Character/Icon_Equipped/Icon_Writer.Icon_Writer</t>
@@ -1035,13 +1044,13 @@
     <t>/Game/External_Assets/ScaledPlayerMesh/Char_Writer/Ani/Writer_Base_Battle_Idle.Writer_Base_Battle_Idle</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Cards/Writer.Writer</t>
+    <t>/Game/External_Assets/UI/Character/CharacterSkills/Icon_PassiveSkill/Icon_PassiveSkill_Writer.Icon_PassiveSkill_Writer</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Ultimate.AM_Writer_Ultimate</t>
   </si>
   <si>
-    <t>((Book, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Book.AM_Writer_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Book_Skill.AM_Writer_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Gun.AM_Writer_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Gun_Skill.AM_Writer_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Melee.AM_Writer_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Melee_Skill.AM_Writer_Melee_Skill")))</t>
+    <t>((Magic, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Book.AM_Writer_Book",SkillMontage="/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Book_Skill.AM_Writer_Book_Skill")),(Gun, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Gun.AM_Writer_Gun",SkillMontage="/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Gun_Skill.AM_Writer_Gun_Skill")),(Melee, (BasicAttackMontage="/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Melee.AM_Writer_Melee",SkillMontage="/Game/Blueprints/Characters/Char_Player/Writer/AM_Writer_Melee_Skill.AM_Writer_Melee_Skill")))</t>
   </si>
   <si>
     <t>(FXData="/Game/Data/Assets/PlayerFXAssets/DA_CharFX_Writer.DA_CharFX_Writer",BasicAttackTag=(TagName="FX.Character.Writer.BasicAttack"),SkillTag=(TagName="FX.Character.Writer.WeaponSkill"),UltimateTag=(TagName="FX.Character.Writer.Ultimate"),UltimateHitTag=(TagName="FX.Character.Writer.UltimateHit"),HitTag=(TagName="FX.Character.Writer.Hit"),DeathTag=(TagName="FX.Character.Writer.Death"))</t>
@@ -1980,10 +1989,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2035,1224 +2044,1368 @@
       <c r="Q1" t="s">
         <v>16</v>
       </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2" t="s">
+        <v>31</v>
+      </c>
+      <c r="O2" t="s">
+        <v>32</v>
+      </c>
+      <c r="P2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>34</v>
+      </c>
+      <c r="R2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K3" t="s">
+        <v>45</v>
+      </c>
+      <c r="L3" t="s">
+        <v>46</v>
+      </c>
+      <c r="M3" t="s">
+        <v>47</v>
+      </c>
+      <c r="N3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3" t="s">
+        <v>48</v>
+      </c>
+      <c r="P3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>50</v>
+      </c>
+      <c r="R3" t="s">
+        <v>51</v>
+      </c>
+      <c r="S3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J4" t="s">
+        <v>60</v>
+      </c>
+      <c r="K4" t="s">
+        <v>61</v>
+      </c>
+      <c r="L4" t="s">
+        <v>62</v>
+      </c>
+      <c r="M4" t="s">
+        <v>63</v>
+      </c>
+      <c r="N4" t="s">
+        <v>31</v>
+      </c>
+      <c r="O4" t="s">
+        <v>64</v>
+      </c>
+      <c r="P4" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R4" t="s">
+        <v>67</v>
+      </c>
+      <c r="S4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K5" t="s">
+        <v>76</v>
+      </c>
+      <c r="L5" t="s">
+        <v>77</v>
+      </c>
+      <c r="M5" t="s">
+        <v>78</v>
+      </c>
+      <c r="N5" t="s">
+        <v>31</v>
+      </c>
+      <c r="O5" t="s">
+        <v>79</v>
+      </c>
+      <c r="P5" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>81</v>
+      </c>
+      <c r="R5" t="s">
+        <v>82</v>
+      </c>
+      <c r="S5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H6" t="s">
+        <v>89</v>
+      </c>
+      <c r="I6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" t="s">
+        <v>90</v>
+      </c>
+      <c r="K6" t="s">
+        <v>91</v>
+      </c>
+      <c r="L6" t="s">
+        <v>92</v>
+      </c>
+      <c r="M6" t="s">
+        <v>93</v>
+      </c>
+      <c r="N6" t="s">
+        <v>31</v>
+      </c>
+      <c r="O6" t="s">
+        <v>94</v>
+      </c>
+      <c r="P6" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>96</v>
+      </c>
+      <c r="R6" t="s">
+        <v>97</v>
+      </c>
+      <c r="S6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" t="s">
+        <v>103</v>
+      </c>
+      <c r="H7" t="s">
         <v>25</v>
       </c>
-      <c r="J2" t="s">
+      <c r="I7" t="s">
         <v>26</v>
       </c>
-      <c r="K2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L2" t="s">
-        <v>28</v>
-      </c>
-      <c r="M2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N2" t="s">
-        <v>30</v>
-      </c>
-      <c r="O2" t="s">
+      <c r="J7" t="s">
+        <v>104</v>
+      </c>
+      <c r="K7" t="s">
+        <v>105</v>
+      </c>
+      <c r="L7" t="s">
+        <v>106</v>
+      </c>
+      <c r="M7" t="s">
+        <v>107</v>
+      </c>
+      <c r="N7" t="s">
         <v>31</v>
       </c>
-      <c r="P2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>33</v>
+      <c r="O7" t="s">
+        <v>108</v>
+      </c>
+      <c r="P7" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>110</v>
+      </c>
+      <c r="R7" t="s">
+        <v>111</v>
+      </c>
+      <c r="S7" t="s">
+        <v>112</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I3" t="s">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B8" t="s">
+        <v>114</v>
+      </c>
+      <c r="C8" t="s">
+        <v>115</v>
+      </c>
+      <c r="D8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" t="s">
+        <v>117</v>
+      </c>
+      <c r="H8" t="s">
+        <v>89</v>
+      </c>
+      <c r="I8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" t="s">
+        <v>118</v>
+      </c>
+      <c r="K8" t="s">
+        <v>119</v>
+      </c>
+      <c r="L8" t="s">
+        <v>120</v>
+      </c>
+      <c r="M8" t="s">
+        <v>121</v>
+      </c>
+      <c r="N8" t="s">
+        <v>31</v>
+      </c>
+      <c r="O8" t="s">
+        <v>122</v>
+      </c>
+      <c r="P8" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>124</v>
+      </c>
+      <c r="R8" t="s">
+        <v>125</v>
+      </c>
+      <c r="S8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C9" t="s">
+        <v>129</v>
+      </c>
+      <c r="D9" t="s">
+        <v>130</v>
+      </c>
+      <c r="E9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" t="s">
+        <v>131</v>
+      </c>
+      <c r="H9" t="s">
         <v>42</v>
       </c>
-      <c r="J3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K3" t="s">
-        <v>44</v>
-      </c>
-      <c r="L3" t="s">
-        <v>28</v>
-      </c>
-      <c r="M3" t="s">
-        <v>45</v>
-      </c>
-      <c r="N3" t="s">
-        <v>46</v>
-      </c>
-      <c r="O3" t="s">
-        <v>47</v>
-      </c>
-      <c r="P3" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>49</v>
+      <c r="I9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J9" t="s">
+        <v>132</v>
+      </c>
+      <c r="K9" t="s">
+        <v>133</v>
+      </c>
+      <c r="L9" t="s">
+        <v>134</v>
+      </c>
+      <c r="M9" t="s">
+        <v>135</v>
+      </c>
+      <c r="N9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O9" t="s">
+        <v>136</v>
+      </c>
+      <c r="P9" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>138</v>
+      </c>
+      <c r="R9" t="s">
+        <v>139</v>
+      </c>
+      <c r="S9" t="s">
+        <v>140</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G4" t="s">
-        <v>56</v>
-      </c>
-      <c r="H4" t="s">
-        <v>57</v>
-      </c>
-      <c r="I4" t="s">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>141</v>
+      </c>
+      <c r="B10" t="s">
+        <v>142</v>
+      </c>
+      <c r="C10" t="s">
+        <v>143</v>
+      </c>
+      <c r="D10" t="s">
+        <v>144</v>
+      </c>
+      <c r="E10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" t="s">
+        <v>145</v>
+      </c>
+      <c r="H10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" t="s">
+        <v>146</v>
+      </c>
+      <c r="K10" t="s">
+        <v>147</v>
+      </c>
+      <c r="L10" t="s">
+        <v>148</v>
+      </c>
+      <c r="M10" t="s">
+        <v>149</v>
+      </c>
+      <c r="N10" t="s">
+        <v>31</v>
+      </c>
+      <c r="O10" t="s">
+        <v>150</v>
+      </c>
+      <c r="P10" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>152</v>
+      </c>
+      <c r="R10" t="s">
+        <v>153</v>
+      </c>
+      <c r="S10" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>155</v>
+      </c>
+      <c r="B11" t="s">
+        <v>156</v>
+      </c>
+      <c r="C11" t="s">
+        <v>157</v>
+      </c>
+      <c r="D11" t="s">
+        <v>158</v>
+      </c>
+      <c r="E11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" t="s">
+        <v>159</v>
+      </c>
+      <c r="H11" t="s">
+        <v>42</v>
+      </c>
+      <c r="I11" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11" t="s">
+        <v>160</v>
+      </c>
+      <c r="K11" t="s">
+        <v>161</v>
+      </c>
+      <c r="L11" t="s">
+        <v>162</v>
+      </c>
+      <c r="M11" t="s">
+        <v>163</v>
+      </c>
+      <c r="N11" t="s">
+        <v>31</v>
+      </c>
+      <c r="O11" t="s">
+        <v>164</v>
+      </c>
+      <c r="P11" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>166</v>
+      </c>
+      <c r="R11" t="s">
+        <v>167</v>
+      </c>
+      <c r="S11" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>169</v>
+      </c>
+      <c r="B12" t="s">
+        <v>170</v>
+      </c>
+      <c r="C12" t="s">
+        <v>171</v>
+      </c>
+      <c r="D12" t="s">
+        <v>172</v>
+      </c>
+      <c r="E12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" t="s">
+        <v>173</v>
+      </c>
+      <c r="H12" t="s">
         <v>58</v>
       </c>
-      <c r="J4" t="s">
+      <c r="I12" t="s">
+        <v>26</v>
+      </c>
+      <c r="J12" t="s">
+        <v>174</v>
+      </c>
+      <c r="K12" t="s">
+        <v>175</v>
+      </c>
+      <c r="L12" t="s">
+        <v>176</v>
+      </c>
+      <c r="M12" t="s">
+        <v>177</v>
+      </c>
+      <c r="N12" t="s">
+        <v>31</v>
+      </c>
+      <c r="O12" t="s">
+        <v>178</v>
+      </c>
+      <c r="P12" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>180</v>
+      </c>
+      <c r="R12" t="s">
+        <v>181</v>
+      </c>
+      <c r="S12" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>183</v>
+      </c>
+      <c r="B13" t="s">
+        <v>184</v>
+      </c>
+      <c r="C13" t="s">
+        <v>185</v>
+      </c>
+      <c r="D13" t="s">
+        <v>186</v>
+      </c>
+      <c r="E13" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" t="s">
+        <v>187</v>
+      </c>
+      <c r="H13" t="s">
+        <v>74</v>
+      </c>
+      <c r="I13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J13" t="s">
+        <v>188</v>
+      </c>
+      <c r="K13" t="s">
+        <v>189</v>
+      </c>
+      <c r="L13" t="s">
+        <v>190</v>
+      </c>
+      <c r="M13" t="s">
+        <v>191</v>
+      </c>
+      <c r="N13" t="s">
+        <v>31</v>
+      </c>
+      <c r="O13" t="s">
+        <v>192</v>
+      </c>
+      <c r="P13" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>194</v>
+      </c>
+      <c r="R13" t="s">
+        <v>195</v>
+      </c>
+      <c r="S13" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>197</v>
+      </c>
+      <c r="B14" t="s">
+        <v>198</v>
+      </c>
+      <c r="C14" t="s">
+        <v>199</v>
+      </c>
+      <c r="D14" t="s">
+        <v>200</v>
+      </c>
+      <c r="E14" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" t="s">
+        <v>201</v>
+      </c>
+      <c r="H14" t="s">
+        <v>58</v>
+      </c>
+      <c r="I14" t="s">
+        <v>26</v>
+      </c>
+      <c r="J14" t="s">
+        <v>202</v>
+      </c>
+      <c r="K14" t="s">
+        <v>203</v>
+      </c>
+      <c r="L14" t="s">
+        <v>204</v>
+      </c>
+      <c r="M14" t="s">
+        <v>205</v>
+      </c>
+      <c r="N14" t="s">
+        <v>31</v>
+      </c>
+      <c r="O14" t="s">
+        <v>206</v>
+      </c>
+      <c r="P14" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>208</v>
+      </c>
+      <c r="R14" t="s">
+        <v>209</v>
+      </c>
+      <c r="S14" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>211</v>
+      </c>
+      <c r="B15" t="s">
+        <v>212</v>
+      </c>
+      <c r="C15" t="s">
+        <v>213</v>
+      </c>
+      <c r="D15" t="s">
+        <v>214</v>
+      </c>
+      <c r="E15" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" t="s">
+        <v>215</v>
+      </c>
+      <c r="H15" t="s">
+        <v>58</v>
+      </c>
+      <c r="I15" t="s">
         <v>59</v>
       </c>
-      <c r="K4" t="s">
-        <v>60</v>
-      </c>
-      <c r="L4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M4" t="s">
-        <v>61</v>
-      </c>
-      <c r="N4" t="s">
-        <v>62</v>
-      </c>
-      <c r="O4" t="s">
-        <v>63</v>
-      </c>
-      <c r="P4" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>65</v>
+      <c r="J15" t="s">
+        <v>216</v>
+      </c>
+      <c r="K15" t="s">
+        <v>217</v>
+      </c>
+      <c r="L15" t="s">
+        <v>218</v>
+      </c>
+      <c r="M15" t="s">
+        <v>219</v>
+      </c>
+      <c r="N15" t="s">
+        <v>31</v>
+      </c>
+      <c r="O15" t="s">
+        <v>220</v>
+      </c>
+      <c r="P15" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>222</v>
+      </c>
+      <c r="R15" t="s">
+        <v>223</v>
+      </c>
+      <c r="S15" t="s">
+        <v>224</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F5" t="s">
-        <v>71</v>
-      </c>
-      <c r="G5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" t="s">
-        <v>72</v>
-      </c>
-      <c r="I5" t="s">
-        <v>73</v>
-      </c>
-      <c r="J5" t="s">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>225</v>
+      </c>
+      <c r="B16" t="s">
+        <v>226</v>
+      </c>
+      <c r="C16" t="s">
+        <v>227</v>
+      </c>
+      <c r="D16" t="s">
+        <v>228</v>
+      </c>
+      <c r="E16" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" t="s">
+        <v>229</v>
+      </c>
+      <c r="H16" t="s">
+        <v>25</v>
+      </c>
+      <c r="I16" t="s">
+        <v>26</v>
+      </c>
+      <c r="J16" t="s">
+        <v>230</v>
+      </c>
+      <c r="K16" t="s">
+        <v>231</v>
+      </c>
+      <c r="L16" t="s">
+        <v>232</v>
+      </c>
+      <c r="M16" t="s">
+        <v>233</v>
+      </c>
+      <c r="N16" t="s">
+        <v>31</v>
+      </c>
+      <c r="O16" t="s">
+        <v>234</v>
+      </c>
+      <c r="P16" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>236</v>
+      </c>
+      <c r="R16" t="s">
+        <v>237</v>
+      </c>
+      <c r="S16" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>239</v>
+      </c>
+      <c r="B17" t="s">
+        <v>240</v>
+      </c>
+      <c r="C17" t="s">
+        <v>241</v>
+      </c>
+      <c r="D17" t="s">
+        <v>242</v>
+      </c>
+      <c r="E17" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" t="s">
+        <v>243</v>
+      </c>
+      <c r="H17" t="s">
+        <v>58</v>
+      </c>
+      <c r="I17" t="s">
+        <v>26</v>
+      </c>
+      <c r="J17" t="s">
+        <v>244</v>
+      </c>
+      <c r="K17" t="s">
+        <v>245</v>
+      </c>
+      <c r="L17" t="s">
+        <v>246</v>
+      </c>
+      <c r="M17" t="s">
+        <v>247</v>
+      </c>
+      <c r="N17" t="s">
+        <v>31</v>
+      </c>
+      <c r="O17" t="s">
+        <v>248</v>
+      </c>
+      <c r="P17" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>250</v>
+      </c>
+      <c r="R17" t="s">
+        <v>251</v>
+      </c>
+      <c r="S17" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>253</v>
+      </c>
+      <c r="B18" t="s">
+        <v>254</v>
+      </c>
+      <c r="C18" t="s">
+        <v>255</v>
+      </c>
+      <c r="D18" t="s">
+        <v>256</v>
+      </c>
+      <c r="E18" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" t="s">
+        <v>257</v>
+      </c>
+      <c r="H18" t="s">
         <v>74</v>
       </c>
-      <c r="K5" t="s">
-        <v>75</v>
-      </c>
-      <c r="L5" t="s">
-        <v>28</v>
-      </c>
-      <c r="M5" t="s">
-        <v>76</v>
-      </c>
-      <c r="N5" t="s">
-        <v>77</v>
-      </c>
-      <c r="O5" t="s">
-        <v>78</v>
-      </c>
-      <c r="P5" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>80</v>
+      <c r="I18" t="s">
+        <v>26</v>
+      </c>
+      <c r="J18" t="s">
+        <v>258</v>
+      </c>
+      <c r="K18" t="s">
+        <v>259</v>
+      </c>
+      <c r="L18" t="s">
+        <v>260</v>
+      </c>
+      <c r="M18" t="s">
+        <v>261</v>
+      </c>
+      <c r="N18" t="s">
+        <v>31</v>
+      </c>
+      <c r="O18" t="s">
+        <v>262</v>
+      </c>
+      <c r="P18" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>264</v>
+      </c>
+      <c r="R18" t="s">
+        <v>265</v>
+      </c>
+      <c r="S18" t="s">
+        <v>266</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D6" t="s">
-        <v>84</v>
-      </c>
-      <c r="E6" t="s">
-        <v>85</v>
-      </c>
-      <c r="F6" t="s">
-        <v>86</v>
-      </c>
-      <c r="G6" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" t="s">
-        <v>87</v>
-      </c>
-      <c r="I6" t="s">
-        <v>88</v>
-      </c>
-      <c r="J6" t="s">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>267</v>
+      </c>
+      <c r="B19" t="s">
+        <v>268</v>
+      </c>
+      <c r="C19" t="s">
+        <v>269</v>
+      </c>
+      <c r="D19" t="s">
+        <v>270</v>
+      </c>
+      <c r="E19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" t="s">
+        <v>271</v>
+      </c>
+      <c r="H19" t="s">
         <v>89</v>
       </c>
-      <c r="K6" t="s">
-        <v>90</v>
-      </c>
-      <c r="L6" t="s">
-        <v>28</v>
-      </c>
-      <c r="M6" t="s">
-        <v>91</v>
-      </c>
-      <c r="N6" t="s">
-        <v>92</v>
-      </c>
-      <c r="O6" t="s">
-        <v>93</v>
-      </c>
-      <c r="P6" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>95</v>
+      <c r="I19" t="s">
+        <v>26</v>
+      </c>
+      <c r="J19" t="s">
+        <v>272</v>
+      </c>
+      <c r="K19" t="s">
+        <v>273</v>
+      </c>
+      <c r="L19" t="s">
+        <v>274</v>
+      </c>
+      <c r="M19" t="s">
+        <v>275</v>
+      </c>
+      <c r="N19" t="s">
+        <v>31</v>
+      </c>
+      <c r="O19" t="s">
+        <v>276</v>
+      </c>
+      <c r="P19" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>278</v>
+      </c>
+      <c r="R19" t="s">
+        <v>279</v>
+      </c>
+      <c r="S19" t="s">
+        <v>280</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B7" t="s">
-        <v>97</v>
-      </c>
-      <c r="C7" t="s">
-        <v>98</v>
-      </c>
-      <c r="D7" t="s">
-        <v>99</v>
-      </c>
-      <c r="E7" t="s">
-        <v>100</v>
-      </c>
-      <c r="F7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" t="s">
-        <v>101</v>
-      </c>
-      <c r="I7" t="s">
-        <v>102</v>
-      </c>
-      <c r="J7" t="s">
-        <v>103</v>
-      </c>
-      <c r="K7" t="s">
-        <v>104</v>
-      </c>
-      <c r="L7" t="s">
-        <v>28</v>
-      </c>
-      <c r="M7" t="s">
-        <v>105</v>
-      </c>
-      <c r="N7" t="s">
-        <v>106</v>
-      </c>
-      <c r="O7" t="s">
-        <v>107</v>
-      </c>
-      <c r="P7" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>109</v>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>281</v>
+      </c>
+      <c r="B20" t="s">
+        <v>282</v>
+      </c>
+      <c r="C20" t="s">
+        <v>283</v>
+      </c>
+      <c r="D20" t="s">
+        <v>284</v>
+      </c>
+      <c r="E20" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" t="s">
+        <v>285</v>
+      </c>
+      <c r="H20" t="s">
+        <v>42</v>
+      </c>
+      <c r="I20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J20" t="s">
+        <v>286</v>
+      </c>
+      <c r="K20" t="s">
+        <v>287</v>
+      </c>
+      <c r="L20" t="s">
+        <v>288</v>
+      </c>
+      <c r="M20" t="s">
+        <v>289</v>
+      </c>
+      <c r="N20" t="s">
+        <v>31</v>
+      </c>
+      <c r="O20" t="s">
+        <v>290</v>
+      </c>
+      <c r="P20" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>292</v>
+      </c>
+      <c r="R20" t="s">
+        <v>293</v>
+      </c>
+      <c r="S20" t="s">
+        <v>294</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>110</v>
-      </c>
-      <c r="B8" t="s">
-        <v>111</v>
-      </c>
-      <c r="C8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D8" t="s">
-        <v>113</v>
-      </c>
-      <c r="E8" t="s">
-        <v>114</v>
-      </c>
-      <c r="F8" t="s">
-        <v>86</v>
-      </c>
-      <c r="G8" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" t="s">
-        <v>115</v>
-      </c>
-      <c r="I8" t="s">
-        <v>116</v>
-      </c>
-      <c r="J8" t="s">
-        <v>117</v>
-      </c>
-      <c r="K8" t="s">
-        <v>118</v>
-      </c>
-      <c r="L8" t="s">
-        <v>28</v>
-      </c>
-      <c r="M8" t="s">
-        <v>119</v>
-      </c>
-      <c r="N8" t="s">
-        <v>120</v>
-      </c>
-      <c r="O8" t="s">
-        <v>121</v>
-      </c>
-      <c r="P8" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>123</v>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>295</v>
+      </c>
+      <c r="B21" t="s">
+        <v>296</v>
+      </c>
+      <c r="C21" t="s">
+        <v>297</v>
+      </c>
+      <c r="D21" t="s">
+        <v>298</v>
+      </c>
+      <c r="E21" t="s">
+        <v>23</v>
+      </c>
+      <c r="F21" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" t="s">
+        <v>299</v>
+      </c>
+      <c r="H21" t="s">
+        <v>74</v>
+      </c>
+      <c r="I21" t="s">
+        <v>26</v>
+      </c>
+      <c r="J21" t="s">
+        <v>300</v>
+      </c>
+      <c r="K21" t="s">
+        <v>301</v>
+      </c>
+      <c r="L21" t="s">
+        <v>302</v>
+      </c>
+      <c r="M21" t="s">
+        <v>303</v>
+      </c>
+      <c r="N21" t="s">
+        <v>31</v>
+      </c>
+      <c r="O21" t="s">
+        <v>304</v>
+      </c>
+      <c r="P21" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>306</v>
+      </c>
+      <c r="R21" t="s">
+        <v>307</v>
+      </c>
+      <c r="S21" t="s">
+        <v>308</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>124</v>
-      </c>
-      <c r="B9" t="s">
-        <v>125</v>
-      </c>
-      <c r="C9" t="s">
-        <v>126</v>
-      </c>
-      <c r="D9" t="s">
-        <v>127</v>
-      </c>
-      <c r="E9" t="s">
-        <v>128</v>
-      </c>
-      <c r="F9" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" t="s">
-        <v>129</v>
-      </c>
-      <c r="I9" t="s">
-        <v>130</v>
-      </c>
-      <c r="J9" t="s">
-        <v>131</v>
-      </c>
-      <c r="K9" t="s">
-        <v>132</v>
-      </c>
-      <c r="L9" t="s">
-        <v>28</v>
-      </c>
-      <c r="M9" t="s">
-        <v>133</v>
-      </c>
-      <c r="N9" t="s">
-        <v>134</v>
-      </c>
-      <c r="O9" t="s">
-        <v>135</v>
-      </c>
-      <c r="P9" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>137</v>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>309</v>
+      </c>
+      <c r="B22" t="s">
+        <v>310</v>
+      </c>
+      <c r="C22" t="s">
+        <v>311</v>
+      </c>
+      <c r="D22" t="s">
+        <v>312</v>
+      </c>
+      <c r="E22" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22" t="s">
+        <v>313</v>
+      </c>
+      <c r="H22" t="s">
+        <v>89</v>
+      </c>
+      <c r="I22" t="s">
+        <v>26</v>
+      </c>
+      <c r="J22" t="s">
+        <v>314</v>
+      </c>
+      <c r="K22" t="s">
+        <v>315</v>
+      </c>
+      <c r="L22" t="s">
+        <v>316</v>
+      </c>
+      <c r="M22" t="s">
+        <v>317</v>
+      </c>
+      <c r="N22" t="s">
+        <v>31</v>
+      </c>
+      <c r="O22" t="s">
+        <v>318</v>
+      </c>
+      <c r="P22" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>320</v>
+      </c>
+      <c r="R22" t="s">
+        <v>321</v>
+      </c>
+      <c r="S22" t="s">
+        <v>322</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>138</v>
-      </c>
-      <c r="B10" t="s">
-        <v>139</v>
-      </c>
-      <c r="C10" t="s">
-        <v>140</v>
-      </c>
-      <c r="D10" t="s">
-        <v>141</v>
-      </c>
-      <c r="E10" t="s">
-        <v>142</v>
-      </c>
-      <c r="F10" t="s">
-        <v>71</v>
-      </c>
-      <c r="G10" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" t="s">
-        <v>143</v>
-      </c>
-      <c r="I10" t="s">
-        <v>144</v>
-      </c>
-      <c r="J10" t="s">
-        <v>145</v>
-      </c>
-      <c r="K10" t="s">
-        <v>146</v>
-      </c>
-      <c r="L10" t="s">
-        <v>28</v>
-      </c>
-      <c r="M10" t="s">
-        <v>147</v>
-      </c>
-      <c r="N10" t="s">
-        <v>148</v>
-      </c>
-      <c r="O10" t="s">
-        <v>149</v>
-      </c>
-      <c r="P10" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>151</v>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>323</v>
+      </c>
+      <c r="B23" t="s">
+        <v>324</v>
+      </c>
+      <c r="C23" t="s">
+        <v>325</v>
+      </c>
+      <c r="D23" t="s">
+        <v>326</v>
+      </c>
+      <c r="E23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23" t="s">
+        <v>23</v>
+      </c>
+      <c r="G23" t="s">
+        <v>327</v>
+      </c>
+      <c r="H23" t="s">
+        <v>89</v>
+      </c>
+      <c r="I23" t="s">
+        <v>26</v>
+      </c>
+      <c r="J23" t="s">
+        <v>328</v>
+      </c>
+      <c r="K23" t="s">
+        <v>329</v>
+      </c>
+      <c r="L23" t="s">
+        <v>330</v>
+      </c>
+      <c r="M23" t="s">
+        <v>331</v>
+      </c>
+      <c r="N23" t="s">
+        <v>31</v>
+      </c>
+      <c r="O23" t="s">
+        <v>332</v>
+      </c>
+      <c r="P23" t="s">
+        <v>333</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>334</v>
+      </c>
+      <c r="R23" t="s">
+        <v>335</v>
+      </c>
+      <c r="S23" t="s">
+        <v>336</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>152</v>
-      </c>
-      <c r="B11" t="s">
-        <v>153</v>
-      </c>
-      <c r="C11" t="s">
-        <v>154</v>
-      </c>
-      <c r="D11" t="s">
-        <v>155</v>
-      </c>
-      <c r="E11" t="s">
-        <v>156</v>
-      </c>
-      <c r="F11" t="s">
-        <v>39</v>
-      </c>
-      <c r="G11" t="s">
-        <v>23</v>
-      </c>
-      <c r="H11" t="s">
-        <v>157</v>
-      </c>
-      <c r="I11" t="s">
-        <v>158</v>
-      </c>
-      <c r="J11" t="s">
-        <v>159</v>
-      </c>
-      <c r="K11" t="s">
-        <v>160</v>
-      </c>
-      <c r="L11" t="s">
-        <v>28</v>
-      </c>
-      <c r="M11" t="s">
-        <v>161</v>
-      </c>
-      <c r="N11" t="s">
-        <v>162</v>
-      </c>
-      <c r="O11" t="s">
-        <v>163</v>
-      </c>
-      <c r="P11" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>166</v>
-      </c>
-      <c r="B12" t="s">
-        <v>167</v>
-      </c>
-      <c r="C12" t="s">
-        <v>168</v>
-      </c>
-      <c r="D12" t="s">
-        <v>169</v>
-      </c>
-      <c r="E12" t="s">
-        <v>170</v>
-      </c>
-      <c r="F12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H12" t="s">
-        <v>171</v>
-      </c>
-      <c r="I12" t="s">
-        <v>172</v>
-      </c>
-      <c r="J12" t="s">
-        <v>173</v>
-      </c>
-      <c r="K12" t="s">
-        <v>174</v>
-      </c>
-      <c r="L12" t="s">
-        <v>28</v>
-      </c>
-      <c r="M12" t="s">
-        <v>175</v>
-      </c>
-      <c r="N12" t="s">
-        <v>176</v>
-      </c>
-      <c r="O12" t="s">
-        <v>177</v>
-      </c>
-      <c r="P12" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>180</v>
-      </c>
-      <c r="B13" t="s">
-        <v>181</v>
-      </c>
-      <c r="C13" t="s">
-        <v>182</v>
-      </c>
-      <c r="D13" t="s">
-        <v>183</v>
-      </c>
-      <c r="E13" t="s">
-        <v>184</v>
-      </c>
-      <c r="F13" t="s">
-        <v>71</v>
-      </c>
-      <c r="G13" t="s">
-        <v>23</v>
-      </c>
-      <c r="H13" t="s">
-        <v>185</v>
-      </c>
-      <c r="I13" t="s">
-        <v>186</v>
-      </c>
-      <c r="J13" t="s">
-        <v>187</v>
-      </c>
-      <c r="K13" t="s">
-        <v>188</v>
-      </c>
-      <c r="L13" t="s">
-        <v>28</v>
-      </c>
-      <c r="M13" t="s">
-        <v>189</v>
-      </c>
-      <c r="N13" t="s">
-        <v>190</v>
-      </c>
-      <c r="O13" t="s">
-        <v>191</v>
-      </c>
-      <c r="P13" t="s">
-        <v>192</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>194</v>
-      </c>
-      <c r="B14" t="s">
-        <v>195</v>
-      </c>
-      <c r="C14" t="s">
-        <v>196</v>
-      </c>
-      <c r="D14" t="s">
-        <v>197</v>
-      </c>
-      <c r="E14" t="s">
-        <v>198</v>
-      </c>
-      <c r="F14" t="s">
-        <v>55</v>
-      </c>
-      <c r="G14" t="s">
-        <v>23</v>
-      </c>
-      <c r="H14" t="s">
-        <v>199</v>
-      </c>
-      <c r="I14" t="s">
-        <v>200</v>
-      </c>
-      <c r="J14" t="s">
-        <v>201</v>
-      </c>
-      <c r="K14" t="s">
-        <v>202</v>
-      </c>
-      <c r="L14" t="s">
-        <v>28</v>
-      </c>
-      <c r="M14" t="s">
-        <v>203</v>
-      </c>
-      <c r="N14" t="s">
-        <v>204</v>
-      </c>
-      <c r="O14" t="s">
-        <v>205</v>
-      </c>
-      <c r="P14" t="s">
-        <v>206</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>208</v>
-      </c>
-      <c r="B15" t="s">
-        <v>209</v>
-      </c>
-      <c r="C15" t="s">
-        <v>210</v>
-      </c>
-      <c r="D15" t="s">
-        <v>211</v>
-      </c>
-      <c r="E15" t="s">
-        <v>212</v>
-      </c>
-      <c r="F15" t="s">
-        <v>55</v>
-      </c>
-      <c r="G15" t="s">
-        <v>56</v>
-      </c>
-      <c r="H15" t="s">
-        <v>213</v>
-      </c>
-      <c r="I15" t="s">
-        <v>214</v>
-      </c>
-      <c r="J15" t="s">
-        <v>215</v>
-      </c>
-      <c r="K15" t="s">
-        <v>216</v>
-      </c>
-      <c r="L15" t="s">
-        <v>28</v>
-      </c>
-      <c r="M15" t="s">
-        <v>217</v>
-      </c>
-      <c r="N15" t="s">
-        <v>218</v>
-      </c>
-      <c r="O15" t="s">
-        <v>219</v>
-      </c>
-      <c r="P15" t="s">
-        <v>220</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>222</v>
-      </c>
-      <c r="B16" t="s">
-        <v>223</v>
-      </c>
-      <c r="C16" t="s">
-        <v>224</v>
-      </c>
-      <c r="D16" t="s">
-        <v>225</v>
-      </c>
-      <c r="E16" t="s">
-        <v>226</v>
-      </c>
-      <c r="F16" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" t="s">
-        <v>23</v>
-      </c>
-      <c r="H16" t="s">
-        <v>227</v>
-      </c>
-      <c r="I16" t="s">
-        <v>228</v>
-      </c>
-      <c r="J16" t="s">
-        <v>229</v>
-      </c>
-      <c r="K16" t="s">
-        <v>230</v>
-      </c>
-      <c r="L16" t="s">
-        <v>28</v>
-      </c>
-      <c r="M16" t="s">
-        <v>231</v>
-      </c>
-      <c r="N16" t="s">
-        <v>232</v>
-      </c>
-      <c r="O16" t="s">
-        <v>233</v>
-      </c>
-      <c r="P16" t="s">
-        <v>234</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>236</v>
-      </c>
-      <c r="B17" t="s">
-        <v>237</v>
-      </c>
-      <c r="C17" t="s">
-        <v>238</v>
-      </c>
-      <c r="D17" t="s">
-        <v>239</v>
-      </c>
-      <c r="E17" t="s">
-        <v>240</v>
-      </c>
-      <c r="F17" t="s">
-        <v>55</v>
-      </c>
-      <c r="G17" t="s">
-        <v>23</v>
-      </c>
-      <c r="H17" t="s">
-        <v>241</v>
-      </c>
-      <c r="I17" t="s">
-        <v>242</v>
-      </c>
-      <c r="J17" t="s">
-        <v>243</v>
-      </c>
-      <c r="K17" t="s">
-        <v>244</v>
-      </c>
-      <c r="L17" t="s">
-        <v>28</v>
-      </c>
-      <c r="M17" t="s">
-        <v>245</v>
-      </c>
-      <c r="N17" t="s">
-        <v>246</v>
-      </c>
-      <c r="O17" t="s">
-        <v>247</v>
-      </c>
-      <c r="P17" t="s">
-        <v>248</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>250</v>
-      </c>
-      <c r="B18" t="s">
-        <v>251</v>
-      </c>
-      <c r="C18" t="s">
-        <v>252</v>
-      </c>
-      <c r="D18" t="s">
-        <v>253</v>
-      </c>
-      <c r="E18" t="s">
-        <v>254</v>
-      </c>
-      <c r="F18" t="s">
-        <v>71</v>
-      </c>
-      <c r="G18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H18" t="s">
-        <v>255</v>
-      </c>
-      <c r="I18" t="s">
-        <v>256</v>
-      </c>
-      <c r="J18" t="s">
-        <v>257</v>
-      </c>
-      <c r="K18" t="s">
-        <v>258</v>
-      </c>
-      <c r="L18" t="s">
-        <v>28</v>
-      </c>
-      <c r="M18" t="s">
-        <v>259</v>
-      </c>
-      <c r="N18" t="s">
-        <v>260</v>
-      </c>
-      <c r="O18" t="s">
-        <v>261</v>
-      </c>
-      <c r="P18" t="s">
-        <v>262</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>264</v>
-      </c>
-      <c r="B19" t="s">
-        <v>265</v>
-      </c>
-      <c r="C19" t="s">
-        <v>266</v>
-      </c>
-      <c r="D19" t="s">
-        <v>267</v>
-      </c>
-      <c r="E19" t="s">
-        <v>268</v>
-      </c>
-      <c r="F19" t="s">
-        <v>86</v>
-      </c>
-      <c r="G19" t="s">
-        <v>23</v>
-      </c>
-      <c r="H19" t="s">
-        <v>269</v>
-      </c>
-      <c r="I19" t="s">
-        <v>270</v>
-      </c>
-      <c r="J19" t="s">
-        <v>271</v>
-      </c>
-      <c r="K19" t="s">
-        <v>272</v>
-      </c>
-      <c r="L19" t="s">
-        <v>28</v>
-      </c>
-      <c r="M19" t="s">
-        <v>273</v>
-      </c>
-      <c r="N19" t="s">
-        <v>274</v>
-      </c>
-      <c r="O19" t="s">
-        <v>275</v>
-      </c>
-      <c r="P19" t="s">
-        <v>276</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>278</v>
-      </c>
-      <c r="B20" t="s">
-        <v>279</v>
-      </c>
-      <c r="C20" t="s">
-        <v>280</v>
-      </c>
-      <c r="D20" t="s">
-        <v>281</v>
-      </c>
-      <c r="E20" t="s">
-        <v>282</v>
-      </c>
-      <c r="F20" t="s">
-        <v>39</v>
-      </c>
-      <c r="G20" t="s">
-        <v>23</v>
-      </c>
-      <c r="H20" t="s">
-        <v>283</v>
-      </c>
-      <c r="I20" t="s">
-        <v>284</v>
-      </c>
-      <c r="J20" t="s">
-        <v>285</v>
-      </c>
-      <c r="K20" t="s">
-        <v>286</v>
-      </c>
-      <c r="L20" t="s">
-        <v>28</v>
-      </c>
-      <c r="M20" t="s">
-        <v>287</v>
-      </c>
-      <c r="N20" t="s">
-        <v>288</v>
-      </c>
-      <c r="O20" t="s">
-        <v>289</v>
-      </c>
-      <c r="P20" t="s">
-        <v>290</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>292</v>
-      </c>
-      <c r="B21" t="s">
-        <v>293</v>
-      </c>
-      <c r="C21" t="s">
-        <v>294</v>
-      </c>
-      <c r="D21" t="s">
-        <v>295</v>
-      </c>
-      <c r="E21" t="s">
-        <v>296</v>
-      </c>
-      <c r="F21" t="s">
-        <v>71</v>
-      </c>
-      <c r="G21" t="s">
-        <v>23</v>
-      </c>
-      <c r="H21" t="s">
-        <v>297</v>
-      </c>
-      <c r="I21" t="s">
-        <v>298</v>
-      </c>
-      <c r="J21" t="s">
-        <v>299</v>
-      </c>
-      <c r="K21" t="s">
-        <v>300</v>
-      </c>
-      <c r="L21" t="s">
-        <v>28</v>
-      </c>
-      <c r="M21" t="s">
-        <v>301</v>
-      </c>
-      <c r="N21" t="s">
-        <v>302</v>
-      </c>
-      <c r="O21" t="s">
-        <v>303</v>
-      </c>
-      <c r="P21" t="s">
-        <v>304</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>306</v>
-      </c>
-      <c r="B22" t="s">
-        <v>307</v>
-      </c>
-      <c r="C22" t="s">
-        <v>308</v>
-      </c>
-      <c r="D22" t="s">
-        <v>309</v>
-      </c>
-      <c r="E22" t="s">
-        <v>310</v>
-      </c>
-      <c r="F22" t="s">
-        <v>86</v>
-      </c>
-      <c r="G22" t="s">
-        <v>23</v>
-      </c>
-      <c r="H22" t="s">
-        <v>311</v>
-      </c>
-      <c r="I22" t="s">
-        <v>312</v>
-      </c>
-      <c r="J22" t="s">
-        <v>313</v>
-      </c>
-      <c r="K22" t="s">
-        <v>314</v>
-      </c>
-      <c r="L22" t="s">
-        <v>28</v>
-      </c>
-      <c r="M22" t="s">
-        <v>315</v>
-      </c>
-      <c r="N22" t="s">
-        <v>316</v>
-      </c>
-      <c r="O22" t="s">
-        <v>317</v>
-      </c>
-      <c r="P22" t="s">
-        <v>318</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>320</v>
-      </c>
-      <c r="B23" t="s">
-        <v>321</v>
-      </c>
-      <c r="C23" t="s">
-        <v>322</v>
-      </c>
-      <c r="D23" t="s">
-        <v>323</v>
-      </c>
-      <c r="E23" t="s">
-        <v>324</v>
-      </c>
-      <c r="F23" t="s">
-        <v>86</v>
-      </c>
-      <c r="G23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H23" t="s">
-        <v>325</v>
-      </c>
-      <c r="I23" t="s">
-        <v>326</v>
-      </c>
-      <c r="J23" t="s">
-        <v>327</v>
-      </c>
-      <c r="K23" t="s">
-        <v>328</v>
-      </c>
-      <c r="L23" t="s">
-        <v>28</v>
-      </c>
-      <c r="M23" t="s">
-        <v>329</v>
-      </c>
-      <c r="N23" t="s">
-        <v>330</v>
-      </c>
-      <c r="O23" t="s">
-        <v>331</v>
-      </c>
-      <c r="P23" t="s">
-        <v>332</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B24" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C24" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D24" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="E24" t="s">
-        <v>338</v>
+        <v>23</v>
       </c>
       <c r="F24" t="s">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="G24" t="s">
-        <v>23</v>
+        <v>341</v>
       </c>
       <c r="H24" t="s">
-        <v>339</v>
+        <v>89</v>
       </c>
       <c r="I24" t="s">
-        <v>340</v>
+        <v>26</v>
       </c>
       <c r="J24" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K24" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L24" t="s">
-        <v>28</v>
+        <v>344</v>
       </c>
       <c r="M24" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="N24" t="s">
-        <v>344</v>
+        <v>31</v>
       </c>
       <c r="O24" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P24" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q24" t="s">
-        <v>347</v>
+        <v>348</v>
+      </c>
+      <c r="R24" t="s">
+        <v>349</v>
+      </c>
+      <c r="S24" t="s">
+        <v>350</v>
       </c>
     </row>
   </sheetData>
